--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,6 +1626,4833 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120302939</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91863</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>735534</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7459189</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120302932</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96868</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>734754</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7459460</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120302935</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>734905</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7459394</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fem födosökande individer</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120302929</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96868</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>734710</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7459012</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120302930</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>734730</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7459077</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120302933</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56525</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>735031</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7459592</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120302927</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79115</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>735126</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7459188</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120302940</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96868</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>735608</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7459127</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120302937</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>735316</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7459160</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120302936</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>735289</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7459144</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120302934</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57738</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>734919</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7459493</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120302888</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>733085</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7458027</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120302893</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>732993</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7457764</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120302886</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>733007</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7457822</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120302892</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56514</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>732912</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7457768</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120302894</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79115</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>733092</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7457724</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120302913</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>731549</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7457309</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120302922</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>731611</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7457228</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120302916</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79115</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>731728</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7457308</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120302917</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>731714</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7457298</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120302914</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90724</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>731763</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7457160</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120302920</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>731622</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7457276</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120302915</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>731716</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7457334</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120302923</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>731716</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7457137</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120302908</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>731245</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7457418</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hane</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120302906</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>731352</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7457246</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120302912</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>731416</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7457247</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hane</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120302924</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>731752</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7457204</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackspår på högstubbe</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120302911</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>731347</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7457280</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120302921</v>
+      </c>
+      <c r="B39" t="n">
+        <v>56522</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>731604</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7457238</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>En individ</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120302910</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>731293</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7457377</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar på granlåga</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120302918</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>731673</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7457289</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120302919</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>731642</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7457290</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120302896</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79115</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>733023</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7457503</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120302901</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57738</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>733049</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7457132</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120302897</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>732853</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7457442</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120302895</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>733086</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7457578</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120302878</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>733152</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7457234</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120302882</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>733156</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7457547</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120302898</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>732795</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7457432</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120302902</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79115</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>733046</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7457090</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120302877</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>733127</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7457136</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fyra individer</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120302899</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>732829</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7457380</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120302900</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>733011</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7457133</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120302879</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78262</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>733150</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7457273</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120302903</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57738</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>732779</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7457059</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1631,7 +1631,7 @@
         <v>120302939</v>
       </c>
       <c r="B10" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302932</v>
+        <v>120302935</v>
       </c>
       <c r="B11" t="n">
-        <v>96868</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>734754</v>
+        <v>734905</v>
       </c>
       <c r="R11" t="n">
-        <v>7459460</v>
+        <v>7459394</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,6 +1811,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302935</v>
+        <v>120302934</v>
       </c>
       <c r="B12" t="n">
-        <v>57463</v>
+        <v>57748</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,21 +1858,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>734905</v>
+        <v>734919</v>
       </c>
       <c r="R12" t="n">
-        <v>7459394</v>
+        <v>7459493</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1917,7 +1922,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fem födosökande individer</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120302929</v>
+        <v>120302940</v>
       </c>
       <c r="B13" t="n">
-        <v>96868</v>
+        <v>96891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>734710</v>
+        <v>735608</v>
       </c>
       <c r="R13" t="n">
-        <v>7459012</v>
+        <v>7459127</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2046,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302930</v>
+        <v>120302929</v>
       </c>
       <c r="B14" t="n">
-        <v>56522</v>
+        <v>96891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,21 +2067,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>734730</v>
+        <v>734710</v>
       </c>
       <c r="R14" t="n">
-        <v>7459077</v>
+        <v>7459012</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2122,11 +2127,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302933</v>
+        <v>120302930</v>
       </c>
       <c r="B15" t="n">
-        <v>56525</v>
+        <v>56532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735031</v>
+        <v>734730</v>
       </c>
       <c r="R15" t="n">
-        <v>7459592</v>
+        <v>7459077</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302927</v>
+        <v>120302933</v>
       </c>
       <c r="B16" t="n">
-        <v>79115</v>
+        <v>56535</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,25 +2272,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735126</v>
+        <v>735031</v>
       </c>
       <c r="R16" t="n">
-        <v>7459188</v>
+        <v>7459592</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,12 +2330,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302940</v>
+        <v>120302927</v>
       </c>
       <c r="B17" t="n">
-        <v>96868</v>
+        <v>79131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2374,25 +2379,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735608</v>
+        <v>735126</v>
       </c>
       <c r="R17" t="n">
-        <v>7459127</v>
+        <v>7459188</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,12 +2437,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302937</v>
+        <v>120302936</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735316</v>
+        <v>735289</v>
       </c>
       <c r="R18" t="n">
-        <v>7459160</v>
+        <v>7459144</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,11 +2545,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302936</v>
+        <v>120302932</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>96891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735289</v>
+        <v>734754</v>
       </c>
       <c r="R19" t="n">
-        <v>7459144</v>
+        <v>7459460</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302934</v>
+        <v>120302937</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734919</v>
+        <v>735316</v>
       </c>
       <c r="R20" t="n">
-        <v>7459493</v>
+        <v>7459160</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2783,7 +2783,7 @@
         <v>120302888</v>
       </c>
       <c r="B21" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120302893</v>
+        <v>120302886</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>96885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>732993</v>
+        <v>733007</v>
       </c>
       <c r="R22" t="n">
-        <v>7457764</v>
+        <v>7457822</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2958,11 +2958,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120302886</v>
+        <v>120302894</v>
       </c>
       <c r="B23" t="n">
-        <v>96862</v>
+        <v>79131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,25 +2996,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733007</v>
+        <v>733092</v>
       </c>
       <c r="R23" t="n">
-        <v>7457822</v>
+        <v>7457724</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3094,7 +3089,7 @@
         <v>120302892</v>
       </c>
       <c r="B24" t="n">
-        <v>56514</v>
+        <v>56524</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,10 +3193,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120302894</v>
+        <v>120302893</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3214,21 +3209,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3238,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733092</v>
+        <v>732993</v>
       </c>
       <c r="R25" t="n">
-        <v>7457724</v>
+        <v>7457764</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3274,6 +3269,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302913</v>
+        <v>120302916</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>79131</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731549</v>
+        <v>731728</v>
       </c>
       <c r="R26" t="n">
-        <v>7457309</v>
+        <v>7457308</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,11 +3376,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3402,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302922</v>
+        <v>120302908</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>56532</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3414,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731611</v>
+        <v>731245</v>
       </c>
       <c r="R27" t="n">
-        <v>7457228</v>
+        <v>7457418</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3487,7 +3482,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302916</v>
+        <v>120302911</v>
       </c>
       <c r="B28" t="n">
-        <v>79115</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3530,21 +3525,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731728</v>
+        <v>731347</v>
       </c>
       <c r="R28" t="n">
-        <v>7457308</v>
+        <v>7457280</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3590,6 +3585,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302917</v>
+        <v>120302919</v>
       </c>
       <c r="B29" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731714</v>
+        <v>731642</v>
       </c>
       <c r="R29" t="n">
-        <v>7457298</v>
+        <v>7457290</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302914</v>
+        <v>120302918</v>
       </c>
       <c r="B30" t="n">
-        <v>90724</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,21 +3739,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731763</v>
+        <v>731673</v>
       </c>
       <c r="R30" t="n">
-        <v>7457160</v>
+        <v>7457289</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3799,6 +3799,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3830,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302920</v>
+        <v>120302914</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>90742</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3841,21 +3846,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731622</v>
+        <v>731763</v>
       </c>
       <c r="R31" t="n">
-        <v>7457276</v>
+        <v>7457160</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3927,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302915</v>
+        <v>120302913</v>
       </c>
       <c r="B32" t="n">
-        <v>57421</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,20 +3944,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3967,10 +3972,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731716</v>
+        <v>731549</v>
       </c>
       <c r="R32" t="n">
-        <v>7457334</v>
+        <v>7457309</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4003,6 +4008,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4029,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302923</v>
+        <v>120302910</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4045,21 +4055,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4069,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731716</v>
+        <v>731293</v>
       </c>
       <c r="R33" t="n">
-        <v>7457137</v>
+        <v>7457377</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4109,7 +4119,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4136,10 +4146,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120302908</v>
+        <v>120302921</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4176,10 +4186,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731245</v>
+        <v>731604</v>
       </c>
       <c r="R34" t="n">
-        <v>7457418</v>
+        <v>7457238</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4216,7 +4226,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302906</v>
+        <v>120302912</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>56532</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4255,25 +4265,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4283,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731352</v>
+        <v>731416</v>
       </c>
       <c r="R35" t="n">
-        <v>7457246</v>
+        <v>7457247</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4319,6 +4329,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4345,10 +4360,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302912</v>
+        <v>120302920</v>
       </c>
       <c r="B36" t="n">
-        <v>56522</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4357,25 +4372,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4385,10 +4400,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731416</v>
+        <v>731622</v>
       </c>
       <c r="R36" t="n">
-        <v>7457247</v>
+        <v>7457276</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4421,11 +4436,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hane</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4455,7 +4465,7 @@
         <v>120302924</v>
       </c>
       <c r="B37" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4559,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302911</v>
+        <v>120302906</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4575,21 +4585,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4599,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731347</v>
+        <v>731352</v>
       </c>
       <c r="R38" t="n">
-        <v>7457280</v>
+        <v>7457246</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4635,11 +4645,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302921</v>
+        <v>120302922</v>
       </c>
       <c r="B39" t="n">
-        <v>56522</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4678,25 +4683,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4706,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731604</v>
+        <v>731611</v>
       </c>
       <c r="R39" t="n">
-        <v>7457238</v>
+        <v>7457228</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4746,7 +4751,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>En individ</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4773,10 +4778,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302910</v>
+        <v>120302915</v>
       </c>
       <c r="B40" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4785,25 +4790,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731293</v>
+        <v>731716</v>
       </c>
       <c r="R40" t="n">
-        <v>7457377</v>
+        <v>7457334</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4849,11 +4854,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302918</v>
+        <v>120302923</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731673</v>
+        <v>731716</v>
       </c>
       <c r="R41" t="n">
-        <v>7457289</v>
+        <v>7457137</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302919</v>
+        <v>120302917</v>
       </c>
       <c r="B42" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731642</v>
+        <v>731714</v>
       </c>
       <c r="R42" t="n">
-        <v>7457290</v>
+        <v>7457298</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5094,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120302896</v>
+        <v>120302901</v>
       </c>
       <c r="B43" t="n">
-        <v>79115</v>
+        <v>57748</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733023</v>
+        <v>733049</v>
       </c>
       <c r="R43" t="n">
-        <v>7457503</v>
+        <v>7457132</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5196,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302901</v>
+        <v>120302877</v>
       </c>
       <c r="B44" t="n">
-        <v>57738</v>
+        <v>57431</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5208,25 +5208,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103001</v>
+        <v>103031</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733049</v>
+        <v>733127</v>
       </c>
       <c r="R44" t="n">
-        <v>7457132</v>
+        <v>7457136</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5272,6 +5272,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5298,10 +5303,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120302897</v>
+        <v>120302899</v>
       </c>
       <c r="B45" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5314,16 +5319,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5338,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732853</v>
+        <v>732829</v>
       </c>
       <c r="R45" t="n">
-        <v>7457442</v>
+        <v>7457380</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5374,11 +5379,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5405,10 +5405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302895</v>
+        <v>120302878</v>
       </c>
       <c r="B46" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733086</v>
+        <v>733152</v>
       </c>
       <c r="R46" t="n">
-        <v>7457578</v>
+        <v>7457234</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,10 +5512,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120302878</v>
+        <v>120302897</v>
       </c>
       <c r="B47" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733152</v>
+        <v>732853</v>
       </c>
       <c r="R47" t="n">
-        <v>7457234</v>
+        <v>7457442</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5619,10 +5619,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302882</v>
+        <v>120302900</v>
       </c>
       <c r="B48" t="n">
-        <v>5169</v>
+        <v>57431</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,21 +5635,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733156</v>
+        <v>733011</v>
       </c>
       <c r="R48" t="n">
-        <v>7457547</v>
+        <v>7457133</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5695,6 +5695,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5721,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302898</v>
+        <v>120302879</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>78278</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5737,21 +5742,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5761,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>732795</v>
+        <v>733150</v>
       </c>
       <c r="R49" t="n">
-        <v>7457432</v>
+        <v>7457273</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5797,11 +5802,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302902</v>
+        <v>120302898</v>
       </c>
       <c r="B50" t="n">
-        <v>79115</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5844,21 +5844,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733046</v>
+        <v>732795</v>
       </c>
       <c r="R50" t="n">
-        <v>7457090</v>
+        <v>7457432</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5904,6 +5904,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5930,10 +5935,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302877</v>
+        <v>120302903</v>
       </c>
       <c r="B51" t="n">
-        <v>57421</v>
+        <v>57748</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5942,25 +5947,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>103001</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5970,10 +5975,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733127</v>
+        <v>732779</v>
       </c>
       <c r="R51" t="n">
-        <v>7457136</v>
+        <v>7457059</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6000,17 +6005,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Fyra individer</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,10 +6042,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302899</v>
+        <v>120302896</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>79131</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6053,21 +6058,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6077,10 +6082,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>732829</v>
+        <v>733023</v>
       </c>
       <c r="R52" t="n">
-        <v>7457380</v>
+        <v>7457503</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6139,10 +6144,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302900</v>
+        <v>120302902</v>
       </c>
       <c r="B53" t="n">
-        <v>57421</v>
+        <v>79131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6151,25 +6156,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6179,10 +6184,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733011</v>
+        <v>733046</v>
       </c>
       <c r="R53" t="n">
-        <v>7457133</v>
+        <v>7457090</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6215,11 +6220,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302879</v>
+        <v>120302895</v>
       </c>
       <c r="B54" t="n">
-        <v>78262</v>
+        <v>57336</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6262,21 +6262,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733150</v>
+        <v>733086</v>
       </c>
       <c r="R54" t="n">
-        <v>7457273</v>
+        <v>7457578</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6322,6 +6322,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6348,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302903</v>
+        <v>120302882</v>
       </c>
       <c r="B55" t="n">
-        <v>57738</v>
+        <v>5169</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6360,25 +6365,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103001</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6393,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>732779</v>
+        <v>733156</v>
       </c>
       <c r="R55" t="n">
-        <v>7457059</v>
+        <v>7457547</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6418,17 +6423,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -3402,10 +3402,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302908</v>
+        <v>120302911</v>
       </c>
       <c r="B27" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3414,25 +3414,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731245</v>
+        <v>731347</v>
       </c>
       <c r="R27" t="n">
-        <v>7457418</v>
+        <v>7457280</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302911</v>
+        <v>120302908</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3521,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731347</v>
+        <v>731245</v>
       </c>
       <c r="R28" t="n">
-        <v>7457280</v>
+        <v>7457418</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302918</v>
+        <v>120302914</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,21 +3739,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731673</v>
+        <v>731763</v>
       </c>
       <c r="R30" t="n">
-        <v>7457289</v>
+        <v>7457160</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3799,11 +3799,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302914</v>
+        <v>120302918</v>
       </c>
       <c r="B31" t="n">
-        <v>90742</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3846,21 +3841,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3870,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731763</v>
+        <v>731673</v>
       </c>
       <c r="R31" t="n">
-        <v>7457160</v>
+        <v>7457289</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3906,6 +3901,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302913</v>
+        <v>120302910</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3948,21 +3948,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731549</v>
+        <v>731293</v>
       </c>
       <c r="R32" t="n">
-        <v>7457309</v>
+        <v>7457377</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302910</v>
+        <v>120302913</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4055,21 +4055,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731293</v>
+        <v>731549</v>
       </c>
       <c r="R33" t="n">
-        <v>7457377</v>
+        <v>7457309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302935</v>
+        <v>120302930</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>734905</v>
+        <v>734730</v>
       </c>
       <c r="R11" t="n">
-        <v>7459394</v>
+        <v>7459077</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fem födosökande individer</t>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302934</v>
+        <v>120302935</v>
       </c>
       <c r="B12" t="n">
-        <v>57748</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>734919</v>
+        <v>734905</v>
       </c>
       <c r="R12" t="n">
-        <v>7459493</v>
+        <v>7459394</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120302940</v>
+        <v>120302933</v>
       </c>
       <c r="B13" t="n">
-        <v>96891</v>
+        <v>56535</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,21 +1965,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735608</v>
+        <v>735031</v>
       </c>
       <c r="R13" t="n">
-        <v>7459127</v>
+        <v>7459592</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,6 +2025,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302929</v>
+        <v>120302937</v>
       </c>
       <c r="B14" t="n">
-        <v>96891</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,25 +2068,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2091,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>734710</v>
+        <v>735316</v>
       </c>
       <c r="R14" t="n">
-        <v>7459012</v>
+        <v>7459160</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2127,6 +2132,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302930</v>
+        <v>120302932</v>
       </c>
       <c r="B15" t="n">
-        <v>56532</v>
+        <v>96891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734730</v>
+        <v>734754</v>
       </c>
       <c r="R15" t="n">
-        <v>7459077</v>
+        <v>7459460</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,11 +2239,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302933</v>
+        <v>120302940</v>
       </c>
       <c r="B16" t="n">
-        <v>56535</v>
+        <v>96891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,21 +2281,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102613</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735031</v>
+        <v>735608</v>
       </c>
       <c r="R16" t="n">
-        <v>7459592</v>
+        <v>7459127</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2336,11 +2341,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302927</v>
+        <v>120302936</v>
       </c>
       <c r="B17" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735126</v>
+        <v>735289</v>
       </c>
       <c r="R17" t="n">
-        <v>7459188</v>
+        <v>7459144</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302936</v>
+        <v>120302934</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>57748</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735289</v>
+        <v>734919</v>
       </c>
       <c r="R18" t="n">
-        <v>7459144</v>
+        <v>7459493</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2545,6 +2545,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2576,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302932</v>
+        <v>120302927</v>
       </c>
       <c r="B19" t="n">
-        <v>96891</v>
+        <v>79131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,25 +2588,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734754</v>
+        <v>735126</v>
       </c>
       <c r="R19" t="n">
-        <v>7459460</v>
+        <v>7459188</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,12 +2646,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302937</v>
+        <v>120302929</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>96891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2690,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735316</v>
+        <v>734710</v>
       </c>
       <c r="R20" t="n">
-        <v>7459160</v>
+        <v>7459012</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2749,11 +2754,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120302894</v>
+        <v>120302893</v>
       </c>
       <c r="B23" t="n">
-        <v>79131</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733092</v>
+        <v>732993</v>
       </c>
       <c r="R23" t="n">
-        <v>7457724</v>
+        <v>7457764</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3060,6 +3060,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3086,10 +3091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120302892</v>
+        <v>120302894</v>
       </c>
       <c r="B24" t="n">
-        <v>56524</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,21 +3107,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>732912</v>
+        <v>733092</v>
       </c>
       <c r="R24" t="n">
-        <v>7457768</v>
+        <v>7457724</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3162,11 +3167,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,10 +3193,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120302893</v>
+        <v>120302892</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>732993</v>
+        <v>732912</v>
       </c>
       <c r="R25" t="n">
-        <v>7457764</v>
+        <v>7457768</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302916</v>
+        <v>120302913</v>
       </c>
       <c r="B26" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731728</v>
+        <v>731549</v>
       </c>
       <c r="R26" t="n">
-        <v>7457308</v>
+        <v>7457309</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,6 +3376,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3402,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302911</v>
+        <v>120302924</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3418,16 +3423,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731347</v>
+        <v>731752</v>
       </c>
       <c r="R27" t="n">
-        <v>7457280</v>
+        <v>7457204</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3482,7 +3487,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302908</v>
+        <v>120302916</v>
       </c>
       <c r="B28" t="n">
-        <v>56532</v>
+        <v>79131</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3521,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731245</v>
+        <v>731728</v>
       </c>
       <c r="R28" t="n">
-        <v>7457418</v>
+        <v>7457308</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3585,11 +3590,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hane</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302919</v>
+        <v>120302908</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731642</v>
+        <v>731245</v>
       </c>
       <c r="R29" t="n">
-        <v>7457290</v>
+        <v>7457418</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302914</v>
+        <v>120302910</v>
       </c>
       <c r="B30" t="n">
-        <v>90742</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,21 +3739,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731763</v>
+        <v>731293</v>
       </c>
       <c r="R30" t="n">
-        <v>7457160</v>
+        <v>7457377</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3799,6 +3799,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3830,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302918</v>
+        <v>120302912</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,25 +3842,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731673</v>
+        <v>731416</v>
       </c>
       <c r="R31" t="n">
-        <v>7457289</v>
+        <v>7457247</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3905,7 +3910,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,7 +3937,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302910</v>
+        <v>120302906</v>
       </c>
       <c r="B32" t="n">
         <v>90598</v>
@@ -3972,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731293</v>
+        <v>731352</v>
       </c>
       <c r="R32" t="n">
-        <v>7457377</v>
+        <v>7457246</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4008,11 +4013,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,7 +4039,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302913</v>
+        <v>120302918</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731549</v>
+        <v>731673</v>
       </c>
       <c r="R33" t="n">
-        <v>7457309</v>
+        <v>7457289</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4146,10 +4146,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120302921</v>
+        <v>120302923</v>
       </c>
       <c r="B34" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4158,25 +4158,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731604</v>
+        <v>731716</v>
       </c>
       <c r="R34" t="n">
-        <v>7457238</v>
+        <v>7457137</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>En individ</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302912</v>
+        <v>120302917</v>
       </c>
       <c r="B35" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4265,25 +4265,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731416</v>
+        <v>731714</v>
       </c>
       <c r="R35" t="n">
-        <v>7457247</v>
+        <v>7457298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,10 +4360,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302920</v>
+        <v>120302921</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4372,25 +4372,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731622</v>
+        <v>731604</v>
       </c>
       <c r="R36" t="n">
-        <v>7457276</v>
+        <v>7457238</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4436,6 +4436,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4462,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120302924</v>
+        <v>120302915</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4474,20 +4479,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4502,10 +4507,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731752</v>
+        <v>731716</v>
       </c>
       <c r="R37" t="n">
-        <v>7457204</v>
+        <v>7457334</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4538,11 +4543,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,7 +4569,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302906</v>
+        <v>120302920</v>
       </c>
       <c r="B38" t="n">
         <v>90598</v>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731352</v>
+        <v>731622</v>
       </c>
       <c r="R38" t="n">
-        <v>7457246</v>
+        <v>7457276</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4671,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302922</v>
+        <v>120302914</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731611</v>
+        <v>731763</v>
       </c>
       <c r="R39" t="n">
-        <v>7457228</v>
+        <v>7457160</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,11 +4747,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4778,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302915</v>
+        <v>120302919</v>
       </c>
       <c r="B40" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4790,20 +4785,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731716</v>
+        <v>731642</v>
       </c>
       <c r="R40" t="n">
-        <v>7457334</v>
+        <v>7457290</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4854,6 +4849,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4880,7 +4880,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302923</v>
+        <v>120302922</v>
       </c>
       <c r="B41" t="n">
         <v>57320</v>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731716</v>
+        <v>731611</v>
       </c>
       <c r="R41" t="n">
-        <v>7457137</v>
+        <v>7457228</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302917</v>
+        <v>120302911</v>
       </c>
       <c r="B42" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,16 +5003,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731714</v>
+        <v>731347</v>
       </c>
       <c r="R42" t="n">
-        <v>7457298</v>
+        <v>7457280</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5094,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120302901</v>
+        <v>120302899</v>
       </c>
       <c r="B43" t="n">
-        <v>57748</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733049</v>
+        <v>732829</v>
       </c>
       <c r="R43" t="n">
-        <v>7457132</v>
+        <v>7457380</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5196,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302877</v>
+        <v>120302878</v>
       </c>
       <c r="B44" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5208,20 +5208,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733127</v>
+        <v>733152</v>
       </c>
       <c r="R44" t="n">
-        <v>7457136</v>
+        <v>7457234</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Fyra individer</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5303,10 +5303,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120302899</v>
+        <v>120302901</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>57748</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5319,21 +5319,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732829</v>
+        <v>733049</v>
       </c>
       <c r="R45" t="n">
-        <v>7457380</v>
+        <v>7457132</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5405,10 +5405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302878</v>
+        <v>120302902</v>
       </c>
       <c r="B46" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5421,21 +5421,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733152</v>
+        <v>733046</v>
       </c>
       <c r="R46" t="n">
-        <v>7457234</v>
+        <v>7457090</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5481,11 +5481,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,10 +5507,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120302897</v>
+        <v>120302903</v>
       </c>
       <c r="B47" t="n">
-        <v>57336</v>
+        <v>57748</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5528,21 +5523,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5552,10 +5547,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732853</v>
+        <v>732779</v>
       </c>
       <c r="R47" t="n">
-        <v>7457442</v>
+        <v>7457059</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5582,17 +5577,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5619,10 +5614,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302900</v>
+        <v>120302882</v>
       </c>
       <c r="B48" t="n">
-        <v>57431</v>
+        <v>5169</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5635,21 +5630,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5659,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733011</v>
+        <v>733156</v>
       </c>
       <c r="R48" t="n">
-        <v>7457133</v>
+        <v>7457547</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5695,11 +5690,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5726,10 +5716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302879</v>
+        <v>120302898</v>
       </c>
       <c r="B49" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5742,21 +5732,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5766,10 +5756,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733150</v>
+        <v>732795</v>
       </c>
       <c r="R49" t="n">
-        <v>7457273</v>
+        <v>7457432</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5802,6 +5792,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,10 +5823,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302898</v>
+        <v>120302896</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5844,21 +5839,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5868,10 +5863,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>732795</v>
+        <v>733023</v>
       </c>
       <c r="R50" t="n">
-        <v>7457432</v>
+        <v>7457503</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5904,11 +5899,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5935,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302903</v>
+        <v>120302879</v>
       </c>
       <c r="B51" t="n">
-        <v>57748</v>
+        <v>78278</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5951,21 +5941,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5975,10 +5965,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>732779</v>
+        <v>733150</v>
       </c>
       <c r="R51" t="n">
-        <v>7457059</v>
+        <v>7457273</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6005,17 +5995,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6042,10 +6027,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302896</v>
+        <v>120302877</v>
       </c>
       <c r="B52" t="n">
-        <v>79131</v>
+        <v>57431</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6054,25 +6039,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6082,10 +6067,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733023</v>
+        <v>733127</v>
       </c>
       <c r="R52" t="n">
-        <v>7457503</v>
+        <v>7457136</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6118,6 +6103,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6144,10 +6134,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302902</v>
+        <v>120302895</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>57336</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6160,21 +6150,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6184,10 +6174,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733046</v>
+        <v>733086</v>
       </c>
       <c r="R53" t="n">
-        <v>7457090</v>
+        <v>7457578</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6220,6 +6210,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,7 +6241,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302895</v>
+        <v>120302897</v>
       </c>
       <c r="B54" t="n">
         <v>57336</v>
@@ -6286,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733086</v>
+        <v>732853</v>
       </c>
       <c r="R54" t="n">
-        <v>7457578</v>
+        <v>7457442</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6353,10 +6348,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302882</v>
+        <v>120302900</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>57431</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6369,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6393,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733156</v>
+        <v>733011</v>
       </c>
       <c r="R55" t="n">
-        <v>7457547</v>
+        <v>7457133</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6429,6 +6424,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120302939</v>
+        <v>120302933</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>56535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,25 +1640,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>102613</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735534</v>
+        <v>735031</v>
       </c>
       <c r="R10" t="n">
-        <v>7459189</v>
+        <v>7459592</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302930</v>
+        <v>120302940</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>96891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>734730</v>
+        <v>735608</v>
       </c>
       <c r="R11" t="n">
-        <v>7459077</v>
+        <v>7459127</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,11 +1811,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,7 +1837,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302935</v>
+        <v>120302937</v>
       </c>
       <c r="B12" t="n">
         <v>57473</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>734905</v>
+        <v>735316</v>
       </c>
       <c r="R12" t="n">
-        <v>7459394</v>
+        <v>7459160</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fem födosökande individer</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120302933</v>
+        <v>120302932</v>
       </c>
       <c r="B13" t="n">
-        <v>56535</v>
+        <v>96891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102613</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735031</v>
+        <v>734754</v>
       </c>
       <c r="R13" t="n">
-        <v>7459592</v>
+        <v>7459460</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,11 +2020,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302937</v>
+        <v>120302934</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>57748</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,21 +2062,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735316</v>
+        <v>734919</v>
       </c>
       <c r="R14" t="n">
-        <v>7459160</v>
+        <v>7459493</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2163,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302932</v>
+        <v>120302930</v>
       </c>
       <c r="B15" t="n">
-        <v>96891</v>
+        <v>56532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2203,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734754</v>
+        <v>734730</v>
       </c>
       <c r="R15" t="n">
-        <v>7459460</v>
+        <v>7459077</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2239,6 +2229,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302940</v>
+        <v>120302936</v>
       </c>
       <c r="B16" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,25 +2272,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2305,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735608</v>
+        <v>735289</v>
       </c>
       <c r="R16" t="n">
-        <v>7459127</v>
+        <v>7459144</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2367,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302936</v>
+        <v>120302929</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,25 +2374,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2407,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735289</v>
+        <v>734710</v>
       </c>
       <c r="R17" t="n">
-        <v>7459144</v>
+        <v>7459012</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2469,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302934</v>
+        <v>120302935</v>
       </c>
       <c r="B18" t="n">
-        <v>57748</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2485,21 +2480,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2509,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734919</v>
+        <v>734905</v>
       </c>
       <c r="R18" t="n">
-        <v>7459493</v>
+        <v>7459394</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2549,7 +2544,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302929</v>
+        <v>120302939</v>
       </c>
       <c r="B20" t="n">
-        <v>96891</v>
+        <v>91881</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2718,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734710</v>
+        <v>735534</v>
       </c>
       <c r="R20" t="n">
-        <v>7459012</v>
+        <v>7459189</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2754,6 +2749,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120302886</v>
+        <v>120302892</v>
       </c>
       <c r="B22" t="n">
-        <v>96885</v>
+        <v>56524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733007</v>
+        <v>732912</v>
       </c>
       <c r="R22" t="n">
-        <v>7457822</v>
+        <v>7457768</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2958,6 +2958,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2984,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120302893</v>
+        <v>120302894</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3005,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>732993</v>
+        <v>733092</v>
       </c>
       <c r="R23" t="n">
-        <v>7457764</v>
+        <v>7457724</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3060,11 +3065,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,10 +3091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120302894</v>
+        <v>120302886</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>96885</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3103,25 +3103,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733092</v>
+        <v>733007</v>
       </c>
       <c r="R24" t="n">
-        <v>7457724</v>
+        <v>7457822</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3193,10 +3193,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120302892</v>
+        <v>120302893</v>
       </c>
       <c r="B25" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>732912</v>
+        <v>732993</v>
       </c>
       <c r="R25" t="n">
-        <v>7457768</v>
+        <v>7457764</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302913</v>
+        <v>120302920</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731549</v>
+        <v>731622</v>
       </c>
       <c r="R26" t="n">
-        <v>7457309</v>
+        <v>7457276</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,11 +3376,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3402,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302924</v>
+        <v>120302911</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3423,16 +3418,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731752</v>
+        <v>731347</v>
       </c>
       <c r="R27" t="n">
-        <v>7457204</v>
+        <v>7457280</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3487,7 +3482,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår på högstubbe</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3509,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302916</v>
+        <v>120302910</v>
       </c>
       <c r="B28" t="n">
-        <v>79131</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3530,21 +3525,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3549,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731728</v>
+        <v>731293</v>
       </c>
       <c r="R28" t="n">
-        <v>7457308</v>
+        <v>7457377</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3590,6 +3585,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302908</v>
+        <v>120302922</v>
       </c>
       <c r="B29" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3628,25 +3628,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731245</v>
+        <v>731611</v>
       </c>
       <c r="R29" t="n">
-        <v>7457418</v>
+        <v>7457228</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302910</v>
+        <v>120302912</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,25 +3735,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731293</v>
+        <v>731416</v>
       </c>
       <c r="R30" t="n">
-        <v>7457377</v>
+        <v>7457247</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,10 +3830,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302912</v>
+        <v>120302916</v>
       </c>
       <c r="B31" t="n">
-        <v>56532</v>
+        <v>79131</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3842,25 +3842,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731416</v>
+        <v>731728</v>
       </c>
       <c r="R31" t="n">
-        <v>7457247</v>
+        <v>7457308</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3906,11 +3906,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hane</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3937,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302906</v>
+        <v>120302918</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3953,21 +3948,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3977,10 +3972,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731352</v>
+        <v>731673</v>
       </c>
       <c r="R32" t="n">
-        <v>7457246</v>
+        <v>7457289</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4013,6 +4008,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302918</v>
+        <v>120302917</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731673</v>
+        <v>731714</v>
       </c>
       <c r="R33" t="n">
-        <v>7457289</v>
+        <v>7457298</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302917</v>
+        <v>120302914</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>90742</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1588</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731714</v>
+        <v>731763</v>
       </c>
       <c r="R35" t="n">
-        <v>7457298</v>
+        <v>7457160</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4329,11 +4329,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,7 +4355,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302921</v>
+        <v>120302908</v>
       </c>
       <c r="B36" t="n">
         <v>56532</v>
@@ -4400,10 +4395,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731604</v>
+        <v>731245</v>
       </c>
       <c r="R36" t="n">
-        <v>7457238</v>
+        <v>7457418</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4440,7 +4435,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>En individ</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,10 +4462,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120302915</v>
+        <v>120302919</v>
       </c>
       <c r="B37" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4479,20 +4474,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4507,10 +4502,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731716</v>
+        <v>731642</v>
       </c>
       <c r="R37" t="n">
-        <v>7457334</v>
+        <v>7457290</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4543,6 +4538,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,7 +4569,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302920</v>
+        <v>120302906</v>
       </c>
       <c r="B38" t="n">
         <v>90598</v>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731622</v>
+        <v>731352</v>
       </c>
       <c r="R38" t="n">
-        <v>7457276</v>
+        <v>7457246</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4671,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302914</v>
+        <v>120302924</v>
       </c>
       <c r="B39" t="n">
-        <v>90742</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731763</v>
+        <v>731752</v>
       </c>
       <c r="R39" t="n">
-        <v>7457160</v>
+        <v>7457204</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,6 +4747,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4773,10 +4778,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302919</v>
+        <v>120302913</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4789,16 +4794,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731642</v>
+        <v>731549</v>
       </c>
       <c r="R40" t="n">
-        <v>7457290</v>
+        <v>7457309</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4880,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302922</v>
+        <v>120302915</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4892,20 +4897,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4920,10 +4925,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731611</v>
+        <v>731716</v>
       </c>
       <c r="R41" t="n">
-        <v>7457228</v>
+        <v>7457334</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4956,11 +4961,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302911</v>
+        <v>120302921</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4999,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731347</v>
+        <v>731604</v>
       </c>
       <c r="R42" t="n">
-        <v>7457280</v>
+        <v>7457238</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120302899</v>
+        <v>120302902</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>732829</v>
+        <v>733046</v>
       </c>
       <c r="R43" t="n">
-        <v>7457380</v>
+        <v>7457090</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302878</v>
+        <v>120302895</v>
       </c>
       <c r="B44" t="n">
         <v>57336</v>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733152</v>
+        <v>733086</v>
       </c>
       <c r="R44" t="n">
-        <v>7457234</v>
+        <v>7457578</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5303,10 +5303,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120302901</v>
+        <v>120302900</v>
       </c>
       <c r="B45" t="n">
-        <v>57748</v>
+        <v>57431</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5315,25 +5315,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103001</v>
+        <v>103031</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733049</v>
+        <v>733011</v>
       </c>
       <c r="R45" t="n">
-        <v>7457132</v>
+        <v>7457133</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5379,6 +5379,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5405,10 +5410,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302902</v>
+        <v>120302903</v>
       </c>
       <c r="B46" t="n">
-        <v>79131</v>
+        <v>57748</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5421,21 +5426,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5445,10 +5450,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733046</v>
+        <v>732779</v>
       </c>
       <c r="R46" t="n">
-        <v>7457090</v>
+        <v>7457059</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5475,12 +5480,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5507,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120302903</v>
+        <v>120302897</v>
       </c>
       <c r="B47" t="n">
-        <v>57748</v>
+        <v>57336</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5523,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5547,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732779</v>
+        <v>732853</v>
       </c>
       <c r="R47" t="n">
-        <v>7457059</v>
+        <v>7457442</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5577,17 +5587,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5614,10 +5624,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302882</v>
+        <v>120302898</v>
       </c>
       <c r="B48" t="n">
-        <v>5169</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5626,25 +5636,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5654,10 +5664,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733156</v>
+        <v>732795</v>
       </c>
       <c r="R48" t="n">
-        <v>7457547</v>
+        <v>7457432</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5690,6 +5700,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5716,10 +5731,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302898</v>
+        <v>120302901</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>57748</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5732,21 +5747,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5756,10 +5771,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>732795</v>
+        <v>733049</v>
       </c>
       <c r="R49" t="n">
-        <v>7457432</v>
+        <v>7457132</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5792,11 +5807,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5823,10 +5833,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302896</v>
+        <v>120302879</v>
       </c>
       <c r="B50" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5839,21 +5849,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5863,10 +5873,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733023</v>
+        <v>733150</v>
       </c>
       <c r="R50" t="n">
-        <v>7457503</v>
+        <v>7457273</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5925,10 +5935,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302879</v>
+        <v>120302877</v>
       </c>
       <c r="B51" t="n">
-        <v>78278</v>
+        <v>57431</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5937,25 +5947,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5965,10 +5975,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733150</v>
+        <v>733127</v>
       </c>
       <c r="R51" t="n">
-        <v>7457273</v>
+        <v>7457136</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6001,6 +6011,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6027,10 +6042,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302877</v>
+        <v>120302882</v>
       </c>
       <c r="B52" t="n">
-        <v>57431</v>
+        <v>5169</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6043,21 +6058,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6067,10 +6082,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733127</v>
+        <v>733156</v>
       </c>
       <c r="R52" t="n">
-        <v>7457136</v>
+        <v>7457547</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6103,11 +6118,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6134,7 +6144,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302895</v>
+        <v>120302878</v>
       </c>
       <c r="B53" t="n">
         <v>57336</v>
@@ -6174,10 +6184,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733086</v>
+        <v>733152</v>
       </c>
       <c r="R53" t="n">
-        <v>7457578</v>
+        <v>7457234</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6214,7 +6224,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6241,10 +6251,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302897</v>
+        <v>120302896</v>
       </c>
       <c r="B54" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6257,21 +6267,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6281,10 +6291,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>732853</v>
+        <v>733023</v>
       </c>
       <c r="R54" t="n">
-        <v>7457442</v>
+        <v>7457503</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6317,11 +6327,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6348,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302900</v>
+        <v>120302899</v>
       </c>
       <c r="B55" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6360,20 +6365,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6388,10 +6393,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733011</v>
+        <v>732829</v>
       </c>
       <c r="R55" t="n">
-        <v>7457133</v>
+        <v>7457380</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6424,11 +6429,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120302933</v>
+        <v>120302936</v>
       </c>
       <c r="B10" t="n">
-        <v>56535</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,20 +1640,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735031</v>
+        <v>735289</v>
       </c>
       <c r="R10" t="n">
-        <v>7459592</v>
+        <v>7459144</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,11 +1704,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302940</v>
+        <v>120302934</v>
       </c>
       <c r="B11" t="n">
-        <v>96891</v>
+        <v>57748</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,25 +1742,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735608</v>
+        <v>734919</v>
       </c>
       <c r="R11" t="n">
-        <v>7459127</v>
+        <v>7459493</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,6 +1806,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302937</v>
+        <v>120302939</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735316</v>
+        <v>735534</v>
       </c>
       <c r="R12" t="n">
-        <v>7459160</v>
+        <v>7459189</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302934</v>
+        <v>120302933</v>
       </c>
       <c r="B14" t="n">
-        <v>57748</v>
+        <v>56535</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>102613</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>734919</v>
+        <v>735031</v>
       </c>
       <c r="R14" t="n">
-        <v>7459493</v>
+        <v>7459592</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302930</v>
+        <v>120302935</v>
       </c>
       <c r="B15" t="n">
-        <v>56532</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,25 +2165,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734730</v>
+        <v>734905</v>
       </c>
       <c r="R15" t="n">
-        <v>7459077</v>
+        <v>7459394</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302936</v>
+        <v>120302940</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,25 +2272,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735289</v>
+        <v>735608</v>
       </c>
       <c r="R16" t="n">
-        <v>7459144</v>
+        <v>7459127</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302929</v>
+        <v>120302927</v>
       </c>
       <c r="B17" t="n">
-        <v>96891</v>
+        <v>79131</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2374,25 +2374,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734710</v>
+        <v>735126</v>
       </c>
       <c r="R17" t="n">
-        <v>7459012</v>
+        <v>7459188</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302935</v>
+        <v>120302937</v>
       </c>
       <c r="B18" t="n">
         <v>57473</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734905</v>
+        <v>735316</v>
       </c>
       <c r="R18" t="n">
-        <v>7459394</v>
+        <v>7459160</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fem födosökande individer</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302927</v>
+        <v>120302929</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>96891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735126</v>
+        <v>734710</v>
       </c>
       <c r="R19" t="n">
-        <v>7459188</v>
+        <v>7459012</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302939</v>
+        <v>120302930</v>
       </c>
       <c r="B20" t="n">
-        <v>91881</v>
+        <v>56532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735534</v>
+        <v>734730</v>
       </c>
       <c r="R20" t="n">
-        <v>7459189</v>
+        <v>7459077</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302920</v>
+        <v>120302923</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731622</v>
+        <v>731716</v>
       </c>
       <c r="R26" t="n">
-        <v>7457276</v>
+        <v>7457137</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3376,6 +3376,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3402,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302911</v>
+        <v>120302908</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3414,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731347</v>
+        <v>731245</v>
       </c>
       <c r="R27" t="n">
-        <v>7457280</v>
+        <v>7457418</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3482,7 +3487,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302910</v>
+        <v>120302914</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>90742</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3525,21 +3530,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731293</v>
+        <v>731763</v>
       </c>
       <c r="R28" t="n">
-        <v>7457377</v>
+        <v>7457160</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3585,11 +3590,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302922</v>
+        <v>120302910</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731611</v>
+        <v>731293</v>
       </c>
       <c r="R29" t="n">
-        <v>7457228</v>
+        <v>7457377</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302912</v>
+        <v>120302911</v>
       </c>
       <c r="B30" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3735,25 +3735,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731416</v>
+        <v>731347</v>
       </c>
       <c r="R30" t="n">
-        <v>7457247</v>
+        <v>7457280</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,10 +3830,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302916</v>
+        <v>120302918</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3846,21 +3846,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731728</v>
+        <v>731673</v>
       </c>
       <c r="R31" t="n">
-        <v>7457308</v>
+        <v>7457289</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3906,6 +3906,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,10 +3937,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302918</v>
+        <v>120302912</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3944,25 +3949,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3972,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731673</v>
+        <v>731416</v>
       </c>
       <c r="R32" t="n">
-        <v>7457289</v>
+        <v>7457247</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4012,7 +4017,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4039,10 +4044,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302917</v>
+        <v>120302915</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4051,20 +4056,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4079,10 +4084,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731714</v>
+        <v>731716</v>
       </c>
       <c r="R33" t="n">
-        <v>7457298</v>
+        <v>7457334</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4115,11 +4120,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,10 +4146,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120302923</v>
+        <v>120302919</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4162,16 +4162,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4186,10 +4186,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731716</v>
+        <v>731642</v>
       </c>
       <c r="R34" t="n">
-        <v>7457137</v>
+        <v>7457290</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4253,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302914</v>
+        <v>120302917</v>
       </c>
       <c r="B35" t="n">
-        <v>90742</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731763</v>
+        <v>731714</v>
       </c>
       <c r="R35" t="n">
-        <v>7457160</v>
+        <v>7457298</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4329,6 +4329,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,10 +4360,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302908</v>
+        <v>120302916</v>
       </c>
       <c r="B36" t="n">
-        <v>56532</v>
+        <v>79131</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4367,25 +4372,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4395,10 +4400,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731245</v>
+        <v>731728</v>
       </c>
       <c r="R36" t="n">
-        <v>7457418</v>
+        <v>7457308</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4431,11 +4436,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hane</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4462,10 +4462,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120302919</v>
+        <v>120302906</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731642</v>
+        <v>731352</v>
       </c>
       <c r="R37" t="n">
-        <v>7457290</v>
+        <v>7457246</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4538,11 +4538,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,7 +4564,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302906</v>
+        <v>120302920</v>
       </c>
       <c r="B38" t="n">
         <v>90598</v>
@@ -4609,10 +4604,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731352</v>
+        <v>731622</v>
       </c>
       <c r="R38" t="n">
-        <v>7457246</v>
+        <v>7457276</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4778,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302913</v>
+        <v>120302921</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4790,25 +4785,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731549</v>
+        <v>731604</v>
       </c>
       <c r="R40" t="n">
-        <v>7457309</v>
+        <v>7457238</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4858,7 +4853,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4885,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302915</v>
+        <v>120302922</v>
       </c>
       <c r="B41" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,20 +4892,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4925,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731716</v>
+        <v>731611</v>
       </c>
       <c r="R41" t="n">
-        <v>7457334</v>
+        <v>7457228</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4961,6 +4956,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302921</v>
+        <v>120302913</v>
       </c>
       <c r="B42" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4999,25 +4999,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731604</v>
+        <v>731549</v>
       </c>
       <c r="R42" t="n">
-        <v>7457238</v>
+        <v>7457309</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>En individ</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120302902</v>
+        <v>120302901</v>
       </c>
       <c r="B43" t="n">
-        <v>79131</v>
+        <v>57748</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733046</v>
+        <v>733049</v>
       </c>
       <c r="R43" t="n">
-        <v>7457090</v>
+        <v>7457132</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5196,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302895</v>
+        <v>120302899</v>
       </c>
       <c r="B44" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,16 +5212,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733086</v>
+        <v>732829</v>
       </c>
       <c r="R44" t="n">
-        <v>7457578</v>
+        <v>7457380</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5272,11 +5272,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5410,10 +5405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302903</v>
+        <v>120302902</v>
       </c>
       <c r="B46" t="n">
-        <v>57748</v>
+        <v>79131</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5426,21 +5421,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5450,10 +5445,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732779</v>
+        <v>733046</v>
       </c>
       <c r="R46" t="n">
-        <v>7457059</v>
+        <v>7457090</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5480,17 +5475,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,10 +5614,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302898</v>
+        <v>120302896</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5640,21 +5630,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5664,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>732795</v>
+        <v>733023</v>
       </c>
       <c r="R48" t="n">
-        <v>7457432</v>
+        <v>7457503</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5700,11 +5690,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5731,10 +5716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302901</v>
+        <v>120302878</v>
       </c>
       <c r="B49" t="n">
-        <v>57748</v>
+        <v>57336</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5747,21 +5732,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5771,10 +5756,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733049</v>
+        <v>733152</v>
       </c>
       <c r="R49" t="n">
-        <v>7457132</v>
+        <v>7457234</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5807,6 +5792,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,10 +5823,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302879</v>
+        <v>120302903</v>
       </c>
       <c r="B50" t="n">
-        <v>78278</v>
+        <v>57748</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5849,21 +5839,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5873,10 +5863,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733150</v>
+        <v>732779</v>
       </c>
       <c r="R50" t="n">
-        <v>7457273</v>
+        <v>7457059</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5903,12 +5893,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6042,10 +6037,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302882</v>
+        <v>120302895</v>
       </c>
       <c r="B52" t="n">
-        <v>5169</v>
+        <v>57336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6054,25 +6049,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6082,10 +6077,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733156</v>
+        <v>733086</v>
       </c>
       <c r="R52" t="n">
-        <v>7457547</v>
+        <v>7457578</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6118,6 +6113,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6144,10 +6144,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302878</v>
+        <v>120302879</v>
       </c>
       <c r="B53" t="n">
-        <v>57336</v>
+        <v>78278</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733152</v>
+        <v>733150</v>
       </c>
       <c r="R53" t="n">
-        <v>7457234</v>
+        <v>7457273</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6220,11 +6220,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6251,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302896</v>
+        <v>120302898</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6267,21 +6262,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6291,10 +6286,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733023</v>
+        <v>732795</v>
       </c>
       <c r="R54" t="n">
-        <v>7457503</v>
+        <v>7457432</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6327,6 +6322,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302899</v>
+        <v>120302882</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>5169</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6365,25 +6365,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6393,10 +6393,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>732829</v>
+        <v>733156</v>
       </c>
       <c r="R55" t="n">
-        <v>7457380</v>
+        <v>7457547</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120302936</v>
+        <v>120302929</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>96891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,25 +1640,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>735289</v>
+        <v>734710</v>
       </c>
       <c r="R10" t="n">
-        <v>7459144</v>
+        <v>7459012</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302934</v>
+        <v>120302939</v>
       </c>
       <c r="B11" t="n">
-        <v>57748</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>734919</v>
+        <v>735534</v>
       </c>
       <c r="R11" t="n">
-        <v>7459493</v>
+        <v>7459189</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302939</v>
+        <v>120302930</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>56532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1849,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735534</v>
+        <v>734730</v>
       </c>
       <c r="R12" t="n">
-        <v>7459189</v>
+        <v>7459077</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>9 fruktkroppar</t>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302933</v>
+        <v>120302927</v>
       </c>
       <c r="B14" t="n">
-        <v>56535</v>
+        <v>79131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735031</v>
+        <v>735126</v>
       </c>
       <c r="R14" t="n">
-        <v>7459592</v>
+        <v>7459188</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,17 +2116,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302935</v>
+        <v>120302933</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>56535</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,25 +2160,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734905</v>
+        <v>735031</v>
       </c>
       <c r="R15" t="n">
-        <v>7459394</v>
+        <v>7459592</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fem födosökande individer</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,10 +2357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302927</v>
+        <v>120302937</v>
       </c>
       <c r="B17" t="n">
-        <v>79131</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,21 +2373,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735126</v>
+        <v>735316</v>
       </c>
       <c r="R17" t="n">
-        <v>7459188</v>
+        <v>7459160</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2432,12 +2427,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302937</v>
+        <v>120302934</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>57748</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,21 +2480,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735316</v>
+        <v>734919</v>
       </c>
       <c r="R18" t="n">
-        <v>7459160</v>
+        <v>7459493</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302929</v>
+        <v>120302936</v>
       </c>
       <c r="B19" t="n">
-        <v>96891</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734710</v>
+        <v>735289</v>
       </c>
       <c r="R19" t="n">
-        <v>7459012</v>
+        <v>7459144</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302930</v>
+        <v>120302935</v>
       </c>
       <c r="B20" t="n">
-        <v>56532</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734730</v>
+        <v>734905</v>
       </c>
       <c r="R20" t="n">
-        <v>7459077</v>
+        <v>7459394</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120302892</v>
+        <v>120302893</v>
       </c>
       <c r="B22" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>732912</v>
+        <v>732993</v>
       </c>
       <c r="R22" t="n">
-        <v>7457768</v>
+        <v>7457764</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120302894</v>
+        <v>120302886</v>
       </c>
       <c r="B23" t="n">
-        <v>79131</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,25 +3001,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3029,10 +3029,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733092</v>
+        <v>733007</v>
       </c>
       <c r="R23" t="n">
-        <v>7457724</v>
+        <v>7457822</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120302886</v>
+        <v>120302892</v>
       </c>
       <c r="B24" t="n">
-        <v>96885</v>
+        <v>56524</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3103,25 +3103,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733007</v>
+        <v>732912</v>
       </c>
       <c r="R24" t="n">
-        <v>7457822</v>
+        <v>7457768</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3167,6 +3167,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,10 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120302893</v>
+        <v>120302894</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3209,21 +3214,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3233,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>732993</v>
+        <v>733092</v>
       </c>
       <c r="R25" t="n">
-        <v>7457764</v>
+        <v>7457724</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3269,11 +3274,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302923</v>
+        <v>120302924</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731716</v>
+        <v>731752</v>
       </c>
       <c r="R26" t="n">
-        <v>7457137</v>
+        <v>7457204</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302908</v>
+        <v>120302919</v>
       </c>
       <c r="B27" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731245</v>
+        <v>731642</v>
       </c>
       <c r="R27" t="n">
-        <v>7457418</v>
+        <v>7457290</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302914</v>
+        <v>120302917</v>
       </c>
       <c r="B28" t="n">
-        <v>90742</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731763</v>
+        <v>731714</v>
       </c>
       <c r="R28" t="n">
-        <v>7457160</v>
+        <v>7457298</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3590,6 +3590,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3616,10 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302910</v>
+        <v>120302918</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3632,21 +3637,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731293</v>
+        <v>731673</v>
       </c>
       <c r="R29" t="n">
-        <v>7457377</v>
+        <v>7457289</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3696,7 +3701,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302911</v>
+        <v>120302906</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,21 +3744,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731347</v>
+        <v>731352</v>
       </c>
       <c r="R30" t="n">
-        <v>7457280</v>
+        <v>7457246</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3799,11 +3804,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,10 +3830,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302918</v>
+        <v>120302921</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3842,25 +3842,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731673</v>
+        <v>731604</v>
       </c>
       <c r="R31" t="n">
-        <v>7457289</v>
+        <v>7457238</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3937,10 +3937,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302912</v>
+        <v>120302911</v>
       </c>
       <c r="B32" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3949,25 +3949,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3977,10 +3977,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731416</v>
+        <v>731347</v>
       </c>
       <c r="R32" t="n">
-        <v>7457247</v>
+        <v>7457280</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,10 +4044,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302915</v>
+        <v>120302923</v>
       </c>
       <c r="B33" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4056,20 +4056,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4087,7 +4087,7 @@
         <v>731716</v>
       </c>
       <c r="R33" t="n">
-        <v>7457334</v>
+        <v>7457137</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4120,6 +4120,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4146,10 +4151,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120302919</v>
+        <v>120302920</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4162,21 +4167,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4186,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731642</v>
+        <v>731622</v>
       </c>
       <c r="R34" t="n">
-        <v>7457290</v>
+        <v>7457276</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4222,11 +4227,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302917</v>
+        <v>120302915</v>
       </c>
       <c r="B35" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4265,20 +4265,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731714</v>
+        <v>731716</v>
       </c>
       <c r="R35" t="n">
-        <v>7457298</v>
+        <v>7457334</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4329,11 +4329,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4360,10 +4355,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302916</v>
+        <v>120302922</v>
       </c>
       <c r="B36" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4376,21 +4371,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4400,10 +4395,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731728</v>
+        <v>731611</v>
       </c>
       <c r="R36" t="n">
-        <v>7457308</v>
+        <v>7457228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4436,6 +4431,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4462,10 +4462,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120302906</v>
+        <v>120302912</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731352</v>
+        <v>731416</v>
       </c>
       <c r="R37" t="n">
-        <v>7457246</v>
+        <v>7457247</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4538,6 +4538,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302920</v>
+        <v>120302908</v>
       </c>
       <c r="B38" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4576,25 +4581,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4604,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731622</v>
+        <v>731245</v>
       </c>
       <c r="R38" t="n">
-        <v>7457276</v>
+        <v>7457418</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,6 +4645,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4666,10 +4676,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302924</v>
+        <v>120302916</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4682,21 +4692,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4706,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731752</v>
+        <v>731728</v>
       </c>
       <c r="R39" t="n">
-        <v>7457204</v>
+        <v>7457308</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4742,11 +4752,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4773,10 +4778,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302921</v>
+        <v>120302913</v>
       </c>
       <c r="B40" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4785,25 +4790,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731604</v>
+        <v>731549</v>
       </c>
       <c r="R40" t="n">
-        <v>7457238</v>
+        <v>7457309</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4853,7 +4858,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>En individ</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4880,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302922</v>
+        <v>120302910</v>
       </c>
       <c r="B41" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4896,21 +4901,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4920,10 +4925,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731611</v>
+        <v>731293</v>
       </c>
       <c r="R41" t="n">
-        <v>7457228</v>
+        <v>7457377</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4960,7 +4965,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,10 +4992,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302913</v>
+        <v>120302914</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,21 +5008,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5027,10 +5032,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731549</v>
+        <v>731763</v>
       </c>
       <c r="R42" t="n">
-        <v>7457309</v>
+        <v>7457160</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5063,11 +5068,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120302901</v>
+        <v>120302879</v>
       </c>
       <c r="B43" t="n">
-        <v>57748</v>
+        <v>78278</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103001</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733049</v>
+        <v>733150</v>
       </c>
       <c r="R43" t="n">
-        <v>7457132</v>
+        <v>7457273</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5196,10 +5196,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302899</v>
+        <v>120302903</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>57748</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,21 +5212,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>732829</v>
+        <v>732779</v>
       </c>
       <c r="R44" t="n">
-        <v>7457380</v>
+        <v>7457059</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5266,12 +5266,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5298,7 +5303,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120302900</v>
+        <v>120302877</v>
       </c>
       <c r="B45" t="n">
         <v>57431</v>
@@ -5338,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733011</v>
+        <v>733127</v>
       </c>
       <c r="R45" t="n">
-        <v>7457133</v>
+        <v>7457136</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5378,7 +5383,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tre individer</t>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5405,10 +5410,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302902</v>
+        <v>120302882</v>
       </c>
       <c r="B46" t="n">
-        <v>79131</v>
+        <v>5169</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5417,25 +5422,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5445,10 +5450,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733046</v>
+        <v>733156</v>
       </c>
       <c r="R46" t="n">
-        <v>7457090</v>
+        <v>7457547</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5507,10 +5512,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120302897</v>
+        <v>120302902</v>
       </c>
       <c r="B47" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5523,21 +5528,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5547,10 +5552,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732853</v>
+        <v>733046</v>
       </c>
       <c r="R47" t="n">
-        <v>7457442</v>
+        <v>7457090</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5583,11 +5588,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5614,10 +5614,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302896</v>
+        <v>120302895</v>
       </c>
       <c r="B48" t="n">
-        <v>79131</v>
+        <v>57336</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5630,21 +5630,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733023</v>
+        <v>733086</v>
       </c>
       <c r="R48" t="n">
-        <v>7457503</v>
+        <v>7457578</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5690,6 +5690,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5716,7 +5721,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302878</v>
+        <v>120302897</v>
       </c>
       <c r="B49" t="n">
         <v>57336</v>
@@ -5756,10 +5761,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733152</v>
+        <v>732853</v>
       </c>
       <c r="R49" t="n">
-        <v>7457234</v>
+        <v>7457442</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5796,7 +5801,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5823,10 +5828,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302903</v>
+        <v>120302898</v>
       </c>
       <c r="B50" t="n">
-        <v>57748</v>
+        <v>57320</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5839,21 +5844,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5863,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>732779</v>
+        <v>732795</v>
       </c>
       <c r="R50" t="n">
-        <v>7457059</v>
+        <v>7457432</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5893,17 +5898,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5930,10 +5935,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302877</v>
+        <v>120302878</v>
       </c>
       <c r="B51" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5942,20 +5947,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5970,10 +5975,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733127</v>
+        <v>733152</v>
       </c>
       <c r="R51" t="n">
-        <v>7457136</v>
+        <v>7457234</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6010,7 +6015,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Fyra individer</t>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,10 +6042,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302895</v>
+        <v>120302899</v>
       </c>
       <c r="B52" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6053,16 +6058,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6077,10 +6082,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733086</v>
+        <v>732829</v>
       </c>
       <c r="R52" t="n">
-        <v>7457578</v>
+        <v>7457380</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6113,11 +6118,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6144,10 +6144,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302879</v>
+        <v>120302901</v>
       </c>
       <c r="B53" t="n">
-        <v>78278</v>
+        <v>57748</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733150</v>
+        <v>733049</v>
       </c>
       <c r="R53" t="n">
-        <v>7457273</v>
+        <v>7457132</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302898</v>
+        <v>120302896</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6262,21 +6262,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>732795</v>
+        <v>733023</v>
       </c>
       <c r="R54" t="n">
-        <v>7457432</v>
+        <v>7457503</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6322,11 +6322,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6348,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302882</v>
+        <v>120302900</v>
       </c>
       <c r="B55" t="n">
-        <v>5169</v>
+        <v>57431</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6369,21 +6364,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6393,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733156</v>
+        <v>733011</v>
       </c>
       <c r="R55" t="n">
-        <v>7457547</v>
+        <v>7457133</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6429,6 +6424,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -3728,10 +3728,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302906</v>
+        <v>120302921</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3740,25 +3740,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731352</v>
+        <v>731604</v>
       </c>
       <c r="R30" t="n">
-        <v>7457246</v>
+        <v>7457238</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3804,6 +3804,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3830,10 +3835,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302921</v>
+        <v>120302906</v>
       </c>
       <c r="B31" t="n">
-        <v>56532</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3842,25 +3847,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3870,10 +3875,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731604</v>
+        <v>731352</v>
       </c>
       <c r="R31" t="n">
-        <v>7457238</v>
+        <v>7457246</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3906,11 +3911,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En individ</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120302929</v>
+        <v>120302934</v>
       </c>
       <c r="B10" t="n">
-        <v>96891</v>
+        <v>57748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,25 +1640,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>734710</v>
+        <v>734919</v>
       </c>
       <c r="R10" t="n">
-        <v>7459012</v>
+        <v>7459493</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,6 +1704,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302939</v>
+        <v>120302936</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735534</v>
+        <v>735289</v>
       </c>
       <c r="R11" t="n">
-        <v>7459189</v>
+        <v>7459144</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1806,11 +1811,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302930</v>
+        <v>120302939</v>
       </c>
       <c r="B12" t="n">
-        <v>56532</v>
+        <v>91881</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1849,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>734730</v>
+        <v>735534</v>
       </c>
       <c r="R12" t="n">
-        <v>7459077</v>
+        <v>7459189</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,10 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302927</v>
+        <v>120302933</v>
       </c>
       <c r="B14" t="n">
-        <v>79131</v>
+        <v>56535</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2058,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735126</v>
+        <v>735031</v>
       </c>
       <c r="R14" t="n">
-        <v>7459188</v>
+        <v>7459592</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,12 +2116,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302933</v>
+        <v>120302929</v>
       </c>
       <c r="B15" t="n">
-        <v>56535</v>
+        <v>96891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,21 +2169,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2188,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>735031</v>
+        <v>734710</v>
       </c>
       <c r="R15" t="n">
-        <v>7459592</v>
+        <v>7459012</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2224,11 +2229,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302940</v>
+        <v>120302937</v>
       </c>
       <c r="B16" t="n">
-        <v>96891</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735608</v>
+        <v>735316</v>
       </c>
       <c r="R16" t="n">
-        <v>7459127</v>
+        <v>7459160</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2331,6 +2331,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,7 +2362,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302937</v>
+        <v>120302935</v>
       </c>
       <c r="B17" t="n">
         <v>57473</v>
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735316</v>
+        <v>734905</v>
       </c>
       <c r="R17" t="n">
-        <v>7459160</v>
+        <v>7459394</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2437,7 +2442,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302934</v>
+        <v>120302940</v>
       </c>
       <c r="B18" t="n">
-        <v>57748</v>
+        <v>96891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2476,25 +2481,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103001</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2504,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734919</v>
+        <v>735608</v>
       </c>
       <c r="R18" t="n">
-        <v>7459493</v>
+        <v>7459127</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2540,11 +2545,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302936</v>
+        <v>120302927</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735289</v>
+        <v>735126</v>
       </c>
       <c r="R19" t="n">
-        <v>7459144</v>
+        <v>7459188</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302935</v>
+        <v>120302930</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>56532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734905</v>
+        <v>734730</v>
       </c>
       <c r="R20" t="n">
-        <v>7459394</v>
+        <v>7459077</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Fem födosökande individer</t>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120302893</v>
+        <v>120302886</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>96885</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>732993</v>
+        <v>733007</v>
       </c>
       <c r="R22" t="n">
-        <v>7457764</v>
+        <v>7457822</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2958,11 +2958,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120302886</v>
+        <v>120302892</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
+        <v>56524</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3001,25 +2996,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3029,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733007</v>
+        <v>732912</v>
       </c>
       <c r="R23" t="n">
-        <v>7457822</v>
+        <v>7457768</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3065,6 +3060,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,10 +3091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120302892</v>
+        <v>120302894</v>
       </c>
       <c r="B24" t="n">
-        <v>56524</v>
+        <v>79131</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>732912</v>
+        <v>733092</v>
       </c>
       <c r="R24" t="n">
-        <v>7457768</v>
+        <v>7457724</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3167,11 +3167,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3198,10 +3193,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120302894</v>
+        <v>120302893</v>
       </c>
       <c r="B25" t="n">
-        <v>79131</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3214,21 +3209,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3238,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733092</v>
+        <v>732993</v>
       </c>
       <c r="R25" t="n">
-        <v>7457724</v>
+        <v>7457764</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3274,6 +3269,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302924</v>
+        <v>120302910</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3316,21 +3316,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731752</v>
+        <v>731293</v>
       </c>
       <c r="R26" t="n">
-        <v>7457204</v>
+        <v>7457377</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Hackspår på högstubbe</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302919</v>
+        <v>120302908</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731642</v>
+        <v>731245</v>
       </c>
       <c r="R27" t="n">
-        <v>7457290</v>
+        <v>7457418</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302917</v>
+        <v>120302906</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731714</v>
+        <v>731352</v>
       </c>
       <c r="R28" t="n">
-        <v>7457298</v>
+        <v>7457246</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3590,11 +3590,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,7 +3616,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302918</v>
+        <v>120302922</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3661,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731673</v>
+        <v>731611</v>
       </c>
       <c r="R29" t="n">
-        <v>7457289</v>
+        <v>7457228</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3728,10 +3723,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302921</v>
+        <v>120302916</v>
       </c>
       <c r="B30" t="n">
-        <v>56532</v>
+        <v>79131</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3740,25 +3735,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731604</v>
+        <v>731728</v>
       </c>
       <c r="R30" t="n">
-        <v>7457238</v>
+        <v>7457308</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3804,11 +3799,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En individ</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302906</v>
+        <v>120302923</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3851,21 +3841,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3875,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731352</v>
+        <v>731716</v>
       </c>
       <c r="R31" t="n">
-        <v>7457246</v>
+        <v>7457137</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3911,6 +3901,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3937,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302911</v>
+        <v>120302914</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>90742</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3953,21 +3948,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3977,10 +3972,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731347</v>
+        <v>731763</v>
       </c>
       <c r="R32" t="n">
-        <v>7457280</v>
+        <v>7457160</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4013,11 +4008,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,10 +4034,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302923</v>
+        <v>120302921</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4056,25 +4046,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4084,10 +4074,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731716</v>
+        <v>731604</v>
       </c>
       <c r="R33" t="n">
-        <v>7457137</v>
+        <v>7457238</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4124,7 +4114,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4151,10 +4141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120302920</v>
+        <v>120302918</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4167,21 +4157,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4191,10 +4181,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731622</v>
+        <v>731673</v>
       </c>
       <c r="R34" t="n">
-        <v>7457276</v>
+        <v>7457289</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4227,6 +4217,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,10 +4248,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302915</v>
+        <v>120302920</v>
       </c>
       <c r="B35" t="n">
-        <v>57431</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4265,25 +4260,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4293,10 +4288,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731716</v>
+        <v>731622</v>
       </c>
       <c r="R35" t="n">
-        <v>7457334</v>
+        <v>7457276</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4355,10 +4350,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302922</v>
+        <v>120302924</v>
       </c>
       <c r="B36" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4371,16 +4366,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4395,10 +4390,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731611</v>
+        <v>731752</v>
       </c>
       <c r="R36" t="n">
-        <v>7457228</v>
+        <v>7457204</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4435,7 +4430,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4462,10 +4457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120302912</v>
+        <v>120302911</v>
       </c>
       <c r="B37" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4474,25 +4469,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4502,10 +4497,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731416</v>
+        <v>731347</v>
       </c>
       <c r="R37" t="n">
-        <v>7457247</v>
+        <v>7457280</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4542,7 +4537,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,7 +4564,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302908</v>
+        <v>120302912</v>
       </c>
       <c r="B38" t="n">
         <v>56532</v>
@@ -4609,10 +4604,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731245</v>
+        <v>731416</v>
       </c>
       <c r="R38" t="n">
-        <v>7457418</v>
+        <v>7457247</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4676,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302916</v>
+        <v>120302915</v>
       </c>
       <c r="B39" t="n">
-        <v>79131</v>
+        <v>57431</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4688,25 +4683,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4716,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731728</v>
+        <v>731716</v>
       </c>
       <c r="R39" t="n">
-        <v>7457308</v>
+        <v>7457334</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4778,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302913</v>
+        <v>120302917</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4794,16 +4789,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731549</v>
+        <v>731714</v>
       </c>
       <c r="R40" t="n">
-        <v>7457309</v>
+        <v>7457298</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4885,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302910</v>
+        <v>120302919</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,21 +4896,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4925,10 +4920,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731293</v>
+        <v>731642</v>
       </c>
       <c r="R41" t="n">
-        <v>7457377</v>
+        <v>7457290</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4965,7 +4960,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4992,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302914</v>
+        <v>120302913</v>
       </c>
       <c r="B42" t="n">
-        <v>90742</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5008,21 +5003,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5032,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731763</v>
+        <v>731549</v>
       </c>
       <c r="R42" t="n">
-        <v>7457160</v>
+        <v>7457309</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5068,6 +5063,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5094,10 +5094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120302879</v>
+        <v>120302898</v>
       </c>
       <c r="B43" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5110,21 +5110,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733150</v>
+        <v>732795</v>
       </c>
       <c r="R43" t="n">
-        <v>7457273</v>
+        <v>7457432</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5170,6 +5170,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5196,10 +5201,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302903</v>
+        <v>120302896</v>
       </c>
       <c r="B44" t="n">
-        <v>57748</v>
+        <v>79131</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5212,21 +5217,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5236,10 +5241,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>732779</v>
+        <v>733023</v>
       </c>
       <c r="R44" t="n">
-        <v>7457059</v>
+        <v>7457503</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5266,17 +5271,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5303,10 +5303,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120302877</v>
+        <v>120302895</v>
       </c>
       <c r="B45" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5315,20 +5315,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733127</v>
+        <v>733086</v>
       </c>
       <c r="R45" t="n">
-        <v>7457136</v>
+        <v>7457578</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Fyra individer</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5410,10 +5410,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302882</v>
+        <v>120302900</v>
       </c>
       <c r="B46" t="n">
-        <v>5169</v>
+        <v>57431</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733156</v>
+        <v>733011</v>
       </c>
       <c r="R46" t="n">
-        <v>7457547</v>
+        <v>7457133</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5486,6 +5486,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5512,10 +5517,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120302902</v>
+        <v>120302901</v>
       </c>
       <c r="B47" t="n">
-        <v>79131</v>
+        <v>57748</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5528,21 +5533,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5552,10 +5557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733046</v>
+        <v>733049</v>
       </c>
       <c r="R47" t="n">
-        <v>7457090</v>
+        <v>7457132</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5614,10 +5619,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302895</v>
+        <v>120302877</v>
       </c>
       <c r="B48" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5626,20 +5631,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5654,10 +5659,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733086</v>
+        <v>733127</v>
       </c>
       <c r="R48" t="n">
-        <v>7457578</v>
+        <v>7457136</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5694,7 +5699,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5721,10 +5726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302897</v>
+        <v>120302882</v>
       </c>
       <c r="B49" t="n">
-        <v>57336</v>
+        <v>5169</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5733,25 +5738,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5761,10 +5766,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>732853</v>
+        <v>733156</v>
       </c>
       <c r="R49" t="n">
-        <v>7457442</v>
+        <v>7457547</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5797,11 +5802,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5828,7 +5828,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302898</v>
+        <v>120302899</v>
       </c>
       <c r="B50" t="n">
         <v>57320</v>
@@ -5868,10 +5868,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>732795</v>
+        <v>732829</v>
       </c>
       <c r="R50" t="n">
-        <v>7457432</v>
+        <v>7457380</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5904,11 +5904,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6042,10 +6037,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302899</v>
+        <v>120302897</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6058,16 +6053,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6082,10 +6077,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>732829</v>
+        <v>732853</v>
       </c>
       <c r="R52" t="n">
-        <v>7457380</v>
+        <v>7457442</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6118,6 +6113,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6144,10 +6144,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302901</v>
+        <v>120302902</v>
       </c>
       <c r="B53" t="n">
-        <v>57748</v>
+        <v>79131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733049</v>
+        <v>733046</v>
       </c>
       <c r="R53" t="n">
-        <v>7457132</v>
+        <v>7457090</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302896</v>
+        <v>120302903</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>57748</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6262,21 +6262,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>103001</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733023</v>
+        <v>732779</v>
       </c>
       <c r="R54" t="n">
-        <v>7457503</v>
+        <v>7457059</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6316,12 +6316,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6348,10 +6353,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302900</v>
+        <v>120302879</v>
       </c>
       <c r="B55" t="n">
-        <v>57431</v>
+        <v>78278</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6360,25 +6365,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6388,10 +6393,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733011</v>
+        <v>733150</v>
       </c>
       <c r="R55" t="n">
-        <v>7457133</v>
+        <v>7457273</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6424,11 +6429,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120302934</v>
+        <v>120302937</v>
       </c>
       <c r="B10" t="n">
-        <v>57748</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>734919</v>
+        <v>735316</v>
       </c>
       <c r="R10" t="n">
-        <v>7459493</v>
+        <v>7459160</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302936</v>
+        <v>120302934</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57748</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>735289</v>
+        <v>734919</v>
       </c>
       <c r="R11" t="n">
-        <v>7459144</v>
+        <v>7459493</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,6 +1811,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302939</v>
+        <v>120302929</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>96891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>735534</v>
+        <v>734710</v>
       </c>
       <c r="R12" t="n">
-        <v>7459189</v>
+        <v>7459012</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,11 +1918,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120302932</v>
+        <v>120302930</v>
       </c>
       <c r="B13" t="n">
-        <v>96891</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>734754</v>
+        <v>734730</v>
       </c>
       <c r="R13" t="n">
-        <v>7459460</v>
+        <v>7459077</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2020,6 +2020,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302933</v>
+        <v>120302927</v>
       </c>
       <c r="B14" t="n">
-        <v>56535</v>
+        <v>79131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2063,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735031</v>
+        <v>735126</v>
       </c>
       <c r="R14" t="n">
-        <v>7459592</v>
+        <v>7459188</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2116,17 +2121,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302929</v>
+        <v>120302932</v>
       </c>
       <c r="B15" t="n">
         <v>96891</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734710</v>
+        <v>734754</v>
       </c>
       <c r="R15" t="n">
-        <v>7459012</v>
+        <v>7459460</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302937</v>
+        <v>120302939</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>91881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735316</v>
+        <v>735534</v>
       </c>
       <c r="R16" t="n">
-        <v>7459160</v>
+        <v>7459189</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302935</v>
+        <v>120302936</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734905</v>
+        <v>735289</v>
       </c>
       <c r="R17" t="n">
-        <v>7459394</v>
+        <v>7459144</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2438,11 +2438,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,10 +2566,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302927</v>
+        <v>120302933</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>56535</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2583,25 +2578,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>102613</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2611,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>735126</v>
+        <v>735031</v>
       </c>
       <c r="R19" t="n">
-        <v>7459188</v>
+        <v>7459592</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,12 +2636,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120302930</v>
+        <v>120302935</v>
       </c>
       <c r="B20" t="n">
-        <v>56532</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>734730</v>
+        <v>734905</v>
       </c>
       <c r="R20" t="n">
-        <v>7459077</v>
+        <v>7459394</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120302892</v>
+        <v>120302893</v>
       </c>
       <c r="B23" t="n">
-        <v>56524</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,16 +3000,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>732912</v>
+        <v>732993</v>
       </c>
       <c r="R23" t="n">
-        <v>7457768</v>
+        <v>7457764</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3091,10 +3091,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120302894</v>
+        <v>120302892</v>
       </c>
       <c r="B24" t="n">
-        <v>79131</v>
+        <v>56524</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733092</v>
+        <v>732912</v>
       </c>
       <c r="R24" t="n">
-        <v>7457724</v>
+        <v>7457768</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3167,6 +3167,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3193,10 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120302893</v>
+        <v>120302894</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3209,21 +3214,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3233,10 +3238,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>732993</v>
+        <v>733092</v>
       </c>
       <c r="R25" t="n">
-        <v>7457764</v>
+        <v>7457724</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3269,11 +3274,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120302910</v>
+        <v>120302912</v>
       </c>
       <c r="B26" t="n">
-        <v>90598</v>
+        <v>56532</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3312,25 +3312,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731293</v>
+        <v>731416</v>
       </c>
       <c r="R26" t="n">
-        <v>7457377</v>
+        <v>7457247</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3407,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120302908</v>
+        <v>120302919</v>
       </c>
       <c r="B27" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3419,25 +3419,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731245</v>
+        <v>731642</v>
       </c>
       <c r="R27" t="n">
-        <v>7457418</v>
+        <v>7457290</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120302906</v>
+        <v>120302915</v>
       </c>
       <c r="B28" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3526,25 +3526,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731352</v>
+        <v>731716</v>
       </c>
       <c r="R28" t="n">
-        <v>7457246</v>
+        <v>7457334</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120302922</v>
+        <v>120302916</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731611</v>
+        <v>731728</v>
       </c>
       <c r="R29" t="n">
-        <v>7457228</v>
+        <v>7457308</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3692,11 +3692,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3723,10 +3718,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120302916</v>
+        <v>120302913</v>
       </c>
       <c r="B30" t="n">
-        <v>79131</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3739,21 +3734,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3758,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731728</v>
+        <v>731549</v>
       </c>
       <c r="R30" t="n">
-        <v>7457308</v>
+        <v>7457309</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3799,6 +3794,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3825,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120302923</v>
+        <v>120302921</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3837,25 +3837,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731716</v>
+        <v>731604</v>
       </c>
       <c r="R31" t="n">
-        <v>7457137</v>
+        <v>7457238</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120302914</v>
+        <v>120302908</v>
       </c>
       <c r="B32" t="n">
-        <v>90742</v>
+        <v>56532</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3944,25 +3944,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731763</v>
+        <v>731245</v>
       </c>
       <c r="R32" t="n">
-        <v>7457160</v>
+        <v>7457418</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4008,6 +4008,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4034,10 +4039,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302921</v>
+        <v>120302910</v>
       </c>
       <c r="B33" t="n">
-        <v>56532</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4046,25 +4051,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4074,10 +4079,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731604</v>
+        <v>731293</v>
       </c>
       <c r="R33" t="n">
-        <v>7457238</v>
+        <v>7457377</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4114,7 +4119,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>En individ</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4141,10 +4146,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120302918</v>
+        <v>120302917</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4157,16 +4162,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4181,10 +4186,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731673</v>
+        <v>731714</v>
       </c>
       <c r="R34" t="n">
-        <v>7457289</v>
+        <v>7457298</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4248,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120302920</v>
+        <v>120302918</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4264,21 +4269,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4288,10 +4293,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731622</v>
+        <v>731673</v>
       </c>
       <c r="R35" t="n">
-        <v>7457276</v>
+        <v>7457289</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4324,6 +4329,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4350,10 +4360,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120302924</v>
+        <v>120302922</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4366,16 +4376,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4390,10 +4400,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731752</v>
+        <v>731611</v>
       </c>
       <c r="R36" t="n">
-        <v>7457204</v>
+        <v>7457228</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4430,7 +4440,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackspår på högstubbe</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4457,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120302911</v>
+        <v>120302920</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4473,21 +4483,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4497,10 +4507,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731347</v>
+        <v>731622</v>
       </c>
       <c r="R37" t="n">
-        <v>7457280</v>
+        <v>7457276</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4533,11 +4543,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4564,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302912</v>
+        <v>120302911</v>
       </c>
       <c r="B38" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4576,25 +4581,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4604,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731416</v>
+        <v>731347</v>
       </c>
       <c r="R38" t="n">
-        <v>7457247</v>
+        <v>7457280</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4644,7 +4649,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4671,10 +4676,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302915</v>
+        <v>120302914</v>
       </c>
       <c r="B39" t="n">
-        <v>57431</v>
+        <v>90742</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4683,25 +4688,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>1588</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4711,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731716</v>
+        <v>731763</v>
       </c>
       <c r="R39" t="n">
-        <v>7457334</v>
+        <v>7457160</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4773,10 +4778,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302917</v>
+        <v>120302923</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4789,16 +4794,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4813,10 +4818,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731714</v>
+        <v>731716</v>
       </c>
       <c r="R40" t="n">
-        <v>7457298</v>
+        <v>7457137</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4880,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302919</v>
+        <v>120302906</v>
       </c>
       <c r="B41" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4896,21 +4901,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4920,10 +4925,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731642</v>
+        <v>731352</v>
       </c>
       <c r="R41" t="n">
-        <v>7457290</v>
+        <v>7457246</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4956,11 +4961,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,10 +4987,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120302913</v>
+        <v>120302924</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5003,16 +5003,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5027,10 +5027,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731549</v>
+        <v>731752</v>
       </c>
       <c r="R42" t="n">
-        <v>7457309</v>
+        <v>7457204</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5201,10 +5201,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120302896</v>
+        <v>120302879</v>
       </c>
       <c r="B44" t="n">
-        <v>79131</v>
+        <v>78278</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5217,21 +5217,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733023</v>
+        <v>733150</v>
       </c>
       <c r="R44" t="n">
-        <v>7457503</v>
+        <v>7457273</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5303,10 +5303,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120302895</v>
+        <v>120302903</v>
       </c>
       <c r="B45" t="n">
-        <v>57336</v>
+        <v>57748</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5319,21 +5319,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733086</v>
+        <v>732779</v>
       </c>
       <c r="R45" t="n">
-        <v>7457578</v>
+        <v>7457059</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5373,17 +5373,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5410,10 +5410,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120302900</v>
+        <v>120302899</v>
       </c>
       <c r="B46" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5422,20 +5422,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5450,10 +5450,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733011</v>
+        <v>732829</v>
       </c>
       <c r="R46" t="n">
-        <v>7457133</v>
+        <v>7457380</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5486,11 +5486,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5517,10 +5512,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120302901</v>
+        <v>120302902</v>
       </c>
       <c r="B47" t="n">
-        <v>57748</v>
+        <v>79131</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5533,21 +5528,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5557,10 +5552,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733049</v>
+        <v>733046</v>
       </c>
       <c r="R47" t="n">
-        <v>7457132</v>
+        <v>7457090</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5619,10 +5614,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302877</v>
+        <v>120302901</v>
       </c>
       <c r="B48" t="n">
-        <v>57431</v>
+        <v>57748</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5631,25 +5626,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>103001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5659,10 +5654,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733127</v>
+        <v>733049</v>
       </c>
       <c r="R48" t="n">
-        <v>7457136</v>
+        <v>7457132</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5695,11 +5690,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5828,10 +5818,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302899</v>
+        <v>120302897</v>
       </c>
       <c r="B50" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5844,16 +5834,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5868,10 +5858,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>732829</v>
+        <v>732853</v>
       </c>
       <c r="R50" t="n">
-        <v>7457380</v>
+        <v>7457442</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5904,6 +5894,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5930,7 +5925,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302878</v>
+        <v>120302895</v>
       </c>
       <c r="B51" t="n">
         <v>57336</v>
@@ -5970,10 +5965,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733152</v>
+        <v>733086</v>
       </c>
       <c r="R51" t="n">
-        <v>7457234</v>
+        <v>7457578</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6010,7 +6005,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6037,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302897</v>
+        <v>120302877</v>
       </c>
       <c r="B52" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6049,20 +6044,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6077,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>732853</v>
+        <v>733127</v>
       </c>
       <c r="R52" t="n">
-        <v>7457442</v>
+        <v>7457136</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6117,7 +6112,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6144,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302902</v>
+        <v>120302878</v>
       </c>
       <c r="B53" t="n">
-        <v>79131</v>
+        <v>57336</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6160,21 +6155,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6184,10 +6179,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733046</v>
+        <v>733152</v>
       </c>
       <c r="R53" t="n">
-        <v>7457090</v>
+        <v>7457234</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6220,6 +6215,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6246,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302903</v>
+        <v>120302896</v>
       </c>
       <c r="B54" t="n">
-        <v>57748</v>
+        <v>79131</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6262,21 +6262,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103001</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>732779</v>
+        <v>733023</v>
       </c>
       <c r="R54" t="n">
-        <v>7457059</v>
+        <v>7457503</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6316,17 +6316,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6353,10 +6348,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302879</v>
+        <v>120302900</v>
       </c>
       <c r="B55" t="n">
-        <v>78278</v>
+        <v>57431</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6365,25 +6360,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6393,10 +6388,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733150</v>
+        <v>733011</v>
       </c>
       <c r="R55" t="n">
-        <v>7457273</v>
+        <v>7457133</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6429,6 +6424,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -5925,10 +5925,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302895</v>
+        <v>120302877</v>
       </c>
       <c r="B51" t="n">
-        <v>57336</v>
+        <v>57431</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5937,20 +5937,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733086</v>
+        <v>733127</v>
       </c>
       <c r="R51" t="n">
-        <v>7457578</v>
+        <v>7457136</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6032,10 +6032,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302877</v>
+        <v>120302895</v>
       </c>
       <c r="B52" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6044,20 +6044,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733127</v>
+        <v>733086</v>
       </c>
       <c r="R52" t="n">
-        <v>7457136</v>
+        <v>7457578</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Fyra individer</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6139,10 +6139,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302878</v>
+        <v>120302896</v>
       </c>
       <c r="B53" t="n">
-        <v>57336</v>
+        <v>79131</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6155,21 +6155,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733152</v>
+        <v>733023</v>
       </c>
       <c r="R53" t="n">
-        <v>7457234</v>
+        <v>7457503</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6215,11 +6215,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6246,10 +6241,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302896</v>
+        <v>120302878</v>
       </c>
       <c r="B54" t="n">
-        <v>79131</v>
+        <v>57336</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6262,21 +6257,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6286,10 +6281,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733023</v>
+        <v>733152</v>
       </c>
       <c r="R54" t="n">
-        <v>7457503</v>
+        <v>7457234</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6322,6 +6317,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -5136,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338692</v>
+        <v>121338686</v>
       </c>
       <c r="B44" t="n">
-        <v>57348</v>
+        <v>57776</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5152,21 +5152,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>732035</v>
+        <v>731797</v>
       </c>
       <c r="R44" t="n">
-        <v>7457821</v>
+        <v>7457819</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338686</v>
+        <v>121338692</v>
       </c>
       <c r="B45" t="n">
-        <v>57776</v>
+        <v>57348</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731797</v>
+        <v>732035</v>
       </c>
       <c r="R45" t="n">
-        <v>7457819</v>
+        <v>7457821</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2783,7 +2783,7 @@
         <v>121338701</v>
       </c>
       <c r="B21" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338721</v>
+        <v>121338716</v>
       </c>
       <c r="B22" t="n">
-        <v>97025</v>
+        <v>79711</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735756</v>
+        <v>735787</v>
       </c>
       <c r="R22" t="n">
-        <v>7459178</v>
+        <v>7459247</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338712</v>
+        <v>121338717</v>
       </c>
       <c r="B23" t="n">
-        <v>97025</v>
+        <v>79711</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735645</v>
+        <v>735799</v>
       </c>
       <c r="R23" t="n">
-        <v>7459290</v>
+        <v>7459254</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338700</v>
+        <v>121338704</v>
       </c>
       <c r="B24" t="n">
-        <v>97031</v>
+        <v>91967</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735294</v>
+        <v>735170</v>
       </c>
       <c r="R24" t="n">
-        <v>7459118</v>
+        <v>7459303</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338718</v>
+        <v>121338703</v>
       </c>
       <c r="B25" t="n">
-        <v>90705</v>
+        <v>97035</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735749</v>
+        <v>735177</v>
       </c>
       <c r="R25" t="n">
-        <v>7459256</v>
+        <v>7459280</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338702</v>
+        <v>121338721</v>
       </c>
       <c r="B26" t="n">
-        <v>91955</v>
+        <v>97035</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735224</v>
+        <v>735756</v>
       </c>
       <c r="R26" t="n">
-        <v>7459176</v>
+        <v>7459178</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338704</v>
+        <v>121338699</v>
       </c>
       <c r="B27" t="n">
-        <v>91957</v>
+        <v>97041</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735170</v>
+        <v>735424</v>
       </c>
       <c r="R27" t="n">
-        <v>7459303</v>
+        <v>7459188</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338703</v>
+        <v>121338700</v>
       </c>
       <c r="B28" t="n">
-        <v>97025</v>
+        <v>97041</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735177</v>
+        <v>735294</v>
       </c>
       <c r="R28" t="n">
-        <v>7459280</v>
+        <v>7459118</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338699</v>
+        <v>121338718</v>
       </c>
       <c r="B29" t="n">
-        <v>97031</v>
+        <v>90715</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3608,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735424</v>
+        <v>735749</v>
       </c>
       <c r="R29" t="n">
-        <v>7459188</v>
+        <v>7459256</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338719</v>
+        <v>121338702</v>
       </c>
       <c r="B30" t="n">
-        <v>90687</v>
+        <v>91965</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735757</v>
+        <v>735224</v>
       </c>
       <c r="R30" t="n">
-        <v>7459269</v>
+        <v>7459176</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338717</v>
+        <v>121338712</v>
       </c>
       <c r="B31" t="n">
-        <v>79708</v>
+        <v>97035</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735799</v>
+        <v>735645</v>
       </c>
       <c r="R31" t="n">
-        <v>7459254</v>
+        <v>7459290</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338716</v>
+        <v>121338719</v>
       </c>
       <c r="B32" t="n">
-        <v>79708</v>
+        <v>90697</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735787</v>
+        <v>735757</v>
       </c>
       <c r="R32" t="n">
-        <v>7459247</v>
+        <v>7459269</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338671</v>
+        <v>121338674</v>
       </c>
       <c r="B34" t="n">
-        <v>56552</v>
+        <v>100320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732502</v>
+        <v>732485</v>
       </c>
       <c r="R34" t="n">
-        <v>7457961</v>
+        <v>7457959</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4211,7 +4211,7 @@
         <v>121338672</v>
       </c>
       <c r="B35" t="n">
-        <v>57782</v>
+        <v>57785</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338674</v>
+        <v>121338676</v>
       </c>
       <c r="B36" t="n">
-        <v>100310</v>
+        <v>97035</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4326,21 +4326,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732485</v>
+        <v>732460</v>
       </c>
       <c r="R36" t="n">
-        <v>7457959</v>
+        <v>7457939</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338676</v>
+        <v>121338671</v>
       </c>
       <c r="B37" t="n">
-        <v>97025</v>
+        <v>56555</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,25 +4424,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732460</v>
+        <v>732502</v>
       </c>
       <c r="R37" t="n">
-        <v>7457939</v>
+        <v>7457961</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338689</v>
+        <v>121338691</v>
       </c>
       <c r="B42" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731977</v>
+        <v>732025</v>
       </c>
       <c r="R42" t="n">
-        <v>7457792</v>
+        <v>7457818</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5037,7 +5037,7 @@
         <v>121338690</v>
       </c>
       <c r="B43" t="n">
-        <v>90973</v>
+        <v>90983</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338686</v>
+        <v>121338687</v>
       </c>
       <c r="B44" t="n">
-        <v>57776</v>
+        <v>97035</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5148,25 +5148,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731797</v>
+        <v>731849</v>
       </c>
       <c r="R44" t="n">
-        <v>7457819</v>
+        <v>7457769</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338692</v>
+        <v>121338686</v>
       </c>
       <c r="B45" t="n">
-        <v>57348</v>
+        <v>57779</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732035</v>
+        <v>731797</v>
       </c>
       <c r="R45" t="n">
-        <v>7457821</v>
+        <v>7457819</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5340,10 +5340,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338691</v>
+        <v>121338692</v>
       </c>
       <c r="B46" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5356,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732025</v>
+        <v>732035</v>
       </c>
       <c r="R46" t="n">
-        <v>7457818</v>
+        <v>7457821</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5442,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338687</v>
+        <v>121338689</v>
       </c>
       <c r="B47" t="n">
-        <v>97025</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,25 +5454,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731849</v>
+        <v>731977</v>
       </c>
       <c r="R47" t="n">
-        <v>7457769</v>
+        <v>7457792</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8699,10 +8699,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338668</v>
+        <v>121338665</v>
       </c>
       <c r="B78" t="n">
-        <v>90973</v>
+        <v>90697</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>732643</v>
+        <v>733143</v>
       </c>
       <c r="R78" t="n">
-        <v>7457301</v>
+        <v>7456923</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8801,10 +8801,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338634</v>
+        <v>121338663</v>
       </c>
       <c r="B79" t="n">
-        <v>90705</v>
+        <v>90697</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8817,21 +8817,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733192</v>
+        <v>733283</v>
       </c>
       <c r="R79" t="n">
-        <v>7456971</v>
+        <v>7456886</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338663</v>
+        <v>121338634</v>
       </c>
       <c r="B80" t="n">
-        <v>90687</v>
+        <v>90715</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8919,21 +8919,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733283</v>
+        <v>733192</v>
       </c>
       <c r="R80" t="n">
-        <v>7456886</v>
+        <v>7456971</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338694</v>
+        <v>121338662</v>
       </c>
       <c r="B81" t="n">
-        <v>57776</v>
+        <v>97041</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9017,25 +9017,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103001</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>732301</v>
+        <v>733321</v>
       </c>
       <c r="R81" t="n">
-        <v>7457166</v>
+        <v>7456889</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9075,12 +9075,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9107,10 +9107,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338669</v>
+        <v>121338668</v>
       </c>
       <c r="B82" t="n">
-        <v>56560</v>
+        <v>90983</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9119,25 +9119,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732688</v>
+        <v>732643</v>
       </c>
       <c r="R82" t="n">
-        <v>7457404</v>
+        <v>7457301</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9209,10 +9209,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338695</v>
+        <v>121338664</v>
       </c>
       <c r="B83" t="n">
-        <v>56560</v>
+        <v>57367</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9221,25 +9221,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>732297</v>
+        <v>733274</v>
       </c>
       <c r="R83" t="n">
-        <v>7457098</v>
+        <v>7456913</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9279,17 +9279,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9316,10 +9311,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338664</v>
+        <v>121338670</v>
       </c>
       <c r="B84" t="n">
-        <v>57364</v>
+        <v>97041</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9328,25 +9323,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9356,10 +9351,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733274</v>
+        <v>732725</v>
       </c>
       <c r="R84" t="n">
-        <v>7456913</v>
+        <v>7457530</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9386,12 +9381,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9418,10 +9413,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338670</v>
+        <v>121338695</v>
       </c>
       <c r="B85" t="n">
-        <v>97031</v>
+        <v>56563</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9434,21 +9429,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9458,10 +9453,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732725</v>
+        <v>732297</v>
       </c>
       <c r="R85" t="n">
-        <v>7457530</v>
+        <v>7457098</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9494,6 +9489,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9520,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338665</v>
+        <v>121338669</v>
       </c>
       <c r="B86" t="n">
-        <v>90687</v>
+        <v>56563</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9532,25 +9532,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733143</v>
+        <v>732688</v>
       </c>
       <c r="R86" t="n">
-        <v>7456923</v>
+        <v>7457404</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9590,12 +9590,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338662</v>
+        <v>121338697</v>
       </c>
       <c r="B87" t="n">
-        <v>97031</v>
+        <v>97041</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733321</v>
+        <v>732290</v>
       </c>
       <c r="R87" t="n">
-        <v>7456889</v>
+        <v>7457046</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338697</v>
+        <v>121338694</v>
       </c>
       <c r="B88" t="n">
-        <v>97031</v>
+        <v>57779</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9736,25 +9736,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>103001</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732290</v>
+        <v>732301</v>
       </c>
       <c r="R88" t="n">
-        <v>7457046</v>
+        <v>7457166</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338712</v>
+        <v>121338719</v>
       </c>
       <c r="B31" t="n">
-        <v>97035</v>
+        <v>90697</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735645</v>
+        <v>735757</v>
       </c>
       <c r="R31" t="n">
-        <v>7459290</v>
+        <v>7459269</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338719</v>
+        <v>121338712</v>
       </c>
       <c r="B32" t="n">
-        <v>90697</v>
+        <v>97035</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735757</v>
+        <v>735645</v>
       </c>
       <c r="R32" t="n">
-        <v>7459269</v>
+        <v>7459290</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338701</v>
+        <v>121338716</v>
       </c>
       <c r="B21" t="n">
-        <v>91973</v>
+        <v>79711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735254</v>
+        <v>735787</v>
       </c>
       <c r="R21" t="n">
-        <v>7459137</v>
+        <v>7459247</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338716</v>
+        <v>121338712</v>
       </c>
       <c r="B22" t="n">
-        <v>79711</v>
+        <v>97035</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735787</v>
+        <v>735645</v>
       </c>
       <c r="R22" t="n">
-        <v>7459247</v>
+        <v>7459290</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338717</v>
+        <v>121338699</v>
       </c>
       <c r="B23" t="n">
-        <v>79711</v>
+        <v>97041</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735799</v>
+        <v>735424</v>
       </c>
       <c r="R23" t="n">
-        <v>7459254</v>
+        <v>7459188</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338704</v>
+        <v>121338701</v>
       </c>
       <c r="B24" t="n">
-        <v>91967</v>
+        <v>91973</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735170</v>
+        <v>735254</v>
       </c>
       <c r="R24" t="n">
-        <v>7459303</v>
+        <v>7459137</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338703</v>
+        <v>121338718</v>
       </c>
       <c r="B25" t="n">
-        <v>97035</v>
+        <v>90715</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735177</v>
+        <v>735749</v>
       </c>
       <c r="R25" t="n">
-        <v>7459280</v>
+        <v>7459256</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338721</v>
+        <v>121338702</v>
       </c>
       <c r="B26" t="n">
-        <v>97035</v>
+        <v>91965</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735756</v>
+        <v>735224</v>
       </c>
       <c r="R26" t="n">
-        <v>7459178</v>
+        <v>7459176</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338699</v>
+        <v>121338700</v>
       </c>
       <c r="B27" t="n">
         <v>97041</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735424</v>
+        <v>735294</v>
       </c>
       <c r="R27" t="n">
-        <v>7459188</v>
+        <v>7459118</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338700</v>
+        <v>121338703</v>
       </c>
       <c r="B28" t="n">
-        <v>97041</v>
+        <v>97035</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735294</v>
+        <v>735177</v>
       </c>
       <c r="R28" t="n">
-        <v>7459118</v>
+        <v>7459280</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338718</v>
+        <v>121338717</v>
       </c>
       <c r="B29" t="n">
-        <v>90715</v>
+        <v>79711</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3608,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735749</v>
+        <v>735799</v>
       </c>
       <c r="R29" t="n">
-        <v>7459256</v>
+        <v>7459254</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338702</v>
+        <v>121338721</v>
       </c>
       <c r="B30" t="n">
-        <v>91965</v>
+        <v>97035</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,25 +3710,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735224</v>
+        <v>735756</v>
       </c>
       <c r="R30" t="n">
-        <v>7459176</v>
+        <v>7459178</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338712</v>
+        <v>121338704</v>
       </c>
       <c r="B32" t="n">
-        <v>97035</v>
+        <v>91967</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735645</v>
+        <v>735170</v>
       </c>
       <c r="R32" t="n">
-        <v>7459290</v>
+        <v>7459303</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338674</v>
+        <v>121338671</v>
       </c>
       <c r="B34" t="n">
-        <v>100320</v>
+        <v>56555</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732485</v>
+        <v>732502</v>
       </c>
       <c r="R34" t="n">
-        <v>7457959</v>
+        <v>7457961</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338672</v>
+        <v>121338675</v>
       </c>
       <c r="B35" t="n">
-        <v>57785</v>
+        <v>100320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4220,25 +4220,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102999</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732533</v>
+        <v>732485</v>
       </c>
       <c r="R35" t="n">
-        <v>7457997</v>
+        <v>7457959</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4284,6 +4284,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4310,10 +4315,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338676</v>
+        <v>121338672</v>
       </c>
       <c r="B36" t="n">
-        <v>97035</v>
+        <v>57785</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4327,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>102999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4355,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732460</v>
+        <v>732533</v>
       </c>
       <c r="R36" t="n">
-        <v>7457939</v>
+        <v>7457997</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4412,10 +4417,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338671</v>
+        <v>121338676</v>
       </c>
       <c r="B37" t="n">
-        <v>56555</v>
+        <v>97035</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,25 +4429,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4457,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732502</v>
+        <v>732460</v>
       </c>
       <c r="R37" t="n">
-        <v>7457961</v>
+        <v>7457939</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4932,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338691</v>
+        <v>121338689</v>
       </c>
       <c r="B42" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4953,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>732025</v>
+        <v>731977</v>
       </c>
       <c r="R42" t="n">
-        <v>7457818</v>
+        <v>7457792</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5238,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338686</v>
+        <v>121338692</v>
       </c>
       <c r="B45" t="n">
-        <v>57779</v>
+        <v>57351</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5259,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731797</v>
+        <v>732035</v>
       </c>
       <c r="R45" t="n">
-        <v>7457819</v>
+        <v>7457821</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5340,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338692</v>
+        <v>121338691</v>
       </c>
       <c r="B46" t="n">
-        <v>57351</v>
+        <v>90715</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5361,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732035</v>
+        <v>732025</v>
       </c>
       <c r="R46" t="n">
-        <v>7457821</v>
+        <v>7457818</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5442,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338689</v>
+        <v>121338686</v>
       </c>
       <c r="B47" t="n">
-        <v>90697</v>
+        <v>57779</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731977</v>
+        <v>731797</v>
       </c>
       <c r="R47" t="n">
-        <v>7457792</v>
+        <v>7457819</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8699,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338665</v>
+        <v>121338634</v>
       </c>
       <c r="B78" t="n">
-        <v>90697</v>
+        <v>90715</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8715,21 +8720,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733143</v>
+        <v>733192</v>
       </c>
       <c r="R78" t="n">
-        <v>7456923</v>
+        <v>7456971</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8801,10 +8806,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338663</v>
+        <v>121338664</v>
       </c>
       <c r="B79" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8817,21 +8822,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8841,10 +8846,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733283</v>
+        <v>733274</v>
       </c>
       <c r="R79" t="n">
-        <v>7456886</v>
+        <v>7456913</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8903,10 +8908,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338634</v>
+        <v>121338663</v>
       </c>
       <c r="B80" t="n">
-        <v>90715</v>
+        <v>90697</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8919,21 +8924,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733192</v>
+        <v>733283</v>
       </c>
       <c r="R80" t="n">
-        <v>7456971</v>
+        <v>7456886</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9005,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338662</v>
+        <v>121338665</v>
       </c>
       <c r="B81" t="n">
-        <v>97041</v>
+        <v>90697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9017,25 +9022,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9045,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733321</v>
+        <v>733143</v>
       </c>
       <c r="R81" t="n">
-        <v>7456889</v>
+        <v>7456923</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9209,10 +9214,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338664</v>
+        <v>121338670</v>
       </c>
       <c r="B83" t="n">
-        <v>57367</v>
+        <v>97041</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9221,25 +9226,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9249,10 +9254,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733274</v>
+        <v>732725</v>
       </c>
       <c r="R83" t="n">
-        <v>7456913</v>
+        <v>7457530</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9279,12 +9284,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9311,10 +9316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338670</v>
+        <v>121338669</v>
       </c>
       <c r="B84" t="n">
-        <v>97041</v>
+        <v>56563</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9327,21 +9332,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9351,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732725</v>
+        <v>732688</v>
       </c>
       <c r="R84" t="n">
-        <v>7457530</v>
+        <v>7457404</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9413,10 +9418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338695</v>
+        <v>121338694</v>
       </c>
       <c r="B85" t="n">
-        <v>56563</v>
+        <v>57779</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9425,25 +9430,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9453,10 +9458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732297</v>
+        <v>732301</v>
       </c>
       <c r="R85" t="n">
-        <v>7457098</v>
+        <v>7457166</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9489,11 +9494,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9520,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338669</v>
+        <v>121338697</v>
       </c>
       <c r="B86" t="n">
-        <v>56563</v>
+        <v>97041</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9536,21 +9536,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732688</v>
+        <v>732290</v>
       </c>
       <c r="R86" t="n">
-        <v>7457404</v>
+        <v>7457046</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9622,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338697</v>
+        <v>121338695</v>
       </c>
       <c r="B87" t="n">
-        <v>97041</v>
+        <v>56563</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9638,21 +9638,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>732290</v>
+        <v>732297</v>
       </c>
       <c r="R87" t="n">
-        <v>7457046</v>
+        <v>7457098</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9698,6 +9698,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9724,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338694</v>
+        <v>121338662</v>
       </c>
       <c r="B88" t="n">
-        <v>57779</v>
+        <v>97041</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9736,25 +9741,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103001</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9769,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732301</v>
+        <v>733321</v>
       </c>
       <c r="R88" t="n">
-        <v>7457166</v>
+        <v>7456889</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9794,12 +9799,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338716</v>
+        <v>121338712</v>
       </c>
       <c r="B21" t="n">
-        <v>79711</v>
+        <v>97035</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735787</v>
+        <v>735645</v>
       </c>
       <c r="R21" t="n">
-        <v>7459247</v>
+        <v>7459290</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338712</v>
+        <v>121338699</v>
       </c>
       <c r="B22" t="n">
-        <v>97035</v>
+        <v>97041</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735645</v>
+        <v>735424</v>
       </c>
       <c r="R22" t="n">
-        <v>7459290</v>
+        <v>7459188</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338699</v>
+        <v>121338716</v>
       </c>
       <c r="B23" t="n">
-        <v>97041</v>
+        <v>79711</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735424</v>
+        <v>735787</v>
       </c>
       <c r="R23" t="n">
-        <v>7459188</v>
+        <v>7459247</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338689</v>
+        <v>121338690</v>
       </c>
       <c r="B42" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4953,21 +4953,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,7 +4980,7 @@
         <v>731977</v>
       </c>
       <c r="R42" t="n">
-        <v>7457792</v>
+        <v>7457791</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338690</v>
+        <v>121338689</v>
       </c>
       <c r="B43" t="n">
-        <v>90983</v>
+        <v>90697</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5055,21 +5055,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
         <v>731977</v>
       </c>
       <c r="R43" t="n">
-        <v>7457791</v>
+        <v>7457792</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338712</v>
+        <v>121338704</v>
       </c>
       <c r="B21" t="n">
-        <v>97035</v>
+        <v>91979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735645</v>
+        <v>735170</v>
       </c>
       <c r="R21" t="n">
-        <v>7459290</v>
+        <v>7459303</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338699</v>
+        <v>121338718</v>
       </c>
       <c r="B22" t="n">
-        <v>97041</v>
+        <v>90727</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735424</v>
+        <v>735749</v>
       </c>
       <c r="R22" t="n">
-        <v>7459188</v>
+        <v>7459256</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338716</v>
+        <v>121338712</v>
       </c>
       <c r="B23" t="n">
-        <v>79711</v>
+        <v>97048</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735787</v>
+        <v>735645</v>
       </c>
       <c r="R23" t="n">
-        <v>7459247</v>
+        <v>7459290</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338701</v>
+        <v>121338719</v>
       </c>
       <c r="B24" t="n">
-        <v>91973</v>
+        <v>90709</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735254</v>
+        <v>735757</v>
       </c>
       <c r="R24" t="n">
-        <v>7459137</v>
+        <v>7459269</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338718</v>
+        <v>121338701</v>
       </c>
       <c r="B25" t="n">
-        <v>90715</v>
+        <v>91985</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735749</v>
+        <v>735254</v>
       </c>
       <c r="R25" t="n">
-        <v>7459256</v>
+        <v>7459137</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3293,7 +3293,7 @@
         <v>121338702</v>
       </c>
       <c r="B26" t="n">
-        <v>91965</v>
+        <v>91977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338700</v>
+        <v>121338721</v>
       </c>
       <c r="B27" t="n">
-        <v>97041</v>
+        <v>97048</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,16 +3408,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735294</v>
+        <v>735756</v>
       </c>
       <c r="R27" t="n">
-        <v>7459118</v>
+        <v>7459178</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338703</v>
+        <v>121338700</v>
       </c>
       <c r="B28" t="n">
-        <v>97035</v>
+        <v>97054</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735177</v>
+        <v>735294</v>
       </c>
       <c r="R28" t="n">
-        <v>7459280</v>
+        <v>7459118</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338717</v>
+        <v>121338703</v>
       </c>
       <c r="B29" t="n">
-        <v>79711</v>
+        <v>97048</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735799</v>
+        <v>735177</v>
       </c>
       <c r="R29" t="n">
-        <v>7459254</v>
+        <v>7459280</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338721</v>
+        <v>121338717</v>
       </c>
       <c r="B30" t="n">
-        <v>97035</v>
+        <v>79714</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735756</v>
+        <v>735799</v>
       </c>
       <c r="R30" t="n">
-        <v>7459178</v>
+        <v>7459254</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338719</v>
+        <v>121338716</v>
       </c>
       <c r="B31" t="n">
-        <v>90697</v>
+        <v>79714</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735757</v>
+        <v>735787</v>
       </c>
       <c r="R31" t="n">
-        <v>7459269</v>
+        <v>7459247</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338704</v>
+        <v>121338699</v>
       </c>
       <c r="B32" t="n">
-        <v>91967</v>
+        <v>97054</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735170</v>
+        <v>735424</v>
       </c>
       <c r="R32" t="n">
-        <v>7459303</v>
+        <v>7459188</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338671</v>
+        <v>121338672</v>
       </c>
       <c r="B34" t="n">
-        <v>56555</v>
+        <v>57785</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>102999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732502</v>
+        <v>732533</v>
       </c>
       <c r="R34" t="n">
-        <v>7457961</v>
+        <v>7457997</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338675</v>
+        <v>121338674</v>
       </c>
       <c r="B35" t="n">
-        <v>100320</v>
+        <v>100333</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4284,11 +4284,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 m2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4315,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338672</v>
+        <v>121338676</v>
       </c>
       <c r="B36" t="n">
-        <v>57785</v>
+        <v>97048</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4327,25 +4322,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102999</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4355,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732533</v>
+        <v>732460</v>
       </c>
       <c r="R36" t="n">
-        <v>7457997</v>
+        <v>7457939</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4417,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338676</v>
+        <v>121338671</v>
       </c>
       <c r="B37" t="n">
-        <v>97035</v>
+        <v>56555</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4429,25 +4424,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4457,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732460</v>
+        <v>732502</v>
       </c>
       <c r="R37" t="n">
-        <v>7457939</v>
+        <v>7457961</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4937,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338690</v>
+        <v>121338692</v>
       </c>
       <c r="B42" t="n">
-        <v>90983</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4953,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731977</v>
+        <v>732035</v>
       </c>
       <c r="R42" t="n">
-        <v>7457791</v>
+        <v>7457821</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5039,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338689</v>
+        <v>121338687</v>
       </c>
       <c r="B43" t="n">
-        <v>90697</v>
+        <v>97048</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5051,25 +5046,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5079,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>731977</v>
+        <v>731849</v>
       </c>
       <c r="R43" t="n">
-        <v>7457792</v>
+        <v>7457769</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5141,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338687</v>
+        <v>121338689</v>
       </c>
       <c r="B44" t="n">
-        <v>97035</v>
+        <v>90709</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,25 +5148,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5181,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731849</v>
+        <v>731977</v>
       </c>
       <c r="R44" t="n">
-        <v>7457769</v>
+        <v>7457792</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338692</v>
+        <v>121338690</v>
       </c>
       <c r="B45" t="n">
-        <v>57351</v>
+        <v>90995</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5259,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732035</v>
+        <v>731977</v>
       </c>
       <c r="R45" t="n">
-        <v>7457821</v>
+        <v>7457791</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5345,10 +5340,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338691</v>
+        <v>121338686</v>
       </c>
       <c r="B46" t="n">
-        <v>90715</v>
+        <v>57779</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5361,21 +5356,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5385,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732025</v>
+        <v>731797</v>
       </c>
       <c r="R46" t="n">
-        <v>7457818</v>
+        <v>7457819</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5447,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338686</v>
+        <v>121338691</v>
       </c>
       <c r="B47" t="n">
-        <v>57779</v>
+        <v>90727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,21 +5458,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5482,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731797</v>
+        <v>732025</v>
       </c>
       <c r="R47" t="n">
-        <v>7457819</v>
+        <v>7457818</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8704,10 +8699,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338634</v>
+        <v>121338665</v>
       </c>
       <c r="B78" t="n">
-        <v>90715</v>
+        <v>90709</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8720,21 +8715,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733192</v>
+        <v>733143</v>
       </c>
       <c r="R78" t="n">
-        <v>7456971</v>
+        <v>7456923</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338664</v>
+        <v>121338694</v>
       </c>
       <c r="B79" t="n">
-        <v>57367</v>
+        <v>57779</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8822,21 +8817,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8846,10 +8841,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733274</v>
+        <v>732301</v>
       </c>
       <c r="R79" t="n">
-        <v>7456913</v>
+        <v>7457166</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8876,12 +8871,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8908,10 +8903,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338663</v>
+        <v>121338697</v>
       </c>
       <c r="B80" t="n">
-        <v>90697</v>
+        <v>97054</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8920,25 +8915,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733283</v>
+        <v>732290</v>
       </c>
       <c r="R80" t="n">
-        <v>7456886</v>
+        <v>7457046</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8978,12 +8973,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9010,10 +9005,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338665</v>
+        <v>121338664</v>
       </c>
       <c r="B81" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9026,21 +9021,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9045,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733143</v>
+        <v>733274</v>
       </c>
       <c r="R81" t="n">
-        <v>7456923</v>
+        <v>7456913</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9112,10 +9107,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338668</v>
+        <v>121338663</v>
       </c>
       <c r="B82" t="n">
-        <v>90983</v>
+        <v>90709</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9128,21 +9123,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9152,10 +9147,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732643</v>
+        <v>733283</v>
       </c>
       <c r="R82" t="n">
-        <v>7457301</v>
+        <v>7456886</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9182,12 +9177,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9214,10 +9209,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338670</v>
+        <v>121338669</v>
       </c>
       <c r="B83" t="n">
-        <v>97041</v>
+        <v>56563</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9230,21 +9225,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9254,10 +9249,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>732725</v>
+        <v>732688</v>
       </c>
       <c r="R83" t="n">
-        <v>7457530</v>
+        <v>7457404</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9316,10 +9311,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338669</v>
+        <v>121338662</v>
       </c>
       <c r="B84" t="n">
-        <v>56563</v>
+        <v>97054</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9332,21 +9327,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9356,10 +9351,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732688</v>
+        <v>733321</v>
       </c>
       <c r="R84" t="n">
-        <v>7457404</v>
+        <v>7456889</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9386,12 +9381,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9418,10 +9413,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338694</v>
+        <v>121338668</v>
       </c>
       <c r="B85" t="n">
-        <v>57779</v>
+        <v>90995</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9434,21 +9429,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103001</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9458,10 +9453,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732301</v>
+        <v>732643</v>
       </c>
       <c r="R85" t="n">
-        <v>7457166</v>
+        <v>7457301</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9520,10 +9515,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338697</v>
+        <v>121338695</v>
       </c>
       <c r="B86" t="n">
-        <v>97041</v>
+        <v>56563</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9536,21 +9531,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9555,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732290</v>
+        <v>732297</v>
       </c>
       <c r="R86" t="n">
-        <v>7457046</v>
+        <v>7457098</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9596,6 +9591,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338695</v>
+        <v>121338670</v>
       </c>
       <c r="B87" t="n">
-        <v>56563</v>
+        <v>97054</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9638,21 +9638,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>732297</v>
+        <v>732725</v>
       </c>
       <c r="R87" t="n">
-        <v>7457098</v>
+        <v>7457530</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9698,11 +9698,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9729,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338662</v>
+        <v>121338634</v>
       </c>
       <c r="B88" t="n">
-        <v>97041</v>
+        <v>90727</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9741,25 +9736,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9769,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733321</v>
+        <v>733192</v>
       </c>
       <c r="R88" t="n">
-        <v>7456889</v>
+        <v>7456971</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338704</v>
+        <v>121338719</v>
       </c>
       <c r="B21" t="n">
-        <v>91979</v>
+        <v>90710</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735170</v>
+        <v>735757</v>
       </c>
       <c r="R21" t="n">
-        <v>7459303</v>
+        <v>7459269</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338718</v>
+        <v>121338703</v>
       </c>
       <c r="B22" t="n">
-        <v>90727</v>
+        <v>97049</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735749</v>
+        <v>735177</v>
       </c>
       <c r="R22" t="n">
-        <v>7459256</v>
+        <v>7459280</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338712</v>
+        <v>121338721</v>
       </c>
       <c r="B23" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735645</v>
+        <v>735756</v>
       </c>
       <c r="R23" t="n">
-        <v>7459290</v>
+        <v>7459178</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338719</v>
+        <v>121338717</v>
       </c>
       <c r="B24" t="n">
-        <v>90709</v>
+        <v>79714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735757</v>
+        <v>735799</v>
       </c>
       <c r="R24" t="n">
-        <v>7459269</v>
+        <v>7459254</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338701</v>
+        <v>121338712</v>
       </c>
       <c r="B25" t="n">
-        <v>91985</v>
+        <v>97049</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735254</v>
+        <v>735645</v>
       </c>
       <c r="R25" t="n">
-        <v>7459137</v>
+        <v>7459290</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338702</v>
+        <v>121338700</v>
       </c>
       <c r="B26" t="n">
-        <v>91977</v>
+        <v>97055</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735224</v>
+        <v>735294</v>
       </c>
       <c r="R26" t="n">
-        <v>7459176</v>
+        <v>7459118</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338721</v>
+        <v>121338718</v>
       </c>
       <c r="B27" t="n">
-        <v>97048</v>
+        <v>90728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735756</v>
+        <v>735749</v>
       </c>
       <c r="R27" t="n">
-        <v>7459178</v>
+        <v>7459256</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338700</v>
+        <v>121338704</v>
       </c>
       <c r="B28" t="n">
-        <v>97054</v>
+        <v>91980</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,25 +3506,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735294</v>
+        <v>735170</v>
       </c>
       <c r="R28" t="n">
-        <v>7459118</v>
+        <v>7459303</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338703</v>
+        <v>121338702</v>
       </c>
       <c r="B29" t="n">
-        <v>97048</v>
+        <v>91978</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3608,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735177</v>
+        <v>735224</v>
       </c>
       <c r="R29" t="n">
-        <v>7459280</v>
+        <v>7459176</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338717</v>
+        <v>121338701</v>
       </c>
       <c r="B30" t="n">
-        <v>79714</v>
+        <v>91986</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735799</v>
+        <v>735254</v>
       </c>
       <c r="R30" t="n">
-        <v>7459254</v>
+        <v>7459137</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338716</v>
+        <v>121338699</v>
       </c>
       <c r="B31" t="n">
-        <v>79714</v>
+        <v>97055</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735787</v>
+        <v>735424</v>
       </c>
       <c r="R31" t="n">
-        <v>7459247</v>
+        <v>7459188</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338699</v>
+        <v>121338716</v>
       </c>
       <c r="B32" t="n">
-        <v>97054</v>
+        <v>79714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735424</v>
+        <v>735787</v>
       </c>
       <c r="R32" t="n">
-        <v>7459188</v>
+        <v>7459247</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338672</v>
+        <v>121338674</v>
       </c>
       <c r="B34" t="n">
-        <v>57785</v>
+        <v>100334</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102999</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732533</v>
+        <v>732485</v>
       </c>
       <c r="R34" t="n">
-        <v>7457997</v>
+        <v>7457959</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338674</v>
+        <v>121338672</v>
       </c>
       <c r="B35" t="n">
-        <v>100333</v>
+        <v>57785</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4220,25 +4220,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>102999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732485</v>
+        <v>732533</v>
       </c>
       <c r="R35" t="n">
-        <v>7457959</v>
+        <v>7457997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338676</v>
+        <v>121338671</v>
       </c>
       <c r="B36" t="n">
-        <v>97048</v>
+        <v>56555</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732460</v>
+        <v>732502</v>
       </c>
       <c r="R36" t="n">
-        <v>7457939</v>
+        <v>7457961</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338671</v>
+        <v>121338676</v>
       </c>
       <c r="B37" t="n">
-        <v>56555</v>
+        <v>97049</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,25 +4424,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732502</v>
+        <v>732460</v>
       </c>
       <c r="R37" t="n">
-        <v>7457961</v>
+        <v>7457939</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338692</v>
+        <v>121338690</v>
       </c>
       <c r="B42" t="n">
-        <v>57351</v>
+        <v>90996</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>732035</v>
+        <v>731977</v>
       </c>
       <c r="R42" t="n">
-        <v>7457821</v>
+        <v>7457791</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338687</v>
+        <v>121338692</v>
       </c>
       <c r="B43" t="n">
-        <v>97048</v>
+        <v>57351</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5046,25 +5046,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>731849</v>
+        <v>732035</v>
       </c>
       <c r="R43" t="n">
-        <v>7457769</v>
+        <v>7457821</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5139,7 +5139,7 @@
         <v>121338689</v>
       </c>
       <c r="B44" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338690</v>
+        <v>121338691</v>
       </c>
       <c r="B45" t="n">
-        <v>90995</v>
+        <v>90728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731977</v>
+        <v>732025</v>
       </c>
       <c r="R45" t="n">
-        <v>7457791</v>
+        <v>7457818</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5442,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338691</v>
+        <v>121338687</v>
       </c>
       <c r="B47" t="n">
-        <v>90727</v>
+        <v>97049</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,25 +5454,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732025</v>
+        <v>731849</v>
       </c>
       <c r="R47" t="n">
-        <v>7457818</v>
+        <v>7457769</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8702,7 +8702,7 @@
         <v>121338665</v>
       </c>
       <c r="B78" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8801,10 +8801,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338694</v>
+        <v>121338668</v>
       </c>
       <c r="B79" t="n">
-        <v>57779</v>
+        <v>90996</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8817,21 +8817,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103001</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>732301</v>
+        <v>732643</v>
       </c>
       <c r="R79" t="n">
-        <v>7457166</v>
+        <v>7457301</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338697</v>
+        <v>121338695</v>
       </c>
       <c r="B80" t="n">
-        <v>97054</v>
+        <v>56563</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8919,21 +8919,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>732290</v>
+        <v>732297</v>
       </c>
       <c r="R80" t="n">
-        <v>7457046</v>
+        <v>7457098</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8979,6 +8979,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9005,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338664</v>
+        <v>121338670</v>
       </c>
       <c r="B81" t="n">
-        <v>57367</v>
+        <v>97055</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9017,25 +9022,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9045,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733274</v>
+        <v>732725</v>
       </c>
       <c r="R81" t="n">
-        <v>7456913</v>
+        <v>7457530</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9075,12 +9080,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9107,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338663</v>
+        <v>121338662</v>
       </c>
       <c r="B82" t="n">
-        <v>90709</v>
+        <v>97055</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9119,25 +9124,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9147,10 +9152,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733283</v>
+        <v>733321</v>
       </c>
       <c r="R82" t="n">
-        <v>7456886</v>
+        <v>7456889</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9209,10 +9214,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338669</v>
+        <v>121338697</v>
       </c>
       <c r="B83" t="n">
-        <v>56563</v>
+        <v>97055</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9225,21 +9230,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9249,10 +9254,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>732688</v>
+        <v>732290</v>
       </c>
       <c r="R83" t="n">
-        <v>7457404</v>
+        <v>7457046</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9311,10 +9316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338662</v>
+        <v>121338694</v>
       </c>
       <c r="B84" t="n">
-        <v>97054</v>
+        <v>57779</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9323,25 +9328,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>103001</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9351,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733321</v>
+        <v>732301</v>
       </c>
       <c r="R84" t="n">
-        <v>7456889</v>
+        <v>7457166</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9381,12 +9386,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9413,10 +9418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338668</v>
+        <v>121338669</v>
       </c>
       <c r="B85" t="n">
-        <v>90995</v>
+        <v>56563</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9425,25 +9430,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9453,10 +9458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732643</v>
+        <v>732688</v>
       </c>
       <c r="R85" t="n">
-        <v>7457301</v>
+        <v>7457404</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9515,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338695</v>
+        <v>121338634</v>
       </c>
       <c r="B86" t="n">
-        <v>56563</v>
+        <v>90728</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9527,25 +9532,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9555,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732297</v>
+        <v>733192</v>
       </c>
       <c r="R86" t="n">
-        <v>7457098</v>
+        <v>7456971</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9585,17 +9590,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338670</v>
+        <v>121338663</v>
       </c>
       <c r="B87" t="n">
-        <v>97054</v>
+        <v>90710</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9634,25 +9634,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>732725</v>
+        <v>733283</v>
       </c>
       <c r="R87" t="n">
-        <v>7457530</v>
+        <v>7456886</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338634</v>
+        <v>121338664</v>
       </c>
       <c r="B88" t="n">
-        <v>90727</v>
+        <v>57367</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9740,21 +9740,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733192</v>
+        <v>733274</v>
       </c>
       <c r="R88" t="n">
-        <v>7456971</v>
+        <v>7456913</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338719</v>
+        <v>121338700</v>
       </c>
       <c r="B21" t="n">
-        <v>90710</v>
+        <v>97058</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735757</v>
+        <v>735294</v>
       </c>
       <c r="R21" t="n">
-        <v>7459269</v>
+        <v>7459118</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338703</v>
+        <v>121338717</v>
       </c>
       <c r="B22" t="n">
-        <v>97049</v>
+        <v>79717</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735177</v>
+        <v>735799</v>
       </c>
       <c r="R22" t="n">
-        <v>7459280</v>
+        <v>7459254</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338721</v>
+        <v>121338718</v>
       </c>
       <c r="B23" t="n">
-        <v>97049</v>
+        <v>90731</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2996,25 +2996,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735756</v>
+        <v>735749</v>
       </c>
       <c r="R23" t="n">
-        <v>7459178</v>
+        <v>7459256</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338717</v>
+        <v>121338716</v>
       </c>
       <c r="B24" t="n">
-        <v>79714</v>
+        <v>79717</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735799</v>
+        <v>735787</v>
       </c>
       <c r="R24" t="n">
-        <v>7459254</v>
+        <v>7459247</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338712</v>
+        <v>121338701</v>
       </c>
       <c r="B25" t="n">
-        <v>97049</v>
+        <v>91989</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735645</v>
+        <v>735254</v>
       </c>
       <c r="R25" t="n">
-        <v>7459290</v>
+        <v>7459137</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338700</v>
+        <v>121338699</v>
       </c>
       <c r="B26" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735294</v>
+        <v>735424</v>
       </c>
       <c r="R26" t="n">
-        <v>7459118</v>
+        <v>7459188</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338718</v>
+        <v>121338704</v>
       </c>
       <c r="B27" t="n">
-        <v>90728</v>
+        <v>91983</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735749</v>
+        <v>735170</v>
       </c>
       <c r="R27" t="n">
-        <v>7459256</v>
+        <v>7459303</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338704</v>
+        <v>121338712</v>
       </c>
       <c r="B28" t="n">
-        <v>91980</v>
+        <v>97052</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,25 +3506,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735170</v>
+        <v>735645</v>
       </c>
       <c r="R28" t="n">
-        <v>7459303</v>
+        <v>7459290</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338702</v>
+        <v>121338703</v>
       </c>
       <c r="B29" t="n">
-        <v>91978</v>
+        <v>97052</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3608,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735224</v>
+        <v>735177</v>
       </c>
       <c r="R29" t="n">
-        <v>7459176</v>
+        <v>7459280</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338701</v>
+        <v>121338719</v>
       </c>
       <c r="B30" t="n">
-        <v>91986</v>
+        <v>90713</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,25 +3710,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735254</v>
+        <v>735757</v>
       </c>
       <c r="R30" t="n">
-        <v>7459137</v>
+        <v>7459269</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338699</v>
+        <v>121338702</v>
       </c>
       <c r="B31" t="n">
-        <v>97055</v>
+        <v>91981</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735424</v>
+        <v>735224</v>
       </c>
       <c r="R31" t="n">
-        <v>7459188</v>
+        <v>7459176</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338716</v>
+        <v>121338721</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>97052</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735787</v>
+        <v>735756</v>
       </c>
       <c r="R32" t="n">
-        <v>7459247</v>
+        <v>7459178</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338674</v>
+        <v>121338676</v>
       </c>
       <c r="B34" t="n">
-        <v>100334</v>
+        <v>97052</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732485</v>
+        <v>732460</v>
       </c>
       <c r="R34" t="n">
-        <v>7457959</v>
+        <v>7457939</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4211,7 +4211,7 @@
         <v>121338672</v>
       </c>
       <c r="B35" t="n">
-        <v>57785</v>
+        <v>57788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338671</v>
+        <v>121338675</v>
       </c>
       <c r="B36" t="n">
-        <v>56555</v>
+        <v>100337</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732502</v>
+        <v>732485</v>
       </c>
       <c r="R36" t="n">
-        <v>7457961</v>
+        <v>7457959</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4386,6 +4386,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4412,10 +4417,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338676</v>
+        <v>121338671</v>
       </c>
       <c r="B37" t="n">
-        <v>97049</v>
+        <v>56558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,25 +4429,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4457,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732460</v>
+        <v>732502</v>
       </c>
       <c r="R37" t="n">
-        <v>7457939</v>
+        <v>7457961</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4932,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338690</v>
+        <v>121338689</v>
       </c>
       <c r="B42" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4953,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4975,7 +4980,7 @@
         <v>731977</v>
       </c>
       <c r="R42" t="n">
-        <v>7457791</v>
+        <v>7457792</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5034,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338692</v>
+        <v>121338686</v>
       </c>
       <c r="B43" t="n">
-        <v>57351</v>
+        <v>57782</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5050,21 +5055,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5074,10 +5079,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>732035</v>
+        <v>731797</v>
       </c>
       <c r="R43" t="n">
-        <v>7457821</v>
+        <v>7457819</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5136,10 +5141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338689</v>
+        <v>121338687</v>
       </c>
       <c r="B44" t="n">
-        <v>90710</v>
+        <v>97052</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5148,25 +5153,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5176,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731977</v>
+        <v>731849</v>
       </c>
       <c r="R44" t="n">
-        <v>7457792</v>
+        <v>7457769</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5238,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338691</v>
+        <v>121338690</v>
       </c>
       <c r="B45" t="n">
-        <v>90728</v>
+        <v>90999</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5259,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5283,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732025</v>
+        <v>731977</v>
       </c>
       <c r="R45" t="n">
-        <v>7457818</v>
+        <v>7457791</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5340,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338686</v>
+        <v>121338692</v>
       </c>
       <c r="B46" t="n">
-        <v>57779</v>
+        <v>57354</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5361,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731797</v>
+        <v>732035</v>
       </c>
       <c r="R46" t="n">
-        <v>7457819</v>
+        <v>7457821</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5442,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338687</v>
+        <v>121338691</v>
       </c>
       <c r="B47" t="n">
-        <v>97049</v>
+        <v>90731</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5454,25 +5459,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731849</v>
+        <v>732025</v>
       </c>
       <c r="R47" t="n">
-        <v>7457769</v>
+        <v>7457818</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8699,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338665</v>
+        <v>121338694</v>
       </c>
       <c r="B78" t="n">
-        <v>90710</v>
+        <v>57782</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8715,21 +8720,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733143</v>
+        <v>732301</v>
       </c>
       <c r="R78" t="n">
-        <v>7456923</v>
+        <v>7457166</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8769,12 +8774,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8801,10 +8806,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338668</v>
+        <v>121338670</v>
       </c>
       <c r="B79" t="n">
-        <v>90996</v>
+        <v>97058</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8813,25 +8818,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8841,10 +8846,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>732643</v>
+        <v>732725</v>
       </c>
       <c r="R79" t="n">
-        <v>7457301</v>
+        <v>7457530</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8903,10 +8908,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338695</v>
+        <v>121338668</v>
       </c>
       <c r="B80" t="n">
-        <v>56563</v>
+        <v>90999</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8915,25 +8920,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>732297</v>
+        <v>732643</v>
       </c>
       <c r="R80" t="n">
-        <v>7457098</v>
+        <v>7457301</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8979,11 +8984,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9010,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338670</v>
+        <v>121338664</v>
       </c>
       <c r="B81" t="n">
-        <v>97055</v>
+        <v>57370</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9022,25 +9022,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>732725</v>
+        <v>733274</v>
       </c>
       <c r="R81" t="n">
-        <v>7457530</v>
+        <v>7456913</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9112,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338662</v>
+        <v>121338669</v>
       </c>
       <c r="B82" t="n">
-        <v>97055</v>
+        <v>56566</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9128,21 +9128,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733321</v>
+        <v>732688</v>
       </c>
       <c r="R82" t="n">
-        <v>7456889</v>
+        <v>7457404</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9217,7 +9217,7 @@
         <v>121338697</v>
       </c>
       <c r="B83" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9316,10 +9316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338694</v>
+        <v>121338662</v>
       </c>
       <c r="B84" t="n">
-        <v>57779</v>
+        <v>97058</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9328,25 +9328,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103001</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732301</v>
+        <v>733321</v>
       </c>
       <c r="R84" t="n">
-        <v>7457166</v>
+        <v>7456889</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9386,12 +9386,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9418,10 +9418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338669</v>
+        <v>121338665</v>
       </c>
       <c r="B85" t="n">
-        <v>56563</v>
+        <v>90713</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9430,25 +9430,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9458,10 +9458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732688</v>
+        <v>733143</v>
       </c>
       <c r="R85" t="n">
-        <v>7457404</v>
+        <v>7456923</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9488,12 +9488,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9520,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338634</v>
+        <v>121338695</v>
       </c>
       <c r="B86" t="n">
-        <v>90728</v>
+        <v>56566</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9532,25 +9532,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733192</v>
+        <v>732297</v>
       </c>
       <c r="R86" t="n">
-        <v>7456971</v>
+        <v>7457098</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9590,12 +9590,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338663</v>
+        <v>121338634</v>
       </c>
       <c r="B87" t="n">
-        <v>90710</v>
+        <v>90731</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9638,21 +9643,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9667,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733283</v>
+        <v>733192</v>
       </c>
       <c r="R87" t="n">
-        <v>7456886</v>
+        <v>7456971</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9724,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338664</v>
+        <v>121338663</v>
       </c>
       <c r="B88" t="n">
-        <v>57367</v>
+        <v>90713</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9740,21 +9745,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9769,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733274</v>
+        <v>733283</v>
       </c>
       <c r="R88" t="n">
-        <v>7456913</v>
+        <v>7456886</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338700</v>
+        <v>121338702</v>
       </c>
       <c r="B21" t="n">
-        <v>97058</v>
+        <v>91981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735294</v>
+        <v>735224</v>
       </c>
       <c r="R21" t="n">
-        <v>7459118</v>
+        <v>7459176</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338717</v>
+        <v>121338703</v>
       </c>
       <c r="B22" t="n">
-        <v>79717</v>
+        <v>97052</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735799</v>
+        <v>735177</v>
       </c>
       <c r="R22" t="n">
-        <v>7459254</v>
+        <v>7459280</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338716</v>
+        <v>121338721</v>
       </c>
       <c r="B24" t="n">
-        <v>79717</v>
+        <v>97052</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,21 +3102,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735787</v>
+        <v>735756</v>
       </c>
       <c r="R24" t="n">
-        <v>7459247</v>
+        <v>7459178</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338701</v>
+        <v>121338700</v>
       </c>
       <c r="B25" t="n">
-        <v>91989</v>
+        <v>97058</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735254</v>
+        <v>735294</v>
       </c>
       <c r="R25" t="n">
-        <v>7459137</v>
+        <v>7459118</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338699</v>
+        <v>121338704</v>
       </c>
       <c r="B26" t="n">
-        <v>97058</v>
+        <v>91983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735424</v>
+        <v>735170</v>
       </c>
       <c r="R26" t="n">
-        <v>7459188</v>
+        <v>7459303</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338704</v>
+        <v>121338717</v>
       </c>
       <c r="B27" t="n">
-        <v>91983</v>
+        <v>79717</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735170</v>
+        <v>735799</v>
       </c>
       <c r="R27" t="n">
-        <v>7459303</v>
+        <v>7459254</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338703</v>
+        <v>121338701</v>
       </c>
       <c r="B29" t="n">
-        <v>97052</v>
+        <v>91989</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735177</v>
+        <v>735254</v>
       </c>
       <c r="R29" t="n">
-        <v>7459280</v>
+        <v>7459137</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338719</v>
+        <v>121338699</v>
       </c>
       <c r="B30" t="n">
-        <v>90713</v>
+        <v>97058</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,25 +3710,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735757</v>
+        <v>735424</v>
       </c>
       <c r="R30" t="n">
-        <v>7459269</v>
+        <v>7459188</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338702</v>
+        <v>121338719</v>
       </c>
       <c r="B31" t="n">
-        <v>91981</v>
+        <v>90713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735224</v>
+        <v>735757</v>
       </c>
       <c r="R31" t="n">
-        <v>7459176</v>
+        <v>7459269</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338721</v>
+        <v>121338716</v>
       </c>
       <c r="B32" t="n">
-        <v>97052</v>
+        <v>79717</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735756</v>
+        <v>735787</v>
       </c>
       <c r="R32" t="n">
-        <v>7459178</v>
+        <v>7459247</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338676</v>
+        <v>121338675</v>
       </c>
       <c r="B34" t="n">
-        <v>97052</v>
+        <v>100337</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732460</v>
+        <v>732485</v>
       </c>
       <c r="R34" t="n">
-        <v>7457939</v>
+        <v>7457959</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4182,6 +4182,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4208,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338672</v>
+        <v>121338676</v>
       </c>
       <c r="B35" t="n">
-        <v>57788</v>
+        <v>97052</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4220,25 +4225,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102999</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4248,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732533</v>
+        <v>732460</v>
       </c>
       <c r="R35" t="n">
-        <v>7457997</v>
+        <v>7457939</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4310,10 +4315,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338675</v>
+        <v>121338672</v>
       </c>
       <c r="B36" t="n">
-        <v>100337</v>
+        <v>57788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4327,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>102999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4355,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732485</v>
+        <v>732533</v>
       </c>
       <c r="R36" t="n">
-        <v>7457959</v>
+        <v>7457997</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4386,11 +4391,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>1 m2</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4937,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338689</v>
+        <v>121338687</v>
       </c>
       <c r="B42" t="n">
-        <v>90713</v>
+        <v>97052</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4949,25 +4949,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731977</v>
+        <v>731849</v>
       </c>
       <c r="R42" t="n">
-        <v>7457792</v>
+        <v>7457769</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338686</v>
+        <v>121338689</v>
       </c>
       <c r="B43" t="n">
-        <v>57782</v>
+        <v>90713</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5055,21 +5055,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5079,10 +5079,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>731797</v>
+        <v>731977</v>
       </c>
       <c r="R43" t="n">
-        <v>7457819</v>
+        <v>7457792</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5141,10 +5141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338687</v>
+        <v>121338690</v>
       </c>
       <c r="B44" t="n">
-        <v>97052</v>
+        <v>90999</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,25 +5153,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731849</v>
+        <v>731977</v>
       </c>
       <c r="R44" t="n">
-        <v>7457769</v>
+        <v>7457791</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338690</v>
+        <v>121338692</v>
       </c>
       <c r="B45" t="n">
-        <v>90999</v>
+        <v>57354</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731977</v>
+        <v>732035</v>
       </c>
       <c r="R45" t="n">
-        <v>7457791</v>
+        <v>7457821</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338692</v>
+        <v>121338686</v>
       </c>
       <c r="B46" t="n">
-        <v>57354</v>
+        <v>57782</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5361,21 +5361,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732035</v>
+        <v>731797</v>
       </c>
       <c r="R46" t="n">
-        <v>7457821</v>
+        <v>7457819</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338694</v>
+        <v>121338663</v>
       </c>
       <c r="B78" t="n">
-        <v>57782</v>
+        <v>90713</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>732301</v>
+        <v>733283</v>
       </c>
       <c r="R78" t="n">
-        <v>7457166</v>
+        <v>7456886</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8908,10 +8908,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338668</v>
+        <v>121338694</v>
       </c>
       <c r="B80" t="n">
-        <v>90999</v>
+        <v>57782</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8924,21 +8924,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>103001</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>732643</v>
+        <v>732301</v>
       </c>
       <c r="R80" t="n">
-        <v>7457301</v>
+        <v>7457166</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338664</v>
+        <v>121338695</v>
       </c>
       <c r="B81" t="n">
-        <v>57370</v>
+        <v>56566</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9022,25 +9022,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733274</v>
+        <v>732297</v>
       </c>
       <c r="R81" t="n">
-        <v>7456913</v>
+        <v>7457098</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9080,12 +9080,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9112,10 +9117,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338669</v>
+        <v>121338634</v>
       </c>
       <c r="B82" t="n">
-        <v>56566</v>
+        <v>90731</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9124,25 +9129,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9152,10 +9157,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732688</v>
+        <v>733192</v>
       </c>
       <c r="R82" t="n">
-        <v>7457404</v>
+        <v>7456971</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9182,12 +9187,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9316,10 +9321,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338662</v>
+        <v>121338665</v>
       </c>
       <c r="B84" t="n">
-        <v>97058</v>
+        <v>90713</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9328,25 +9333,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9356,10 +9361,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733321</v>
+        <v>733143</v>
       </c>
       <c r="R84" t="n">
-        <v>7456889</v>
+        <v>7456923</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9418,10 +9423,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338665</v>
+        <v>121338662</v>
       </c>
       <c r="B85" t="n">
-        <v>90713</v>
+        <v>97058</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9430,25 +9435,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9458,10 +9463,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733143</v>
+        <v>733321</v>
       </c>
       <c r="R85" t="n">
-        <v>7456923</v>
+        <v>7456889</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9520,10 +9525,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338695</v>
+        <v>121338668</v>
       </c>
       <c r="B86" t="n">
-        <v>56566</v>
+        <v>90999</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9532,25 +9537,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9565,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732297</v>
+        <v>732643</v>
       </c>
       <c r="R86" t="n">
-        <v>7457098</v>
+        <v>7457301</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9596,11 +9601,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9627,10 +9627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338634</v>
+        <v>121338664</v>
       </c>
       <c r="B87" t="n">
-        <v>90731</v>
+        <v>57370</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9643,21 +9643,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733192</v>
+        <v>733274</v>
       </c>
       <c r="R87" t="n">
-        <v>7456971</v>
+        <v>7456913</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9729,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338663</v>
+        <v>121338669</v>
       </c>
       <c r="B88" t="n">
-        <v>90713</v>
+        <v>56566</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9741,25 +9741,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9769,10 +9769,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733283</v>
+        <v>732688</v>
       </c>
       <c r="R88" t="n">
-        <v>7456886</v>
+        <v>7457404</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -9627,10 +9627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338664</v>
+        <v>121338669</v>
       </c>
       <c r="B87" t="n">
-        <v>57370</v>
+        <v>56566</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9639,25 +9639,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733274</v>
+        <v>732688</v>
       </c>
       <c r="R87" t="n">
-        <v>7456913</v>
+        <v>7457404</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9697,12 +9697,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9729,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338669</v>
+        <v>121338664</v>
       </c>
       <c r="B88" t="n">
-        <v>56566</v>
+        <v>57370</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9741,25 +9741,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9769,10 +9769,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732688</v>
+        <v>733274</v>
       </c>
       <c r="R88" t="n">
-        <v>7457404</v>
+        <v>7456913</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -9627,10 +9627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338669</v>
+        <v>121338664</v>
       </c>
       <c r="B87" t="n">
-        <v>56566</v>
+        <v>57370</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9639,25 +9639,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>732688</v>
+        <v>733274</v>
       </c>
       <c r="R87" t="n">
-        <v>7457404</v>
+        <v>7456913</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9697,12 +9697,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9729,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338664</v>
+        <v>121338669</v>
       </c>
       <c r="B88" t="n">
-        <v>57370</v>
+        <v>56566</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9741,25 +9741,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9769,10 +9769,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>733274</v>
+        <v>732688</v>
       </c>
       <c r="R88" t="n">
-        <v>7456913</v>
+        <v>7457404</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2783,7 +2783,7 @@
         <v>121338702</v>
       </c>
       <c r="B21" t="n">
-        <v>91981</v>
+        <v>91987</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338703</v>
+        <v>121338719</v>
       </c>
       <c r="B22" t="n">
-        <v>97052</v>
+        <v>90719</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735177</v>
+        <v>735757</v>
       </c>
       <c r="R22" t="n">
-        <v>7459280</v>
+        <v>7459269</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338718</v>
+        <v>121338717</v>
       </c>
       <c r="B23" t="n">
-        <v>90731</v>
+        <v>79718</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2996,25 +2996,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735749</v>
+        <v>735799</v>
       </c>
       <c r="R23" t="n">
-        <v>7459256</v>
+        <v>7459254</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338721</v>
+        <v>121338701</v>
       </c>
       <c r="B24" t="n">
-        <v>97052</v>
+        <v>91995</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,21 +3102,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735756</v>
+        <v>735254</v>
       </c>
       <c r="R24" t="n">
-        <v>7459178</v>
+        <v>7459137</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338700</v>
+        <v>121338704</v>
       </c>
       <c r="B25" t="n">
-        <v>97058</v>
+        <v>91989</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735294</v>
+        <v>735170</v>
       </c>
       <c r="R25" t="n">
-        <v>7459118</v>
+        <v>7459303</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338704</v>
+        <v>121338703</v>
       </c>
       <c r="B26" t="n">
-        <v>91983</v>
+        <v>97058</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735170</v>
+        <v>735177</v>
       </c>
       <c r="R26" t="n">
-        <v>7459303</v>
+        <v>7459280</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338717</v>
+        <v>121338700</v>
       </c>
       <c r="B27" t="n">
-        <v>79717</v>
+        <v>97064</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735799</v>
+        <v>735294</v>
       </c>
       <c r="R27" t="n">
-        <v>7459254</v>
+        <v>7459118</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338712</v>
+        <v>121338699</v>
       </c>
       <c r="B28" t="n">
-        <v>97052</v>
+        <v>97064</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735645</v>
+        <v>735424</v>
       </c>
       <c r="R28" t="n">
-        <v>7459290</v>
+        <v>7459188</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338701</v>
+        <v>121338712</v>
       </c>
       <c r="B29" t="n">
-        <v>91989</v>
+        <v>97058</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735254</v>
+        <v>735645</v>
       </c>
       <c r="R29" t="n">
-        <v>7459137</v>
+        <v>7459290</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338699</v>
+        <v>121338716</v>
       </c>
       <c r="B30" t="n">
-        <v>97058</v>
+        <v>79718</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735424</v>
+        <v>735787</v>
       </c>
       <c r="R30" t="n">
-        <v>7459188</v>
+        <v>7459247</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338719</v>
+        <v>121338718</v>
       </c>
       <c r="B31" t="n">
-        <v>90713</v>
+        <v>90737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735757</v>
+        <v>735749</v>
       </c>
       <c r="R31" t="n">
-        <v>7459269</v>
+        <v>7459256</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338716</v>
+        <v>121338721</v>
       </c>
       <c r="B32" t="n">
-        <v>79717</v>
+        <v>97058</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735787</v>
+        <v>735756</v>
       </c>
       <c r="R32" t="n">
-        <v>7459247</v>
+        <v>7459178</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338675</v>
+        <v>121338676</v>
       </c>
       <c r="B34" t="n">
-        <v>100337</v>
+        <v>97058</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732485</v>
+        <v>732460</v>
       </c>
       <c r="R34" t="n">
-        <v>7457959</v>
+        <v>7457939</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4182,11 +4182,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 m2</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338676</v>
+        <v>121338675</v>
       </c>
       <c r="B35" t="n">
-        <v>97052</v>
+        <v>100343</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4224,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732460</v>
+        <v>732485</v>
       </c>
       <c r="R35" t="n">
-        <v>7457939</v>
+        <v>7457959</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4289,6 +4284,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,7 +4318,7 @@
         <v>121338672</v>
       </c>
       <c r="B36" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>121338671</v>
       </c>
       <c r="B37" t="n">
-        <v>56558</v>
+        <v>56559</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338687</v>
+        <v>121338686</v>
       </c>
       <c r="B42" t="n">
-        <v>97052</v>
+        <v>57783</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4949,25 +4949,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731849</v>
+        <v>731797</v>
       </c>
       <c r="R42" t="n">
-        <v>7457769</v>
+        <v>7457819</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338689</v>
+        <v>121338690</v>
       </c>
       <c r="B43" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5055,21 +5055,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5082,7 +5082,7 @@
         <v>731977</v>
       </c>
       <c r="R43" t="n">
-        <v>7457792</v>
+        <v>7457791</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5141,10 +5141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338690</v>
+        <v>121338687</v>
       </c>
       <c r="B44" t="n">
-        <v>90999</v>
+        <v>97058</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,25 +5153,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731977</v>
+        <v>731849</v>
       </c>
       <c r="R44" t="n">
-        <v>7457791</v>
+        <v>7457769</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338692</v>
+        <v>121338689</v>
       </c>
       <c r="B45" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5259,21 +5259,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732035</v>
+        <v>731977</v>
       </c>
       <c r="R45" t="n">
-        <v>7457821</v>
+        <v>7457792</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338686</v>
+        <v>121338691</v>
       </c>
       <c r="B46" t="n">
-        <v>57782</v>
+        <v>90737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5361,21 +5361,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731797</v>
+        <v>732025</v>
       </c>
       <c r="R46" t="n">
-        <v>7457819</v>
+        <v>7457818</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338691</v>
+        <v>121338692</v>
       </c>
       <c r="B47" t="n">
-        <v>90731</v>
+        <v>57355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732025</v>
+        <v>732035</v>
       </c>
       <c r="R47" t="n">
-        <v>7457818</v>
+        <v>7457821</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338663</v>
+        <v>121338662</v>
       </c>
       <c r="B78" t="n">
-        <v>90713</v>
+        <v>97064</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8716,25 +8716,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733283</v>
+        <v>733321</v>
       </c>
       <c r="R78" t="n">
-        <v>7456886</v>
+        <v>7456889</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8806,10 +8806,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338670</v>
+        <v>121338669</v>
       </c>
       <c r="B79" t="n">
-        <v>97058</v>
+        <v>56567</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8822,21 +8822,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>732725</v>
+        <v>732688</v>
       </c>
       <c r="R79" t="n">
-        <v>7457530</v>
+        <v>7457404</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8908,10 +8908,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338694</v>
+        <v>121338663</v>
       </c>
       <c r="B80" t="n">
-        <v>57782</v>
+        <v>90719</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8924,21 +8924,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>732301</v>
+        <v>733283</v>
       </c>
       <c r="R80" t="n">
-        <v>7457166</v>
+        <v>7456886</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9010,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338695</v>
+        <v>121338634</v>
       </c>
       <c r="B81" t="n">
-        <v>56566</v>
+        <v>90737</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9022,25 +9022,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>732297</v>
+        <v>733192</v>
       </c>
       <c r="R81" t="n">
-        <v>7457098</v>
+        <v>7456971</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9080,17 +9080,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9117,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338634</v>
+        <v>121338694</v>
       </c>
       <c r="B82" t="n">
-        <v>90731</v>
+        <v>57783</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9133,21 +9128,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9157,10 +9152,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733192</v>
+        <v>732301</v>
       </c>
       <c r="R82" t="n">
-        <v>7456971</v>
+        <v>7457166</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9187,12 +9182,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9219,10 +9214,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338697</v>
+        <v>121338665</v>
       </c>
       <c r="B83" t="n">
-        <v>97058</v>
+        <v>90719</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9231,25 +9226,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9259,10 +9254,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>732290</v>
+        <v>733143</v>
       </c>
       <c r="R83" t="n">
-        <v>7457046</v>
+        <v>7456923</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9289,12 +9284,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9321,10 +9316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338665</v>
+        <v>121338668</v>
       </c>
       <c r="B84" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9337,21 +9332,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9361,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733143</v>
+        <v>732643</v>
       </c>
       <c r="R84" t="n">
-        <v>7456923</v>
+        <v>7457301</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9391,12 +9386,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9423,10 +9418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338662</v>
+        <v>121338697</v>
       </c>
       <c r="B85" t="n">
-        <v>97058</v>
+        <v>97064</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9463,10 +9458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733321</v>
+        <v>732290</v>
       </c>
       <c r="R85" t="n">
-        <v>7456889</v>
+        <v>7457046</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9493,12 +9488,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9525,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338668</v>
+        <v>121338670</v>
       </c>
       <c r="B86" t="n">
-        <v>90999</v>
+        <v>97064</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9537,25 +9532,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9565,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732643</v>
+        <v>732725</v>
       </c>
       <c r="R86" t="n">
-        <v>7457301</v>
+        <v>7457530</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9630,7 +9625,7 @@
         <v>121338664</v>
       </c>
       <c r="B87" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9729,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338669</v>
+        <v>121338695</v>
       </c>
       <c r="B88" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9769,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732688</v>
+        <v>732297</v>
       </c>
       <c r="R88" t="n">
-        <v>7457404</v>
+        <v>7457098</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9805,6 +9800,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338702</v>
+        <v>121338721</v>
       </c>
       <c r="B21" t="n">
-        <v>91987</v>
+        <v>97059</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735224</v>
+        <v>735756</v>
       </c>
       <c r="R21" t="n">
-        <v>7459176</v>
+        <v>7459178</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338719</v>
+        <v>121338718</v>
       </c>
       <c r="B22" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735757</v>
+        <v>735749</v>
       </c>
       <c r="R22" t="n">
-        <v>7459269</v>
+        <v>7459256</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338717</v>
+        <v>121338719</v>
       </c>
       <c r="B23" t="n">
-        <v>79718</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2996,25 +2996,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735799</v>
+        <v>735757</v>
       </c>
       <c r="R23" t="n">
-        <v>7459254</v>
+        <v>7459269</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338701</v>
+        <v>121338703</v>
       </c>
       <c r="B24" t="n">
-        <v>91995</v>
+        <v>97059</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,21 +3102,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735254</v>
+        <v>735177</v>
       </c>
       <c r="R24" t="n">
-        <v>7459137</v>
+        <v>7459280</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338704</v>
+        <v>121338699</v>
       </c>
       <c r="B25" t="n">
-        <v>91989</v>
+        <v>97065</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735170</v>
+        <v>735424</v>
       </c>
       <c r="R25" t="n">
-        <v>7459303</v>
+        <v>7459188</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338703</v>
+        <v>121338716</v>
       </c>
       <c r="B26" t="n">
-        <v>97058</v>
+        <v>79719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,21 +3306,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735177</v>
+        <v>735787</v>
       </c>
       <c r="R26" t="n">
-        <v>7459280</v>
+        <v>7459247</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338700</v>
+        <v>121338717</v>
       </c>
       <c r="B27" t="n">
-        <v>97064</v>
+        <v>79719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735294</v>
+        <v>735799</v>
       </c>
       <c r="R27" t="n">
-        <v>7459118</v>
+        <v>7459254</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338699</v>
+        <v>121338704</v>
       </c>
       <c r="B28" t="n">
-        <v>97064</v>
+        <v>91990</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,25 +3506,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735424</v>
+        <v>735170</v>
       </c>
       <c r="R28" t="n">
-        <v>7459188</v>
+        <v>7459303</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338712</v>
+        <v>121338700</v>
       </c>
       <c r="B29" t="n">
-        <v>97058</v>
+        <v>97065</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,16 +3612,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735645</v>
+        <v>735294</v>
       </c>
       <c r="R29" t="n">
-        <v>7459290</v>
+        <v>7459118</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338716</v>
+        <v>121338712</v>
       </c>
       <c r="B30" t="n">
-        <v>79718</v>
+        <v>97059</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735787</v>
+        <v>735645</v>
       </c>
       <c r="R30" t="n">
-        <v>7459247</v>
+        <v>7459290</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338718</v>
+        <v>121338701</v>
       </c>
       <c r="B31" t="n">
-        <v>90737</v>
+        <v>91996</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735749</v>
+        <v>735254</v>
       </c>
       <c r="R31" t="n">
-        <v>7459256</v>
+        <v>7459137</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338721</v>
+        <v>121338702</v>
       </c>
       <c r="B32" t="n">
-        <v>97058</v>
+        <v>91988</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735756</v>
+        <v>735224</v>
       </c>
       <c r="R32" t="n">
-        <v>7459178</v>
+        <v>7459176</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338676</v>
+        <v>121338674</v>
       </c>
       <c r="B34" t="n">
-        <v>97058</v>
+        <v>100344</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732460</v>
+        <v>732485</v>
       </c>
       <c r="R34" t="n">
-        <v>7457939</v>
+        <v>7457959</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338675</v>
+        <v>121338671</v>
       </c>
       <c r="B35" t="n">
-        <v>100343</v>
+        <v>56560</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4220,25 +4220,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732485</v>
+        <v>732502</v>
       </c>
       <c r="R35" t="n">
-        <v>7457959</v>
+        <v>7457961</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4284,11 +4284,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 m2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,7 +4313,7 @@
         <v>121338672</v>
       </c>
       <c r="B36" t="n">
-        <v>57789</v>
+        <v>57790</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4417,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338671</v>
+        <v>121338676</v>
       </c>
       <c r="B37" t="n">
-        <v>56559</v>
+        <v>97059</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4429,25 +4424,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4457,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732502</v>
+        <v>732460</v>
       </c>
       <c r="R37" t="n">
-        <v>7457961</v>
+        <v>7457939</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4937,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338686</v>
+        <v>121338691</v>
       </c>
       <c r="B42" t="n">
-        <v>57783</v>
+        <v>90738</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4953,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731797</v>
+        <v>732025</v>
       </c>
       <c r="R42" t="n">
-        <v>7457819</v>
+        <v>7457818</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5039,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338690</v>
+        <v>121338687</v>
       </c>
       <c r="B43" t="n">
-        <v>91005</v>
+        <v>97059</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5051,25 +5046,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5079,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>731977</v>
+        <v>731849</v>
       </c>
       <c r="R43" t="n">
-        <v>7457791</v>
+        <v>7457769</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5141,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338687</v>
+        <v>121338692</v>
       </c>
       <c r="B44" t="n">
-        <v>97058</v>
+        <v>57356</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,25 +5148,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5181,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731849</v>
+        <v>732035</v>
       </c>
       <c r="R44" t="n">
-        <v>7457769</v>
+        <v>7457821</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338689</v>
+        <v>121338690</v>
       </c>
       <c r="B45" t="n">
-        <v>90719</v>
+        <v>91006</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5259,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,7 +5281,7 @@
         <v>731977</v>
       </c>
       <c r="R45" t="n">
-        <v>7457792</v>
+        <v>7457791</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5345,10 +5340,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338691</v>
+        <v>121338686</v>
       </c>
       <c r="B46" t="n">
-        <v>90737</v>
+        <v>57784</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5361,21 +5356,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5385,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732025</v>
+        <v>731797</v>
       </c>
       <c r="R46" t="n">
-        <v>7457818</v>
+        <v>7457819</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5447,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338692</v>
+        <v>121338689</v>
       </c>
       <c r="B47" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,21 +5458,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5482,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732035</v>
+        <v>731977</v>
       </c>
       <c r="R47" t="n">
-        <v>7457821</v>
+        <v>7457792</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8704,10 +8699,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338662</v>
+        <v>121338634</v>
       </c>
       <c r="B78" t="n">
-        <v>97064</v>
+        <v>90738</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8716,25 +8711,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733321</v>
+        <v>733192</v>
       </c>
       <c r="R78" t="n">
-        <v>7456889</v>
+        <v>7456971</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338669</v>
+        <v>121338662</v>
       </c>
       <c r="B79" t="n">
-        <v>56567</v>
+        <v>97065</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8822,21 +8817,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8846,10 +8841,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>732688</v>
+        <v>733321</v>
       </c>
       <c r="R79" t="n">
-        <v>7457404</v>
+        <v>7456889</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8876,12 +8871,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8911,7 +8906,7 @@
         <v>121338663</v>
       </c>
       <c r="B80" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9010,10 +9005,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338634</v>
+        <v>121338664</v>
       </c>
       <c r="B81" t="n">
-        <v>90737</v>
+        <v>57372</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9026,21 +9021,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9045,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733192</v>
+        <v>733274</v>
       </c>
       <c r="R81" t="n">
-        <v>7456971</v>
+        <v>7456913</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9112,10 +9107,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338694</v>
+        <v>121338697</v>
       </c>
       <c r="B82" t="n">
-        <v>57783</v>
+        <v>97065</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9124,25 +9119,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103001</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9152,10 +9147,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732301</v>
+        <v>732290</v>
       </c>
       <c r="R82" t="n">
-        <v>7457166</v>
+        <v>7457046</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9214,10 +9209,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338665</v>
+        <v>121338670</v>
       </c>
       <c r="B83" t="n">
-        <v>90719</v>
+        <v>97065</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9226,25 +9221,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9254,10 +9249,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733143</v>
+        <v>732725</v>
       </c>
       <c r="R83" t="n">
-        <v>7456923</v>
+        <v>7457530</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9284,12 +9279,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9316,10 +9311,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338668</v>
+        <v>121338694</v>
       </c>
       <c r="B84" t="n">
-        <v>91005</v>
+        <v>57784</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9332,21 +9327,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>103001</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9356,10 +9351,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732643</v>
+        <v>732301</v>
       </c>
       <c r="R84" t="n">
-        <v>7457301</v>
+        <v>7457166</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9418,10 +9413,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338697</v>
+        <v>121338665</v>
       </c>
       <c r="B85" t="n">
-        <v>97064</v>
+        <v>90720</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9430,25 +9425,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9458,10 +9453,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732290</v>
+        <v>733143</v>
       </c>
       <c r="R85" t="n">
-        <v>7457046</v>
+        <v>7456923</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9488,12 +9483,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9520,10 +9515,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338670</v>
+        <v>121338695</v>
       </c>
       <c r="B86" t="n">
-        <v>97064</v>
+        <v>56568</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9536,21 +9531,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9555,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732725</v>
+        <v>732297</v>
       </c>
       <c r="R86" t="n">
-        <v>7457530</v>
+        <v>7457098</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9596,6 +9591,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338664</v>
+        <v>121338669</v>
       </c>
       <c r="B87" t="n">
-        <v>57371</v>
+        <v>56568</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9634,25 +9634,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733274</v>
+        <v>732688</v>
       </c>
       <c r="R87" t="n">
-        <v>7456913</v>
+        <v>7457404</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338695</v>
+        <v>121338668</v>
       </c>
       <c r="B88" t="n">
-        <v>56567</v>
+        <v>91006</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9736,25 +9736,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732297</v>
+        <v>732643</v>
       </c>
       <c r="R88" t="n">
-        <v>7457098</v>
+        <v>7457301</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9800,11 +9800,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338721</v>
+        <v>121338718</v>
       </c>
       <c r="B21" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735756</v>
+        <v>735749</v>
       </c>
       <c r="R21" t="n">
-        <v>7459178</v>
+        <v>7459256</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338718</v>
+        <v>121338712</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735749</v>
+        <v>735645</v>
       </c>
       <c r="R22" t="n">
-        <v>7459256</v>
+        <v>7459290</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338719</v>
+        <v>121338704</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>91990</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735757</v>
+        <v>735170</v>
       </c>
       <c r="R23" t="n">
-        <v>7459269</v>
+        <v>7459303</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338703</v>
+        <v>121338701</v>
       </c>
       <c r="B24" t="n">
-        <v>97059</v>
+        <v>91996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,21 +3102,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735177</v>
+        <v>735254</v>
       </c>
       <c r="R24" t="n">
-        <v>7459280</v>
+        <v>7459137</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338699</v>
+        <v>121338700</v>
       </c>
       <c r="B25" t="n">
         <v>97065</v>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735424</v>
+        <v>735294</v>
       </c>
       <c r="R25" t="n">
-        <v>7459188</v>
+        <v>7459118</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338716</v>
+        <v>121338699</v>
       </c>
       <c r="B26" t="n">
-        <v>79719</v>
+        <v>97065</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,21 +3306,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735787</v>
+        <v>735424</v>
       </c>
       <c r="R26" t="n">
-        <v>7459247</v>
+        <v>7459188</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338717</v>
+        <v>121338719</v>
       </c>
       <c r="B27" t="n">
-        <v>79719</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735799</v>
+        <v>735757</v>
       </c>
       <c r="R27" t="n">
-        <v>7459254</v>
+        <v>7459269</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338704</v>
+        <v>121338702</v>
       </c>
       <c r="B28" t="n">
-        <v>91990</v>
+        <v>91988</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735170</v>
+        <v>735224</v>
       </c>
       <c r="R28" t="n">
-        <v>7459303</v>
+        <v>7459176</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338700</v>
+        <v>121338721</v>
       </c>
       <c r="B29" t="n">
-        <v>97065</v>
+        <v>97059</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,16 +3612,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735294</v>
+        <v>735756</v>
       </c>
       <c r="R29" t="n">
-        <v>7459118</v>
+        <v>7459178</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338712</v>
+        <v>121338703</v>
       </c>
       <c r="B30" t="n">
         <v>97059</v>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735645</v>
+        <v>735177</v>
       </c>
       <c r="R30" t="n">
-        <v>7459290</v>
+        <v>7459280</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338701</v>
+        <v>121338717</v>
       </c>
       <c r="B31" t="n">
-        <v>91996</v>
+        <v>79719</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735254</v>
+        <v>735799</v>
       </c>
       <c r="R31" t="n">
-        <v>7459137</v>
+        <v>7459254</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338702</v>
+        <v>121338716</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>79719</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735224</v>
+        <v>735787</v>
       </c>
       <c r="R32" t="n">
-        <v>7459176</v>
+        <v>7459247</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338674</v>
+        <v>121338671</v>
       </c>
       <c r="B34" t="n">
-        <v>100344</v>
+        <v>56560</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732485</v>
+        <v>732502</v>
       </c>
       <c r="R34" t="n">
-        <v>7457959</v>
+        <v>7457961</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338671</v>
+        <v>121338672</v>
       </c>
       <c r="B35" t="n">
-        <v>56560</v>
+        <v>57790</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4224,21 +4224,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>102999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732502</v>
+        <v>732533</v>
       </c>
       <c r="R35" t="n">
-        <v>7457961</v>
+        <v>7457997</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338672</v>
+        <v>121338674</v>
       </c>
       <c r="B36" t="n">
-        <v>57790</v>
+        <v>100344</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102999</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732533</v>
+        <v>732485</v>
       </c>
       <c r="R36" t="n">
-        <v>7457997</v>
+        <v>7457959</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338691</v>
+        <v>121338687</v>
       </c>
       <c r="B42" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4944,25 +4944,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>732025</v>
+        <v>731849</v>
       </c>
       <c r="R42" t="n">
-        <v>7457818</v>
+        <v>7457769</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338687</v>
+        <v>121338691</v>
       </c>
       <c r="B43" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5046,25 +5046,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>731849</v>
+        <v>732025</v>
       </c>
       <c r="R43" t="n">
-        <v>7457769</v>
+        <v>7457818</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5136,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338692</v>
+        <v>121338686</v>
       </c>
       <c r="B44" t="n">
-        <v>57356</v>
+        <v>57784</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5152,21 +5152,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>732035</v>
+        <v>731797</v>
       </c>
       <c r="R44" t="n">
-        <v>7457821</v>
+        <v>7457819</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338690</v>
+        <v>121338692</v>
       </c>
       <c r="B45" t="n">
-        <v>91006</v>
+        <v>57356</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731977</v>
+        <v>732035</v>
       </c>
       <c r="R45" t="n">
-        <v>7457791</v>
+        <v>7457821</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5340,10 +5340,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338686</v>
+        <v>121338689</v>
       </c>
       <c r="B46" t="n">
-        <v>57784</v>
+        <v>90720</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5356,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731797</v>
+        <v>731977</v>
       </c>
       <c r="R46" t="n">
-        <v>7457819</v>
+        <v>7457792</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5442,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338689</v>
+        <v>121338690</v>
       </c>
       <c r="B47" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
         <v>731977</v>
       </c>
       <c r="R47" t="n">
-        <v>7457792</v>
+        <v>7457791</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8699,10 +8699,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338634</v>
+        <v>121338669</v>
       </c>
       <c r="B78" t="n">
-        <v>90738</v>
+        <v>56568</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8711,25 +8711,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733192</v>
+        <v>732688</v>
       </c>
       <c r="R78" t="n">
-        <v>7456971</v>
+        <v>7457404</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8801,10 +8801,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338662</v>
+        <v>121338663</v>
       </c>
       <c r="B79" t="n">
-        <v>97065</v>
+        <v>90720</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8813,25 +8813,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733321</v>
+        <v>733283</v>
       </c>
       <c r="R79" t="n">
-        <v>7456889</v>
+        <v>7456886</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338663</v>
+        <v>121338662</v>
       </c>
       <c r="B80" t="n">
-        <v>90720</v>
+        <v>97065</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8915,25 +8915,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733283</v>
+        <v>733321</v>
       </c>
       <c r="R80" t="n">
-        <v>7456886</v>
+        <v>7456889</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338664</v>
+        <v>121338697</v>
       </c>
       <c r="B81" t="n">
-        <v>57372</v>
+        <v>97065</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9017,25 +9017,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733274</v>
+        <v>732290</v>
       </c>
       <c r="R81" t="n">
-        <v>7456913</v>
+        <v>7457046</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9075,12 +9075,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9107,10 +9107,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338697</v>
+        <v>121338665</v>
       </c>
       <c r="B82" t="n">
-        <v>97065</v>
+        <v>90720</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9119,25 +9119,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732290</v>
+        <v>733143</v>
       </c>
       <c r="R82" t="n">
-        <v>7457046</v>
+        <v>7456923</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9177,12 +9177,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9209,10 +9209,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338670</v>
+        <v>121338664</v>
       </c>
       <c r="B83" t="n">
-        <v>97065</v>
+        <v>57372</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9221,25 +9221,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>732725</v>
+        <v>733274</v>
       </c>
       <c r="R83" t="n">
-        <v>7457530</v>
+        <v>7456913</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9311,10 +9311,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338694</v>
+        <v>121338670</v>
       </c>
       <c r="B84" t="n">
-        <v>57784</v>
+        <v>97065</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9323,25 +9323,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103001</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732301</v>
+        <v>732725</v>
       </c>
       <c r="R84" t="n">
-        <v>7457166</v>
+        <v>7457530</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338665</v>
+        <v>121338694</v>
       </c>
       <c r="B85" t="n">
-        <v>90720</v>
+        <v>57784</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9429,21 +9429,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733143</v>
+        <v>732301</v>
       </c>
       <c r="R85" t="n">
-        <v>7456923</v>
+        <v>7457166</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9515,10 +9515,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338695</v>
+        <v>121338668</v>
       </c>
       <c r="B86" t="n">
-        <v>56568</v>
+        <v>91006</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9527,25 +9527,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732297</v>
+        <v>732643</v>
       </c>
       <c r="R86" t="n">
-        <v>7457098</v>
+        <v>7457301</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9591,11 +9591,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9617,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338669</v>
+        <v>121338634</v>
       </c>
       <c r="B87" t="n">
-        <v>56568</v>
+        <v>90738</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9634,25 +9629,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9657,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>732688</v>
+        <v>733192</v>
       </c>
       <c r="R87" t="n">
-        <v>7457404</v>
+        <v>7456971</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9692,12 +9687,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9724,10 +9719,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338668</v>
+        <v>121338695</v>
       </c>
       <c r="B88" t="n">
-        <v>91006</v>
+        <v>56568</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9736,25 +9731,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9759,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732643</v>
+        <v>732297</v>
       </c>
       <c r="R88" t="n">
-        <v>7457301</v>
+        <v>7457098</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9800,6 +9795,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338718</v>
+        <v>121338712</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735749</v>
+        <v>735645</v>
       </c>
       <c r="R21" t="n">
-        <v>7459256</v>
+        <v>7459290</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338712</v>
+        <v>121338699</v>
       </c>
       <c r="B22" t="n">
-        <v>97059</v>
+        <v>97065</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735645</v>
+        <v>735424</v>
       </c>
       <c r="R22" t="n">
-        <v>7459290</v>
+        <v>7459188</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338704</v>
+        <v>121338718</v>
       </c>
       <c r="B23" t="n">
-        <v>91990</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735170</v>
+        <v>735749</v>
       </c>
       <c r="R23" t="n">
-        <v>7459303</v>
+        <v>7459256</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338700</v>
+        <v>121338704</v>
       </c>
       <c r="B25" t="n">
-        <v>97065</v>
+        <v>91990</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735294</v>
+        <v>735170</v>
       </c>
       <c r="R25" t="n">
-        <v>7459118</v>
+        <v>7459303</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338699</v>
+        <v>121338702</v>
       </c>
       <c r="B26" t="n">
-        <v>97065</v>
+        <v>91988</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735424</v>
+        <v>735224</v>
       </c>
       <c r="R26" t="n">
-        <v>7459188</v>
+        <v>7459176</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338702</v>
+        <v>121338721</v>
       </c>
       <c r="B28" t="n">
-        <v>91988</v>
+        <v>97059</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3506,25 +3506,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735224</v>
+        <v>735756</v>
       </c>
       <c r="R28" t="n">
-        <v>7459176</v>
+        <v>7459178</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338721</v>
+        <v>121338717</v>
       </c>
       <c r="B29" t="n">
-        <v>97059</v>
+        <v>79719</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735756</v>
+        <v>735799</v>
       </c>
       <c r="R29" t="n">
-        <v>7459178</v>
+        <v>7459254</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338717</v>
+        <v>121338700</v>
       </c>
       <c r="B31" t="n">
-        <v>79719</v>
+        <v>97065</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735799</v>
+        <v>735294</v>
       </c>
       <c r="R31" t="n">
-        <v>7459254</v>
+        <v>7459118</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338671</v>
+        <v>121338676</v>
       </c>
       <c r="B34" t="n">
-        <v>56560</v>
+        <v>97059</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732502</v>
+        <v>732460</v>
       </c>
       <c r="R34" t="n">
-        <v>7457961</v>
+        <v>7457939</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338672</v>
+        <v>121338674</v>
       </c>
       <c r="B35" t="n">
-        <v>57790</v>
+        <v>100344</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4220,25 +4220,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102999</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732533</v>
+        <v>732485</v>
       </c>
       <c r="R35" t="n">
-        <v>7457997</v>
+        <v>7457959</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4310,10 +4310,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338674</v>
+        <v>121338672</v>
       </c>
       <c r="B36" t="n">
-        <v>100344</v>
+        <v>57790</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4322,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>102999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732485</v>
+        <v>732533</v>
       </c>
       <c r="R36" t="n">
-        <v>7457959</v>
+        <v>7457997</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4412,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338676</v>
+        <v>121338671</v>
       </c>
       <c r="B37" t="n">
-        <v>97059</v>
+        <v>56560</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4424,25 +4424,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732460</v>
+        <v>732502</v>
       </c>
       <c r="R37" t="n">
-        <v>7457939</v>
+        <v>7457961</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338687</v>
+        <v>121338690</v>
       </c>
       <c r="B42" t="n">
-        <v>97059</v>
+        <v>91006</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4944,25 +4944,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731849</v>
+        <v>731977</v>
       </c>
       <c r="R42" t="n">
-        <v>7457769</v>
+        <v>7457791</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338691</v>
+        <v>121338692</v>
       </c>
       <c r="B43" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5050,21 +5050,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>732025</v>
+        <v>732035</v>
       </c>
       <c r="R43" t="n">
-        <v>7457818</v>
+        <v>7457821</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338692</v>
+        <v>121338687</v>
       </c>
       <c r="B45" t="n">
-        <v>57356</v>
+        <v>97059</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,25 +5250,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732035</v>
+        <v>731849</v>
       </c>
       <c r="R45" t="n">
-        <v>7457821</v>
+        <v>7457769</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5442,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338690</v>
+        <v>121338691</v>
       </c>
       <c r="B47" t="n">
-        <v>91006</v>
+        <v>90738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,21 +5458,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731977</v>
+        <v>732025</v>
       </c>
       <c r="R47" t="n">
-        <v>7457791</v>
+        <v>7457818</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8699,7 +8699,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338669</v>
+        <v>121338695</v>
       </c>
       <c r="B78" t="n">
         <v>56568</v>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>732688</v>
+        <v>732297</v>
       </c>
       <c r="R78" t="n">
-        <v>7457404</v>
+        <v>7457098</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8775,6 +8775,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8801,10 +8806,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338663</v>
+        <v>121338662</v>
       </c>
       <c r="B79" t="n">
-        <v>90720</v>
+        <v>97065</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8813,25 +8818,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8841,10 +8846,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733283</v>
+        <v>733321</v>
       </c>
       <c r="R79" t="n">
-        <v>7456886</v>
+        <v>7456889</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8903,10 +8908,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338662</v>
+        <v>121338634</v>
       </c>
       <c r="B80" t="n">
-        <v>97065</v>
+        <v>90738</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8915,25 +8920,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733321</v>
+        <v>733192</v>
       </c>
       <c r="R80" t="n">
-        <v>7456889</v>
+        <v>7456971</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9005,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338697</v>
+        <v>121338668</v>
       </c>
       <c r="B81" t="n">
-        <v>97065</v>
+        <v>91006</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9017,25 +9022,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9045,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>732290</v>
+        <v>732643</v>
       </c>
       <c r="R81" t="n">
-        <v>7457046</v>
+        <v>7457301</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9107,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338665</v>
+        <v>121338664</v>
       </c>
       <c r="B82" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9123,21 +9128,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9147,10 +9152,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733143</v>
+        <v>733274</v>
       </c>
       <c r="R82" t="n">
-        <v>7456923</v>
+        <v>7456913</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9209,10 +9214,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338664</v>
+        <v>121338670</v>
       </c>
       <c r="B83" t="n">
-        <v>57372</v>
+        <v>97065</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9221,25 +9226,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9249,10 +9254,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733274</v>
+        <v>732725</v>
       </c>
       <c r="R83" t="n">
-        <v>7456913</v>
+        <v>7457530</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9279,12 +9284,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9311,10 +9316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338670</v>
+        <v>121338669</v>
       </c>
       <c r="B84" t="n">
-        <v>97065</v>
+        <v>56568</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9327,21 +9332,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9351,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732725</v>
+        <v>732688</v>
       </c>
       <c r="R84" t="n">
-        <v>7457530</v>
+        <v>7457404</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9413,10 +9418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338694</v>
+        <v>121338663</v>
       </c>
       <c r="B85" t="n">
-        <v>57784</v>
+        <v>90720</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9429,21 +9434,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9453,10 +9458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>732301</v>
+        <v>733283</v>
       </c>
       <c r="R85" t="n">
-        <v>7457166</v>
+        <v>7456886</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9483,12 +9488,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9515,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338668</v>
+        <v>121338694</v>
       </c>
       <c r="B86" t="n">
-        <v>91006</v>
+        <v>57784</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9531,21 +9536,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>103001</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9555,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732643</v>
+        <v>732301</v>
       </c>
       <c r="R86" t="n">
-        <v>7457301</v>
+        <v>7457166</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9617,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338634</v>
+        <v>121338665</v>
       </c>
       <c r="B87" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9633,21 +9638,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9657,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733192</v>
+        <v>733143</v>
       </c>
       <c r="R87" t="n">
-        <v>7456971</v>
+        <v>7456923</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9719,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338695</v>
+        <v>121338697</v>
       </c>
       <c r="B88" t="n">
-        <v>56568</v>
+        <v>97065</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9735,21 +9740,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9759,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732297</v>
+        <v>732290</v>
       </c>
       <c r="R88" t="n">
-        <v>7457098</v>
+        <v>7457046</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9795,11 +9800,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,7 +2780,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338712</v>
+        <v>121338721</v>
       </c>
       <c r="B21" t="n">
         <v>97059</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735645</v>
+        <v>735756</v>
       </c>
       <c r="R21" t="n">
-        <v>7459290</v>
+        <v>7459178</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338699</v>
+        <v>121338703</v>
       </c>
       <c r="B22" t="n">
-        <v>97065</v>
+        <v>97059</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735424</v>
+        <v>735177</v>
       </c>
       <c r="R22" t="n">
-        <v>7459188</v>
+        <v>7459280</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338718</v>
+        <v>121338719</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735749</v>
+        <v>735757</v>
       </c>
       <c r="R23" t="n">
-        <v>7459256</v>
+        <v>7459269</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338701</v>
+        <v>121338704</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>91990</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3098,25 +3098,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735254</v>
+        <v>735170</v>
       </c>
       <c r="R24" t="n">
-        <v>7459137</v>
+        <v>7459303</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338704</v>
+        <v>121338701</v>
       </c>
       <c r="B25" t="n">
-        <v>91990</v>
+        <v>91996</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735170</v>
+        <v>735254</v>
       </c>
       <c r="R25" t="n">
-        <v>7459303</v>
+        <v>7459137</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338702</v>
+        <v>121338716</v>
       </c>
       <c r="B26" t="n">
-        <v>91988</v>
+        <v>79719</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3302,25 +3302,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735224</v>
+        <v>735787</v>
       </c>
       <c r="R26" t="n">
-        <v>7459176</v>
+        <v>7459247</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338719</v>
+        <v>121338717</v>
       </c>
       <c r="B27" t="n">
-        <v>90720</v>
+        <v>79719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735757</v>
+        <v>735799</v>
       </c>
       <c r="R27" t="n">
-        <v>7459269</v>
+        <v>7459254</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338721</v>
+        <v>121338700</v>
       </c>
       <c r="B28" t="n">
-        <v>97059</v>
+        <v>97065</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735756</v>
+        <v>735294</v>
       </c>
       <c r="R28" t="n">
-        <v>7459178</v>
+        <v>7459118</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338717</v>
+        <v>121338718</v>
       </c>
       <c r="B29" t="n">
-        <v>79719</v>
+        <v>90738</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3608,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735799</v>
+        <v>735749</v>
       </c>
       <c r="R29" t="n">
-        <v>7459254</v>
+        <v>7459256</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338703</v>
+        <v>121338712</v>
       </c>
       <c r="B30" t="n">
         <v>97059</v>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735177</v>
+        <v>735645</v>
       </c>
       <c r="R30" t="n">
-        <v>7459280</v>
+        <v>7459290</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,7 +3800,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338700</v>
+        <v>121338699</v>
       </c>
       <c r="B31" t="n">
         <v>97065</v>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735294</v>
+        <v>735424</v>
       </c>
       <c r="R31" t="n">
-        <v>7459118</v>
+        <v>7459188</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338716</v>
+        <v>121338702</v>
       </c>
       <c r="B32" t="n">
-        <v>79719</v>
+        <v>91988</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735787</v>
+        <v>735224</v>
       </c>
       <c r="R32" t="n">
-        <v>7459247</v>
+        <v>7459176</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338676</v>
+        <v>121338671</v>
       </c>
       <c r="B34" t="n">
-        <v>97059</v>
+        <v>56560</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732460</v>
+        <v>732502</v>
       </c>
       <c r="R34" t="n">
-        <v>7457939</v>
+        <v>7457961</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,7 +4208,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338674</v>
+        <v>121338675</v>
       </c>
       <c r="B35" t="n">
         <v>100344</v>
@@ -4284,6 +4284,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4310,10 +4315,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338672</v>
+        <v>121338676</v>
       </c>
       <c r="B36" t="n">
-        <v>57790</v>
+        <v>97059</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4322,25 +4327,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102999</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4350,10 +4355,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732533</v>
+        <v>732460</v>
       </c>
       <c r="R36" t="n">
-        <v>7457997</v>
+        <v>7457939</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4412,10 +4417,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338671</v>
+        <v>121338672</v>
       </c>
       <c r="B37" t="n">
-        <v>56560</v>
+        <v>57790</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4428,21 +4433,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>102999</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4452,10 +4457,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732502</v>
+        <v>732533</v>
       </c>
       <c r="R37" t="n">
-        <v>7457961</v>
+        <v>7457997</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4932,10 +4937,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338690</v>
+        <v>121338692</v>
       </c>
       <c r="B42" t="n">
-        <v>91006</v>
+        <v>57356</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4948,21 +4953,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4972,10 +4977,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731977</v>
+        <v>732035</v>
       </c>
       <c r="R42" t="n">
-        <v>7457791</v>
+        <v>7457821</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5034,10 +5039,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338692</v>
+        <v>121338691</v>
       </c>
       <c r="B43" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5050,21 +5055,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5074,10 +5079,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>732035</v>
+        <v>732025</v>
       </c>
       <c r="R43" t="n">
-        <v>7457821</v>
+        <v>7457818</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5442,10 +5447,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338691</v>
+        <v>121338690</v>
       </c>
       <c r="B47" t="n">
-        <v>90738</v>
+        <v>91006</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,21 +5463,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5482,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>732025</v>
+        <v>731977</v>
       </c>
       <c r="R47" t="n">
-        <v>7457818</v>
+        <v>7457791</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8699,10 +8704,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338695</v>
+        <v>121338665</v>
       </c>
       <c r="B78" t="n">
-        <v>56568</v>
+        <v>90720</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8711,25 +8716,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>732297</v>
+        <v>733143</v>
       </c>
       <c r="R78" t="n">
-        <v>7457098</v>
+        <v>7456923</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8769,17 +8774,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8806,7 +8806,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338662</v>
+        <v>121338697</v>
       </c>
       <c r="B79" t="n">
         <v>97065</v>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>733321</v>
+        <v>732290</v>
       </c>
       <c r="R79" t="n">
-        <v>7456889</v>
+        <v>7457046</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8876,12 +8876,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8908,10 +8908,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338634</v>
+        <v>121338694</v>
       </c>
       <c r="B80" t="n">
-        <v>90738</v>
+        <v>57784</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8924,21 +8924,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733192</v>
+        <v>732301</v>
       </c>
       <c r="R80" t="n">
-        <v>7456971</v>
+        <v>7457166</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9010,10 +9010,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338668</v>
+        <v>121338663</v>
       </c>
       <c r="B81" t="n">
-        <v>91006</v>
+        <v>90720</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9026,21 +9026,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9050,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>732643</v>
+        <v>733283</v>
       </c>
       <c r="R81" t="n">
-        <v>7457301</v>
+        <v>7456886</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9112,10 +9112,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338664</v>
+        <v>121338670</v>
       </c>
       <c r="B82" t="n">
-        <v>57372</v>
+        <v>97065</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9124,25 +9124,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>733274</v>
+        <v>732725</v>
       </c>
       <c r="R82" t="n">
-        <v>7456913</v>
+        <v>7457530</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9214,10 +9214,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338670</v>
+        <v>121338668</v>
       </c>
       <c r="B83" t="n">
-        <v>97065</v>
+        <v>91006</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9226,25 +9226,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>732725</v>
+        <v>732643</v>
       </c>
       <c r="R83" t="n">
-        <v>7457530</v>
+        <v>7457301</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9316,7 +9316,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338669</v>
+        <v>121338695</v>
       </c>
       <c r="B84" t="n">
         <v>56568</v>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732688</v>
+        <v>732297</v>
       </c>
       <c r="R84" t="n">
-        <v>7457404</v>
+        <v>7457098</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9392,6 +9392,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9418,10 +9423,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338663</v>
+        <v>121338634</v>
       </c>
       <c r="B85" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9434,21 +9439,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9458,10 +9463,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733283</v>
+        <v>733192</v>
       </c>
       <c r="R85" t="n">
-        <v>7456886</v>
+        <v>7456971</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9520,10 +9525,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338694</v>
+        <v>121338664</v>
       </c>
       <c r="B86" t="n">
-        <v>57784</v>
+        <v>57372</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9536,21 +9541,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9560,10 +9565,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>732301</v>
+        <v>733274</v>
       </c>
       <c r="R86" t="n">
-        <v>7457166</v>
+        <v>7456913</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9590,12 +9595,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9622,10 +9627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338665</v>
+        <v>121338662</v>
       </c>
       <c r="B87" t="n">
-        <v>90720</v>
+        <v>97065</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9634,25 +9639,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9662,10 +9667,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733143</v>
+        <v>733321</v>
       </c>
       <c r="R87" t="n">
-        <v>7456923</v>
+        <v>7456889</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9724,10 +9729,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338697</v>
+        <v>121338669</v>
       </c>
       <c r="B88" t="n">
-        <v>97065</v>
+        <v>56568</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9740,21 +9745,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9764,10 +9769,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732290</v>
+        <v>732688</v>
       </c>
       <c r="R88" t="n">
-        <v>7457046</v>
+        <v>7457404</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -9525,10 +9525,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338664</v>
+        <v>121338662</v>
       </c>
       <c r="B86" t="n">
-        <v>57372</v>
+        <v>97065</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9537,25 +9537,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733274</v>
+        <v>733321</v>
       </c>
       <c r="R86" t="n">
-        <v>7456913</v>
+        <v>7456889</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9627,10 +9627,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338662</v>
+        <v>121338664</v>
       </c>
       <c r="B87" t="n">
-        <v>97065</v>
+        <v>57372</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9639,25 +9639,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733321</v>
+        <v>733274</v>
       </c>
       <c r="R87" t="n">
-        <v>7456889</v>
+        <v>7456913</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2780,10 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338721</v>
+        <v>121338719</v>
       </c>
       <c r="B21" t="n">
-        <v>97059</v>
+        <v>90728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,25 +2792,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735756</v>
+        <v>735757</v>
       </c>
       <c r="R21" t="n">
-        <v>7459178</v>
+        <v>7459269</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338703</v>
+        <v>121338716</v>
       </c>
       <c r="B22" t="n">
-        <v>97059</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2898,21 +2898,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735177</v>
+        <v>735787</v>
       </c>
       <c r="R22" t="n">
-        <v>7459280</v>
+        <v>7459247</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338719</v>
+        <v>121338701</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>92004</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2996,25 +2996,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735757</v>
+        <v>735254</v>
       </c>
       <c r="R23" t="n">
-        <v>7459269</v>
+        <v>7459137</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3086,10 +3086,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338704</v>
+        <v>121338718</v>
       </c>
       <c r="B24" t="n">
-        <v>91990</v>
+        <v>90746</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,21 +3102,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735170</v>
+        <v>735749</v>
       </c>
       <c r="R24" t="n">
-        <v>7459303</v>
+        <v>7459256</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338701</v>
+        <v>121338712</v>
       </c>
       <c r="B25" t="n">
-        <v>91996</v>
+        <v>97067</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735254</v>
+        <v>735645</v>
       </c>
       <c r="R25" t="n">
-        <v>7459137</v>
+        <v>7459290</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3290,10 +3290,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338716</v>
+        <v>121338721</v>
       </c>
       <c r="B26" t="n">
-        <v>79719</v>
+        <v>97067</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3306,21 +3306,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735787</v>
+        <v>735756</v>
       </c>
       <c r="R26" t="n">
-        <v>7459247</v>
+        <v>7459178</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338717</v>
+        <v>121338702</v>
       </c>
       <c r="B27" t="n">
-        <v>79719</v>
+        <v>91996</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,25 +3404,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735799</v>
+        <v>735224</v>
       </c>
       <c r="R27" t="n">
-        <v>7459254</v>
+        <v>7459176</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3497,7 +3497,7 @@
         <v>121338700</v>
       </c>
       <c r="B28" t="n">
-        <v>97065</v>
+        <v>97073</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338718</v>
+        <v>121338699</v>
       </c>
       <c r="B29" t="n">
-        <v>90738</v>
+        <v>97073</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,25 +3608,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735749</v>
+        <v>735424</v>
       </c>
       <c r="R29" t="n">
-        <v>7459256</v>
+        <v>7459188</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338712</v>
+        <v>121338717</v>
       </c>
       <c r="B30" t="n">
-        <v>97059</v>
+        <v>79726</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735645</v>
+        <v>735799</v>
       </c>
       <c r="R30" t="n">
-        <v>7459290</v>
+        <v>7459254</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338699</v>
+        <v>121338704</v>
       </c>
       <c r="B31" t="n">
-        <v>97065</v>
+        <v>91998</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3812,25 +3812,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735424</v>
+        <v>735170</v>
       </c>
       <c r="R31" t="n">
-        <v>7459188</v>
+        <v>7459303</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3902,10 +3902,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338702</v>
+        <v>121338703</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>97067</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3914,25 +3914,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735224</v>
+        <v>735177</v>
       </c>
       <c r="R32" t="n">
-        <v>7459176</v>
+        <v>7459280</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338671</v>
+        <v>121338672</v>
       </c>
       <c r="B34" t="n">
-        <v>56560</v>
+        <v>57791</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>102999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732502</v>
+        <v>732533</v>
       </c>
       <c r="R34" t="n">
-        <v>7457961</v>
+        <v>7457997</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338675</v>
+        <v>121338674</v>
       </c>
       <c r="B35" t="n">
-        <v>100344</v>
+        <v>100352</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4284,11 +4284,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 m2</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,7 +4313,7 @@
         <v>121338676</v>
       </c>
       <c r="B36" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4417,10 +4412,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338672</v>
+        <v>121338671</v>
       </c>
       <c r="B37" t="n">
-        <v>57790</v>
+        <v>56561</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4433,21 +4428,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102999</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4457,10 +4452,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732533</v>
+        <v>732502</v>
       </c>
       <c r="R37" t="n">
-        <v>7457997</v>
+        <v>7457961</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4937,10 +4932,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338692</v>
+        <v>121338690</v>
       </c>
       <c r="B42" t="n">
-        <v>57356</v>
+        <v>91014</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4953,21 +4948,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>732035</v>
+        <v>731977</v>
       </c>
       <c r="R42" t="n">
-        <v>7457821</v>
+        <v>7457791</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5039,10 +5034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338691</v>
+        <v>121338687</v>
       </c>
       <c r="B43" t="n">
-        <v>90738</v>
+        <v>97067</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5051,25 +5046,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5079,10 +5074,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>732025</v>
+        <v>731849</v>
       </c>
       <c r="R43" t="n">
-        <v>7457818</v>
+        <v>7457769</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5141,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338686</v>
+        <v>121338691</v>
       </c>
       <c r="B44" t="n">
-        <v>57784</v>
+        <v>90746</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5157,21 +5152,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5181,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731797</v>
+        <v>732025</v>
       </c>
       <c r="R44" t="n">
-        <v>7457819</v>
+        <v>7457818</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5243,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338687</v>
+        <v>121338692</v>
       </c>
       <c r="B45" t="n">
-        <v>97059</v>
+        <v>57357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,25 +5250,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5283,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731849</v>
+        <v>732035</v>
       </c>
       <c r="R45" t="n">
-        <v>7457769</v>
+        <v>7457821</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5348,7 +5343,7 @@
         <v>121338689</v>
       </c>
       <c r="B46" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5447,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338690</v>
+        <v>121338686</v>
       </c>
       <c r="B47" t="n">
-        <v>91006</v>
+        <v>57785</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5463,21 +5458,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>103001</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5482,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731977</v>
+        <v>731797</v>
       </c>
       <c r="R47" t="n">
-        <v>7457791</v>
+        <v>7457819</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -8704,10 +8699,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338665</v>
+        <v>121338697</v>
       </c>
       <c r="B78" t="n">
-        <v>90720</v>
+        <v>97073</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8716,25 +8711,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>733143</v>
+        <v>732290</v>
       </c>
       <c r="R78" t="n">
-        <v>7456923</v>
+        <v>7457046</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8774,12 +8769,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8806,10 +8801,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338697</v>
+        <v>121338664</v>
       </c>
       <c r="B79" t="n">
-        <v>97065</v>
+        <v>57373</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8818,25 +8813,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8846,10 +8841,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>732290</v>
+        <v>733274</v>
       </c>
       <c r="R79" t="n">
-        <v>7457046</v>
+        <v>7456913</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8876,12 +8871,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8908,10 +8903,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338694</v>
+        <v>121338634</v>
       </c>
       <c r="B80" t="n">
-        <v>57784</v>
+        <v>90746</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8924,21 +8919,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>732301</v>
+        <v>733192</v>
       </c>
       <c r="R80" t="n">
-        <v>7457166</v>
+        <v>7456971</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8978,12 +8973,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9010,10 +9005,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338663</v>
+        <v>121338670</v>
       </c>
       <c r="B81" t="n">
-        <v>90720</v>
+        <v>97073</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9022,25 +9017,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9050,10 +9045,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>733283</v>
+        <v>732725</v>
       </c>
       <c r="R81" t="n">
-        <v>7456886</v>
+        <v>7457530</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9080,12 +9075,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9112,10 +9107,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338670</v>
+        <v>121338695</v>
       </c>
       <c r="B82" t="n">
-        <v>97065</v>
+        <v>56569</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9128,21 +9123,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9152,10 +9147,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732725</v>
+        <v>732297</v>
       </c>
       <c r="R82" t="n">
-        <v>7457530</v>
+        <v>7457098</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9188,6 +9183,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9217,7 +9217,7 @@
         <v>121338668</v>
       </c>
       <c r="B83" t="n">
-        <v>91006</v>
+        <v>91014</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9316,10 +9316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338695</v>
+        <v>121338669</v>
       </c>
       <c r="B84" t="n">
-        <v>56568</v>
+        <v>56569</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>732297</v>
+        <v>732688</v>
       </c>
       <c r="R84" t="n">
-        <v>7457098</v>
+        <v>7457404</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9392,11 +9392,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Tjädertupp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9423,10 +9418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338634</v>
+        <v>121338665</v>
       </c>
       <c r="B85" t="n">
-        <v>90738</v>
+        <v>90728</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9439,21 +9434,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9463,10 +9458,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733192</v>
+        <v>733143</v>
       </c>
       <c r="R85" t="n">
-        <v>7456971</v>
+        <v>7456923</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9525,10 +9520,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338662</v>
+        <v>121338663</v>
       </c>
       <c r="B86" t="n">
-        <v>97065</v>
+        <v>90728</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9537,25 +9532,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9565,10 +9560,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733321</v>
+        <v>733283</v>
       </c>
       <c r="R86" t="n">
-        <v>7456889</v>
+        <v>7456886</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9627,10 +9622,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338664</v>
+        <v>121338694</v>
       </c>
       <c r="B87" t="n">
-        <v>57372</v>
+        <v>57785</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9643,21 +9638,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9667,10 +9662,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>733274</v>
+        <v>732301</v>
       </c>
       <c r="R87" t="n">
-        <v>7456913</v>
+        <v>7457166</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9697,12 +9692,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9729,10 +9724,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338669</v>
+        <v>121338662</v>
       </c>
       <c r="B88" t="n">
-        <v>56568</v>
+        <v>97073</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9745,21 +9740,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9769,10 +9764,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732688</v>
+        <v>733321</v>
       </c>
       <c r="R88" t="n">
-        <v>7457404</v>
+        <v>7456889</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9799,12 +9794,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -5238,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338692</v>
+        <v>121338689</v>
       </c>
       <c r="B45" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,21 +5254,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>732035</v>
+        <v>731977</v>
       </c>
       <c r="R45" t="n">
-        <v>7457821</v>
+        <v>7457792</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5340,10 +5340,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338689</v>
+        <v>121338692</v>
       </c>
       <c r="B46" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5356,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731977</v>
+        <v>732035</v>
       </c>
       <c r="R46" t="n">
-        <v>7457792</v>
+        <v>7457821</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120302888</v>
+        <v>121988632</v>
       </c>
       <c r="B33" t="n">
-        <v>56545</v>
+        <v>97073</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4020,37 +4020,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733085</v>
+        <v>735185</v>
       </c>
       <c r="R33" t="n">
-        <v>7458027</v>
+        <v>7459609</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4094,22 +4094,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121338671</v>
+        <v>121988614</v>
       </c>
       <c r="B34" t="n">
-        <v>56561</v>
+        <v>56569</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,41 +4118,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>732502</v>
+        <v>735030</v>
       </c>
       <c r="R34" t="n">
-        <v>7457961</v>
+        <v>7459026</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4176,12 +4176,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4196,22 +4201,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121338675</v>
+        <v>121988625</v>
       </c>
       <c r="B35" t="n">
-        <v>100352</v>
+        <v>97073</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4224,37 +4229,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>732485</v>
+        <v>734707</v>
       </c>
       <c r="R35" t="n">
-        <v>7457959</v>
+        <v>7459457</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4278,17 +4283,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 m2</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,22 +4303,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121338672</v>
+        <v>121988631</v>
       </c>
       <c r="B36" t="n">
-        <v>57791</v>
+        <v>91996</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4331,37 +4331,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102999</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>732533</v>
+        <v>735185</v>
       </c>
       <c r="R36" t="n">
-        <v>7457997</v>
+        <v>7459609</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4385,12 +4385,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4405,22 +4410,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121338676</v>
+        <v>121988630</v>
       </c>
       <c r="B37" t="n">
-        <v>97067</v>
+        <v>91998</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4429,41 +4434,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>732460</v>
+        <v>735177</v>
       </c>
       <c r="R37" t="n">
-        <v>7457939</v>
+        <v>7459602</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4487,12 +4492,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4507,22 +4517,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120302886</v>
+        <v>121988638</v>
       </c>
       <c r="B38" t="n">
-        <v>96960</v>
+        <v>90746</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4531,41 +4541,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733007</v>
+        <v>735553</v>
       </c>
       <c r="R38" t="n">
-        <v>7457822</v>
+        <v>7459238</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4589,12 +4599,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,22 +4624,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120302894</v>
+        <v>121988633</v>
       </c>
       <c r="B39" t="n">
-        <v>79151</v>
+        <v>57357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4637,37 +4652,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>733092</v>
+        <v>735194</v>
       </c>
       <c r="R39" t="n">
-        <v>7457724</v>
+        <v>7459625</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4691,12 +4706,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,22 +4731,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120302893</v>
+        <v>121988618</v>
       </c>
       <c r="B40" t="n">
-        <v>57349</v>
+        <v>56569</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4735,41 +4755,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>732993</v>
+        <v>734513</v>
       </c>
       <c r="R40" t="n">
-        <v>7457764</v>
+        <v>7459096</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4793,17 +4813,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,22 +4838,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120302892</v>
+        <v>121988629</v>
       </c>
       <c r="B41" t="n">
-        <v>56537</v>
+        <v>97073</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4842,41 +4862,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>732912</v>
+        <v>735177</v>
       </c>
       <c r="R41" t="n">
-        <v>7457768</v>
+        <v>7459604</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4900,17 +4920,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,22 +4940,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121338686</v>
+        <v>121988617</v>
       </c>
       <c r="B42" t="n">
-        <v>57785</v>
+        <v>57373</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4953,37 +4968,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731797</v>
+        <v>734668</v>
       </c>
       <c r="R42" t="n">
-        <v>7457819</v>
+        <v>7459020</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5007,12 +5022,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,22 +5047,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121338692</v>
+        <v>121988615</v>
       </c>
       <c r="B43" t="n">
-        <v>57357</v>
+        <v>97073</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5051,41 +5071,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>732035</v>
+        <v>734947</v>
       </c>
       <c r="R43" t="n">
-        <v>7457821</v>
+        <v>7459023</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5109,12 +5129,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5129,22 +5149,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121338690</v>
+        <v>120302888</v>
       </c>
       <c r="B44" t="n">
-        <v>91014</v>
+        <v>56545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5153,41 +5173,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731977</v>
+        <v>733085</v>
       </c>
       <c r="R44" t="n">
-        <v>7457791</v>
+        <v>7458027</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5211,12 +5231,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,22 +5251,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121338689</v>
+        <v>121338671</v>
       </c>
       <c r="B45" t="n">
-        <v>90728</v>
+        <v>56561</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5259,21 +5279,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5283,10 +5303,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731977</v>
+        <v>732502</v>
       </c>
       <c r="R45" t="n">
-        <v>7457792</v>
+        <v>7457961</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5345,10 +5365,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121338691</v>
+        <v>121338675</v>
       </c>
       <c r="B46" t="n">
-        <v>90746</v>
+        <v>100352</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5357,25 +5377,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5385,10 +5405,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>732025</v>
+        <v>732485</v>
       </c>
       <c r="R46" t="n">
-        <v>7457818</v>
+        <v>7457959</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5421,6 +5441,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5447,10 +5472,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121338687</v>
+        <v>121338672</v>
       </c>
       <c r="B47" t="n">
-        <v>97067</v>
+        <v>57791</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5459,25 +5484,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>102999</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5487,10 +5512,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731849</v>
+        <v>732533</v>
       </c>
       <c r="R47" t="n">
-        <v>7457769</v>
+        <v>7457997</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5549,10 +5574,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120302906</v>
+        <v>121338676</v>
       </c>
       <c r="B48" t="n">
-        <v>90654</v>
+        <v>97067</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5561,41 +5586,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>731352</v>
+        <v>732460</v>
       </c>
       <c r="R48" t="n">
-        <v>7457246</v>
+        <v>7457939</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5639,22 +5664,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120302922</v>
+        <v>120302886</v>
       </c>
       <c r="B49" t="n">
-        <v>57333</v>
+        <v>96960</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5663,25 +5688,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5691,10 +5716,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>731611</v>
+        <v>733007</v>
       </c>
       <c r="R49" t="n">
-        <v>7457228</v>
+        <v>7457822</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5721,17 +5746,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5758,10 +5778,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120302910</v>
+        <v>120302894</v>
       </c>
       <c r="B50" t="n">
-        <v>90654</v>
+        <v>79151</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5774,21 +5794,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5798,10 +5818,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>731293</v>
+        <v>733092</v>
       </c>
       <c r="R50" t="n">
-        <v>7457377</v>
+        <v>7457724</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5828,17 +5848,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar på granlåga</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5865,7 +5880,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120302919</v>
+        <v>120302893</v>
       </c>
       <c r="B51" t="n">
         <v>57349</v>
@@ -5905,10 +5920,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>731642</v>
+        <v>732993</v>
       </c>
       <c r="R51" t="n">
-        <v>7457290</v>
+        <v>7457764</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5935,12 +5950,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -5972,10 +5987,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120302923</v>
+        <v>120302892</v>
       </c>
       <c r="B52" t="n">
-        <v>57333</v>
+        <v>56537</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5988,16 +6003,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6012,10 +6027,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>731716</v>
+        <v>732912</v>
       </c>
       <c r="R52" t="n">
-        <v>7457137</v>
+        <v>7457768</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6042,17 +6057,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Hackspår</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6079,10 +6094,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120302908</v>
+        <v>121338686</v>
       </c>
       <c r="B53" t="n">
-        <v>56545</v>
+        <v>57785</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6091,41 +6106,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>731245</v>
+        <v>731797</v>
       </c>
       <c r="R53" t="n">
-        <v>7457418</v>
+        <v>7457819</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6155,11 +6170,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Hane</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6174,22 +6184,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120302914</v>
+        <v>121338692</v>
       </c>
       <c r="B54" t="n">
-        <v>90802</v>
+        <v>57357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6202,37 +6212,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>731763</v>
+        <v>732035</v>
       </c>
       <c r="R54" t="n">
-        <v>7457160</v>
+        <v>7457821</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6276,22 +6286,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120302921</v>
+        <v>121338690</v>
       </c>
       <c r="B55" t="n">
-        <v>56545</v>
+        <v>91014</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,41 +6310,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>731604</v>
+        <v>731977</v>
       </c>
       <c r="R55" t="n">
-        <v>7457238</v>
+        <v>7457791</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6364,11 +6374,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En individ</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6383,22 +6388,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120302916</v>
+        <v>121338689</v>
       </c>
       <c r="B56" t="n">
-        <v>79151</v>
+        <v>90728</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6411,37 +6416,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>731728</v>
+        <v>731977</v>
       </c>
       <c r="R56" t="n">
-        <v>7457308</v>
+        <v>7457792</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6485,22 +6490,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120302917</v>
+        <v>121338691</v>
       </c>
       <c r="B57" t="n">
-        <v>57349</v>
+        <v>90746</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6513,37 +6518,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>731714</v>
+        <v>732025</v>
       </c>
       <c r="R57" t="n">
-        <v>7457298</v>
+        <v>7457818</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6573,11 +6578,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6592,22 +6592,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120302918</v>
+        <v>121338687</v>
       </c>
       <c r="B58" t="n">
-        <v>57333</v>
+        <v>97067</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6616,41 +6616,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>731673</v>
+        <v>731849</v>
       </c>
       <c r="R58" t="n">
-        <v>7457289</v>
+        <v>7457769</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,11 +6680,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6699,22 +6694,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120302920</v>
+        <v>121988601</v>
       </c>
       <c r="B59" t="n">
-        <v>90654</v>
+        <v>56569</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6723,41 +6718,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>731622</v>
+        <v>732420</v>
       </c>
       <c r="R59" t="n">
-        <v>7457276</v>
+        <v>7457510</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6781,12 +6776,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6801,22 +6801,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120302924</v>
+        <v>121988605</v>
       </c>
       <c r="B60" t="n">
-        <v>57349</v>
+        <v>56569</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6825,41 +6825,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731752</v>
+        <v>731925</v>
       </c>
       <c r="R60" t="n">
-        <v>7457204</v>
+        <v>7457696</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6883,17 +6883,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Hackspår på högstubbe</t>
+          <t>3 hanar i flykt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6908,22 +6908,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120302913</v>
+        <v>121988563</v>
       </c>
       <c r="B61" t="n">
-        <v>57333</v>
+        <v>97067</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6932,41 +6932,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>731549</v>
+        <v>734066</v>
       </c>
       <c r="R61" t="n">
-        <v>7457309</v>
+        <v>7457326</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6990,17 +6990,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7015,22 +7010,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120302915</v>
+        <v>120302906</v>
       </c>
       <c r="B62" t="n">
-        <v>57444</v>
+        <v>90654</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7039,25 +7034,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7067,10 +7062,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>731716</v>
+        <v>731352</v>
       </c>
       <c r="R62" t="n">
-        <v>7457334</v>
+        <v>7457246</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7129,7 +7124,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120302911</v>
+        <v>120302922</v>
       </c>
       <c r="B63" t="n">
         <v>57333</v>
@@ -7169,10 +7164,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>731347</v>
+        <v>731611</v>
       </c>
       <c r="R63" t="n">
-        <v>7457280</v>
+        <v>7457228</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7236,10 +7231,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120302912</v>
+        <v>120302910</v>
       </c>
       <c r="B64" t="n">
-        <v>56545</v>
+        <v>90654</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7248,25 +7243,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7276,10 +7271,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>731416</v>
+        <v>731293</v>
       </c>
       <c r="R64" t="n">
-        <v>7457247</v>
+        <v>7457377</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7316,7 +7311,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Hane</t>
+          <t>Rikligt med fruktkroppar på granlåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7343,7 +7338,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120302897</v>
+        <v>120302919</v>
       </c>
       <c r="B65" t="n">
         <v>57349</v>
@@ -7383,10 +7378,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>732853</v>
+        <v>731642</v>
       </c>
       <c r="R65" t="n">
-        <v>7457442</v>
+        <v>7457290</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7413,12 +7408,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7450,10 +7445,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120302896</v>
+        <v>120302923</v>
       </c>
       <c r="B66" t="n">
-        <v>79151</v>
+        <v>57333</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7466,21 +7461,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7490,10 +7485,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>733023</v>
+        <v>731716</v>
       </c>
       <c r="R66" t="n">
-        <v>7457503</v>
+        <v>7457137</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7520,12 +7515,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7552,10 +7552,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120302902</v>
+        <v>120302908</v>
       </c>
       <c r="B67" t="n">
-        <v>79151</v>
+        <v>56545</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7564,25 +7564,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7592,10 +7592,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>733046</v>
+        <v>731245</v>
       </c>
       <c r="R67" t="n">
-        <v>7457090</v>
+        <v>7457418</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7622,12 +7622,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7654,10 +7659,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120302899</v>
+        <v>120302914</v>
       </c>
       <c r="B68" t="n">
-        <v>57333</v>
+        <v>90802</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7670,21 +7675,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7694,10 +7699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>732829</v>
+        <v>731763</v>
       </c>
       <c r="R68" t="n">
-        <v>7457380</v>
+        <v>7457160</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7724,12 +7729,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7756,10 +7761,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120302882</v>
+        <v>120302921</v>
       </c>
       <c r="B69" t="n">
-        <v>5169</v>
+        <v>56545</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7772,21 +7777,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7796,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>733156</v>
+        <v>731604</v>
       </c>
       <c r="R69" t="n">
-        <v>7457547</v>
+        <v>7457238</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7826,12 +7831,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>En individ</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7858,10 +7868,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120302898</v>
+        <v>120302916</v>
       </c>
       <c r="B70" t="n">
-        <v>57333</v>
+        <v>79151</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7874,21 +7884,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7908,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>732795</v>
+        <v>731728</v>
       </c>
       <c r="R70" t="n">
-        <v>7457432</v>
+        <v>7457308</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7928,17 +7938,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Hacksmedja på tall</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7965,10 +7970,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120302877</v>
+        <v>120302917</v>
       </c>
       <c r="B71" t="n">
-        <v>57444</v>
+        <v>57349</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7977,20 +7982,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8005,10 +8010,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>733127</v>
+        <v>731714</v>
       </c>
       <c r="R71" t="n">
-        <v>7457136</v>
+        <v>7457298</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8035,17 +8040,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Fyra individer</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8072,10 +8077,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120302879</v>
+        <v>120302918</v>
       </c>
       <c r="B72" t="n">
-        <v>78298</v>
+        <v>57333</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8088,21 +8093,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>733150</v>
+        <v>731673</v>
       </c>
       <c r="R72" t="n">
-        <v>7457273</v>
+        <v>7457289</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8142,12 +8147,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8174,10 +8184,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120302901</v>
+        <v>120302920</v>
       </c>
       <c r="B73" t="n">
-        <v>57761</v>
+        <v>90654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8190,21 +8200,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8214,10 +8224,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>733049</v>
+        <v>731622</v>
       </c>
       <c r="R73" t="n">
-        <v>7457132</v>
+        <v>7457276</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8244,12 +8254,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8276,7 +8286,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120302878</v>
+        <v>120302924</v>
       </c>
       <c r="B74" t="n">
         <v>57349</v>
@@ -8316,10 +8326,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>733152</v>
+        <v>731752</v>
       </c>
       <c r="R74" t="n">
-        <v>7457234</v>
+        <v>7457204</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8346,17 +8356,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska hackspår</t>
+          <t>Hackspår på högstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8383,10 +8393,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120302903</v>
+        <v>120302913</v>
       </c>
       <c r="B75" t="n">
-        <v>57761</v>
+        <v>57333</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8399,21 +8409,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8423,10 +8433,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>732779</v>
+        <v>731549</v>
       </c>
       <c r="R75" t="n">
-        <v>7457059</v>
+        <v>7457309</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8463,7 +8473,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8490,10 +8500,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120302895</v>
+        <v>120302915</v>
       </c>
       <c r="B76" t="n">
-        <v>57349</v>
+        <v>57444</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8502,20 +8512,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8530,10 +8540,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>733086</v>
+        <v>731716</v>
       </c>
       <c r="R76" t="n">
-        <v>7457578</v>
+        <v>7457334</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8560,17 +8570,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Hackspår</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8597,10 +8602,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120302900</v>
+        <v>120302911</v>
       </c>
       <c r="B77" t="n">
-        <v>57444</v>
+        <v>57333</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8609,20 +8614,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8637,10 +8642,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>733011</v>
+        <v>731347</v>
       </c>
       <c r="R77" t="n">
-        <v>7457133</v>
+        <v>7457280</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8667,17 +8672,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Tre individer</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8704,10 +8709,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121338670</v>
+        <v>120302912</v>
       </c>
       <c r="B78" t="n">
-        <v>97073</v>
+        <v>56545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8720,37 +8725,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>732725</v>
+        <v>731416</v>
       </c>
       <c r="R78" t="n">
-        <v>7457530</v>
+        <v>7457247</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8780,6 +8785,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Hane</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8794,22 +8804,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121338669</v>
+        <v>121988577</v>
       </c>
       <c r="B79" t="n">
-        <v>56569</v>
+        <v>57785</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8818,41 +8828,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>732688</v>
+        <v>734782</v>
       </c>
       <c r="R79" t="n">
-        <v>7457404</v>
+        <v>7456909</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8876,12 +8886,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8896,22 +8906,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121338662</v>
+        <v>121988576</v>
       </c>
       <c r="B80" t="n">
-        <v>97073</v>
+        <v>57373</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8920,41 +8930,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>733321</v>
+        <v>734752</v>
       </c>
       <c r="R80" t="n">
-        <v>7456889</v>
+        <v>7456933</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8978,12 +8988,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8998,22 +9013,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121338694</v>
+        <v>121988573</v>
       </c>
       <c r="B81" t="n">
-        <v>57785</v>
+        <v>97067</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9022,41 +9037,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>732301</v>
+        <v>734788</v>
       </c>
       <c r="R81" t="n">
-        <v>7457166</v>
+        <v>7456898</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9080,12 +9095,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9100,22 +9115,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121338695</v>
+        <v>120302897</v>
       </c>
       <c r="B82" t="n">
-        <v>56569</v>
+        <v>57349</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9124,41 +9139,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>732297</v>
+        <v>732853</v>
       </c>
       <c r="R82" t="n">
-        <v>7457098</v>
+        <v>7457442</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9182,17 +9197,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Tjädertupp</t>
+          <t>Hackspår</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9207,22 +9222,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121338634</v>
+        <v>120302896</v>
       </c>
       <c r="B83" t="n">
-        <v>90746</v>
+        <v>79151</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9235,37 +9250,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>733192</v>
+        <v>733023</v>
       </c>
       <c r="R83" t="n">
-        <v>7456971</v>
+        <v>7457503</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9309,22 +9324,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121338663</v>
+        <v>120302902</v>
       </c>
       <c r="B84" t="n">
-        <v>90728</v>
+        <v>79151</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9337,37 +9352,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>733283</v>
+        <v>733046</v>
       </c>
       <c r="R84" t="n">
-        <v>7456886</v>
+        <v>7457090</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9411,22 +9426,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121338664</v>
+        <v>120302899</v>
       </c>
       <c r="B85" t="n">
-        <v>57373</v>
+        <v>57333</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9439,16 +9454,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9459,17 +9474,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>733274</v>
+        <v>732829</v>
       </c>
       <c r="R85" t="n">
-        <v>7456913</v>
+        <v>7457380</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9513,22 +9528,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121338665</v>
+        <v>120302882</v>
       </c>
       <c r="B86" t="n">
-        <v>90728</v>
+        <v>5169</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9537,41 +9552,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>733143</v>
+        <v>733156</v>
       </c>
       <c r="R86" t="n">
-        <v>7456923</v>
+        <v>7457547</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9615,22 +9630,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121338668</v>
+        <v>120302898</v>
       </c>
       <c r="B87" t="n">
-        <v>91014</v>
+        <v>57333</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9643,37 +9658,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>732643</v>
+        <v>732795</v>
       </c>
       <c r="R87" t="n">
-        <v>7457301</v>
+        <v>7457432</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9697,12 +9712,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hacksmedja på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9717,22 +9737,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121338697</v>
+        <v>120302877</v>
       </c>
       <c r="B88" t="n">
-        <v>97073</v>
+        <v>57444</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9745,37 +9765,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>732290</v>
+        <v>733127</v>
       </c>
       <c r="R88" t="n">
-        <v>7457046</v>
+        <v>7457136</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9799,12 +9819,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Fyra individer</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9819,15 +9844,2839 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120302879</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78298</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>733150</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7457273</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120302901</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>733049</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7457132</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120302878</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57349</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>733152</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7457234</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska hackspår</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120302903</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>732779</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7457059</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Sång</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120302895</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57349</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>733086</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7457578</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Hackspår</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120302900</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57444</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>733011</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7457133</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Tre individer</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121338670</v>
+      </c>
+      <c r="B95" t="n">
+        <v>97073</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>732725</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7457530</v>
+      </c>
+      <c r="S95" t="n">
+        <v>25</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
           <t>Otilia Johansson</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AX95" t="inlineStr">
         <is>
           <t>Otilia Johansson</t>
         </is>
       </c>
-      <c r="AY88" t="inlineStr"/>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>121338669</v>
+      </c>
+      <c r="B96" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>732688</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7457404</v>
+      </c>
+      <c r="S96" t="n">
+        <v>25</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>121338662</v>
+      </c>
+      <c r="B97" t="n">
+        <v>97073</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>733321</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7456889</v>
+      </c>
+      <c r="S97" t="n">
+        <v>25</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>121338694</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>732301</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7457166</v>
+      </c>
+      <c r="S98" t="n">
+        <v>25</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>121338695</v>
+      </c>
+      <c r="B99" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>732297</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7457098</v>
+      </c>
+      <c r="S99" t="n">
+        <v>25</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Tjädertupp</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>121338634</v>
+      </c>
+      <c r="B100" t="n">
+        <v>90746</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>733192</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7456971</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>121338663</v>
+      </c>
+      <c r="B101" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>733283</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7456886</v>
+      </c>
+      <c r="S101" t="n">
+        <v>25</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>121338664</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>733274</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7456913</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>121338665</v>
+      </c>
+      <c r="B103" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>733143</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7456923</v>
+      </c>
+      <c r="S103" t="n">
+        <v>25</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>121338668</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91014</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>658</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>732643</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7457301</v>
+      </c>
+      <c r="S104" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>121338697</v>
+      </c>
+      <c r="B105" t="n">
+        <v>97073</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Gällivare kn, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>732290</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7457046</v>
+      </c>
+      <c r="S105" t="n">
+        <v>25</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>121988613</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91014</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>658</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>732261</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7457083</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>121988610</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57357</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>732280</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7457367</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>hackspår på tall</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>121988600</v>
+      </c>
+      <c r="B108" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>732438</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7457363</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>2 högar spillning</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>121988608</v>
+      </c>
+      <c r="B109" t="n">
+        <v>56572</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>732161</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7457336</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>121988611</v>
+      </c>
+      <c r="B110" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>732230</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7457160</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>1 individ, sång</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>121988599</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57468</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>732438</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7457363</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>1 individ, förbiflygande</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>121988596</v>
+      </c>
+      <c r="B112" t="n">
+        <v>97067</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>732317</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7457282</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>121988595</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>732828</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7457044</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>1 individ, sång</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>121988609</v>
+      </c>
+      <c r="B114" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>732093</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7457394</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>1 hane i flykt</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>121988612</v>
+      </c>
+      <c r="B115" t="n">
+        <v>57468</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Porjusberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>732243</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7457122</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>1 individ, sång</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Hanna Emanuelsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988632</v>
+        <v>121988629</v>
       </c>
       <c r="B33" t="n">
-        <v>97073</v>
+        <v>97091</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>735185</v>
+        <v>735177</v>
       </c>
       <c r="R33" t="n">
-        <v>7459609</v>
+        <v>7459604</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988614</v>
+        <v>121988617</v>
       </c>
       <c r="B34" t="n">
-        <v>56569</v>
+        <v>57381</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>735030</v>
+        <v>734668</v>
       </c>
       <c r="R34" t="n">
-        <v>7459026</v>
+        <v>7459020</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988625</v>
+        <v>121988618</v>
       </c>
       <c r="B35" t="n">
-        <v>97073</v>
+        <v>56577</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>734707</v>
+        <v>734513</v>
       </c>
       <c r="R35" t="n">
-        <v>7459457</v>
+        <v>7459096</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,6 +4289,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4318,7 +4323,7 @@
         <v>121988631</v>
       </c>
       <c r="B36" t="n">
-        <v>91996</v>
+        <v>92010</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4422,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988630</v>
+        <v>121988633</v>
       </c>
       <c r="B37" t="n">
-        <v>91998</v>
+        <v>57365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4438,21 +4443,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4462,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735177</v>
+        <v>735194</v>
       </c>
       <c r="R37" t="n">
-        <v>7459602</v>
+        <v>7459625</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,7 +4507,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2 fruktkroppar</t>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4529,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988638</v>
+        <v>121988632</v>
       </c>
       <c r="B38" t="n">
-        <v>90746</v>
+        <v>97091</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4541,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4569,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>735553</v>
+        <v>735185</v>
       </c>
       <c r="R38" t="n">
-        <v>7459238</v>
+        <v>7459609</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4605,11 +4610,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988633</v>
+        <v>121988615</v>
       </c>
       <c r="B39" t="n">
-        <v>57357</v>
+        <v>97091</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>735194</v>
+        <v>734947</v>
       </c>
       <c r="R39" t="n">
-        <v>7459625</v>
+        <v>7459023</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,11 +4712,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988618</v>
+        <v>121988638</v>
       </c>
       <c r="B40" t="n">
-        <v>56569</v>
+        <v>90760</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4750,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>734513</v>
+        <v>735553</v>
       </c>
       <c r="R40" t="n">
-        <v>7459096</v>
+        <v>7459238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,7 +4818,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 hona i flykt</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4850,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988629</v>
+        <v>121988614</v>
       </c>
       <c r="B41" t="n">
-        <v>97073</v>
+        <v>56577</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4866,21 +4861,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735177</v>
+        <v>735030</v>
       </c>
       <c r="R41" t="n">
-        <v>7459604</v>
+        <v>7459026</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4926,6 +4921,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,10 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988617</v>
+        <v>121988630</v>
       </c>
       <c r="B42" t="n">
-        <v>57373</v>
+        <v>92012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4968,21 +4968,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734668</v>
+        <v>735177</v>
       </c>
       <c r="R42" t="n">
-        <v>7459020</v>
+        <v>7459602</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackmärken i tallraka</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988615</v>
+        <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97073</v>
+        <v>97091</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734947</v>
+        <v>734707</v>
       </c>
       <c r="R43" t="n">
-        <v>7459023</v>
+        <v>7459457</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6709,7 +6709,7 @@
         <v>121988601</v>
       </c>
       <c r="B59" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>121988605</v>
       </c>
       <c r="B60" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>121988563</v>
       </c>
       <c r="B61" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121988577</v>
+        <v>121988573</v>
       </c>
       <c r="B79" t="n">
-        <v>57785</v>
+        <v>97085</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8828,25 +8828,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>734782</v>
+        <v>734788</v>
       </c>
       <c r="R79" t="n">
-        <v>7456909</v>
+        <v>7456898</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8921,7 +8921,7 @@
         <v>121988576</v>
       </c>
       <c r="B80" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9025,10 +9025,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121988573</v>
+        <v>121988577</v>
       </c>
       <c r="B81" t="n">
-        <v>97067</v>
+        <v>57793</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9037,25 +9037,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>734788</v>
+        <v>734782</v>
       </c>
       <c r="R81" t="n">
-        <v>7456898</v>
+        <v>7456909</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988613</v>
+        <v>121988612</v>
       </c>
       <c r="B106" t="n">
-        <v>91014</v>
+        <v>57476</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11627,25 +11627,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732261</v>
+        <v>732243</v>
       </c>
       <c r="R106" t="n">
-        <v>7457083</v>
+        <v>7457122</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11722,10 +11722,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988610</v>
+        <v>121988599</v>
       </c>
       <c r="B107" t="n">
-        <v>57357</v>
+        <v>57476</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11734,20 +11734,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11762,10 +11762,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732280</v>
+        <v>732438</v>
       </c>
       <c r="R107" t="n">
-        <v>7457367</v>
+        <v>7457363</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>hackspår på tall</t>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11829,10 +11829,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988600</v>
+        <v>121988595</v>
       </c>
       <c r="B108" t="n">
-        <v>56569</v>
+        <v>57793</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11841,25 +11841,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732438</v>
+        <v>732828</v>
       </c>
       <c r="R108" t="n">
-        <v>7457363</v>
+        <v>7457044</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11899,17 +11899,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11936,10 +11936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988608</v>
+        <v>121988609</v>
       </c>
       <c r="B109" t="n">
-        <v>56572</v>
+        <v>56577</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11952,21 +11952,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732161</v>
+        <v>732093</v>
       </c>
       <c r="R109" t="n">
-        <v>7457336</v>
+        <v>7457394</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 hane i flykt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12043,10 +12043,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121988611</v>
+        <v>121988608</v>
       </c>
       <c r="B110" t="n">
-        <v>57785</v>
+        <v>56580</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12055,25 +12055,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103001</v>
+        <v>102613</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>732230</v>
+        <v>732161</v>
       </c>
       <c r="R110" t="n">
-        <v>7457160</v>
+        <v>7457336</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12150,10 +12150,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988599</v>
+        <v>121988613</v>
       </c>
       <c r="B111" t="n">
-        <v>57468</v>
+        <v>91028</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12162,25 +12162,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732438</v>
+        <v>732261</v>
       </c>
       <c r="R111" t="n">
-        <v>7457363</v>
+        <v>7457083</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12257,10 +12257,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988596</v>
+        <v>121988600</v>
       </c>
       <c r="B112" t="n">
-        <v>97067</v>
+        <v>56577</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12273,21 +12273,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732317</v>
+        <v>732438</v>
       </c>
       <c r="R112" t="n">
-        <v>7457282</v>
+        <v>7457363</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12327,12 +12327,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12359,10 +12364,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121988595</v>
+        <v>121988610</v>
       </c>
       <c r="B113" t="n">
-        <v>57785</v>
+        <v>57365</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12375,21 +12380,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12399,10 +12404,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>732828</v>
+        <v>732280</v>
       </c>
       <c r="R113" t="n">
-        <v>7457044</v>
+        <v>7457367</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12429,17 +12434,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,10 +12471,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121988609</v>
+        <v>121988596</v>
       </c>
       <c r="B114" t="n">
-        <v>56569</v>
+        <v>97085</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12482,21 +12487,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12506,10 +12511,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732093</v>
+        <v>732317</v>
       </c>
       <c r="R114" t="n">
-        <v>7457394</v>
+        <v>7457282</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12536,17 +12541,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>1 hane i flykt</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12573,10 +12573,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121988612</v>
+        <v>121988611</v>
       </c>
       <c r="B115" t="n">
-        <v>57468</v>
+        <v>57793</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12585,25 +12585,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103031</v>
+        <v>103001</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12613,10 +12613,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732243</v>
+        <v>732230</v>
       </c>
       <c r="R115" t="n">
-        <v>7457122</v>
+        <v>7457160</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988615</v>
+        <v>121988638</v>
       </c>
       <c r="B39" t="n">
-        <v>97091</v>
+        <v>90760</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>734947</v>
+        <v>735553</v>
       </c>
       <c r="R39" t="n">
-        <v>7459023</v>
+        <v>7459238</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,6 +4712,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4738,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988638</v>
+        <v>121988614</v>
       </c>
       <c r="B40" t="n">
-        <v>90760</v>
+        <v>56577</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4750,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4778,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735553</v>
+        <v>735030</v>
       </c>
       <c r="R40" t="n">
-        <v>7459238</v>
+        <v>7459026</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4818,7 +4823,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,10 +4850,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988614</v>
+        <v>121988615</v>
       </c>
       <c r="B41" t="n">
-        <v>56577</v>
+        <v>97091</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4861,21 +4866,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735030</v>
+        <v>734947</v>
       </c>
       <c r="R41" t="n">
-        <v>7459026</v>
+        <v>7459023</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4921,11 +4926,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988629</v>
+        <v>121988615</v>
       </c>
       <c r="B33" t="n">
-        <v>97091</v>
+        <v>97093</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>735177</v>
+        <v>734947</v>
       </c>
       <c r="R33" t="n">
-        <v>7459604</v>
+        <v>7459023</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988617</v>
+        <v>121988638</v>
       </c>
       <c r="B34" t="n">
-        <v>57381</v>
+        <v>90762</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4122,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734668</v>
+        <v>735553</v>
       </c>
       <c r="R34" t="n">
-        <v>7459020</v>
+        <v>7459238</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Hackmärken i tallraka</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988618</v>
+        <v>121988617</v>
       </c>
       <c r="B35" t="n">
-        <v>56577</v>
+        <v>57381</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4225,25 +4225,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>734513</v>
+        <v>734668</v>
       </c>
       <c r="R35" t="n">
-        <v>7459096</v>
+        <v>7459020</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 hona i flykt</t>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,10 +4320,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121988631</v>
+        <v>121988633</v>
       </c>
       <c r="B36" t="n">
-        <v>92010</v>
+        <v>57365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4336,21 +4336,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>735185</v>
+        <v>735194</v>
       </c>
       <c r="R36" t="n">
-        <v>7459609</v>
+        <v>7459625</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 fruktkropp</t>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988633</v>
+        <v>121988629</v>
       </c>
       <c r="B37" t="n">
-        <v>57365</v>
+        <v>97093</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4439,25 +4439,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735194</v>
+        <v>735177</v>
       </c>
       <c r="R37" t="n">
-        <v>7459625</v>
+        <v>7459604</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,11 +4503,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988632</v>
+        <v>121988631</v>
       </c>
       <c r="B38" t="n">
-        <v>97091</v>
+        <v>92012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4541,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,6 +4605,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988638</v>
+        <v>121988625</v>
       </c>
       <c r="B39" t="n">
-        <v>90760</v>
+        <v>97093</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>735553</v>
+        <v>734707</v>
       </c>
       <c r="R39" t="n">
-        <v>7459238</v>
+        <v>7459457</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,11 +4712,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,10 +4738,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988614</v>
+        <v>121988630</v>
       </c>
       <c r="B40" t="n">
-        <v>56577</v>
+        <v>92014</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4750,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735030</v>
+        <v>735177</v>
       </c>
       <c r="R40" t="n">
-        <v>7459026</v>
+        <v>7459602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4823,7 +4818,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4850,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988615</v>
+        <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97091</v>
+        <v>97093</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4890,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>734947</v>
+        <v>735185</v>
       </c>
       <c r="R41" t="n">
-        <v>7459023</v>
+        <v>7459609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4952,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988630</v>
+        <v>121988618</v>
       </c>
       <c r="B42" t="n">
-        <v>92012</v>
+        <v>56577</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4964,25 +4959,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4992,10 +4987,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735177</v>
+        <v>734513</v>
       </c>
       <c r="R42" t="n">
-        <v>7459602</v>
+        <v>7459096</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5027,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2 fruktkroppar</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +5054,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988625</v>
+        <v>121988614</v>
       </c>
       <c r="B43" t="n">
-        <v>97091</v>
+        <v>56577</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5075,21 +5070,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734707</v>
+        <v>735030</v>
       </c>
       <c r="R43" t="n">
-        <v>7459457</v>
+        <v>7459026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,6 +5130,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6923,7 +6923,7 @@
         <v>121988563</v>
       </c>
       <c r="B61" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>121988573</v>
       </c>
       <c r="B79" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8918,10 +8918,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121988576</v>
+        <v>121988577</v>
       </c>
       <c r="B80" t="n">
-        <v>57381</v>
+        <v>57793</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>734752</v>
+        <v>734782</v>
       </c>
       <c r="R80" t="n">
-        <v>7456933</v>
+        <v>7456909</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8994,11 +8994,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9025,10 +9020,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121988577</v>
+        <v>121988576</v>
       </c>
       <c r="B81" t="n">
-        <v>57793</v>
+        <v>57381</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9065,10 +9060,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>734782</v>
+        <v>734752</v>
       </c>
       <c r="R81" t="n">
-        <v>7456909</v>
+        <v>7456933</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9101,6 +9096,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988612</v>
+        <v>121988608</v>
       </c>
       <c r="B106" t="n">
-        <v>57476</v>
+        <v>56580</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11631,16 +11631,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732243</v>
+        <v>732161</v>
       </c>
       <c r="R106" t="n">
-        <v>7457122</v>
+        <v>7457336</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11722,7 +11722,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988599</v>
+        <v>121988612</v>
       </c>
       <c r="B107" t="n">
         <v>57476</v>
@@ -11762,10 +11762,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732438</v>
+        <v>732243</v>
       </c>
       <c r="R107" t="n">
-        <v>7457363</v>
+        <v>7457122</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11829,10 +11829,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988595</v>
+        <v>121988613</v>
       </c>
       <c r="B108" t="n">
-        <v>57793</v>
+        <v>91030</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11845,21 +11845,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103001</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732828</v>
+        <v>732261</v>
       </c>
       <c r="R108" t="n">
-        <v>7457044</v>
+        <v>7457083</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11899,17 +11899,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11936,7 +11936,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988609</v>
+        <v>121988600</v>
       </c>
       <c r="B109" t="n">
         <v>56577</v>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732093</v>
+        <v>732438</v>
       </c>
       <c r="R109" t="n">
-        <v>7457394</v>
+        <v>7457363</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>1 hane i flykt</t>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12043,10 +12043,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121988608</v>
+        <v>121988611</v>
       </c>
       <c r="B110" t="n">
-        <v>56580</v>
+        <v>57793</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12055,25 +12055,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>102613</v>
+        <v>103001</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>732161</v>
+        <v>732230</v>
       </c>
       <c r="R110" t="n">
-        <v>7457336</v>
+        <v>7457160</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12150,10 +12150,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988613</v>
+        <v>121988610</v>
       </c>
       <c r="B111" t="n">
-        <v>91028</v>
+        <v>57365</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12166,21 +12166,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732261</v>
+        <v>732280</v>
       </c>
       <c r="R111" t="n">
-        <v>7457083</v>
+        <v>7457367</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12257,10 +12257,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988600</v>
+        <v>121988595</v>
       </c>
       <c r="B112" t="n">
-        <v>56577</v>
+        <v>57793</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12269,25 +12269,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732438</v>
+        <v>732828</v>
       </c>
       <c r="R112" t="n">
-        <v>7457363</v>
+        <v>7457044</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12327,17 +12327,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12364,10 +12364,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121988610</v>
+        <v>121988596</v>
       </c>
       <c r="B113" t="n">
-        <v>57365</v>
+        <v>97087</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12376,25 +12376,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>732280</v>
+        <v>732317</v>
       </c>
       <c r="R113" t="n">
-        <v>7457367</v>
+        <v>7457282</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12434,17 +12434,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>hackspår på tall</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12471,10 +12466,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121988596</v>
+        <v>121988599</v>
       </c>
       <c r="B114" t="n">
-        <v>97085</v>
+        <v>57476</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12487,21 +12482,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12511,10 +12506,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732317</v>
+        <v>732438</v>
       </c>
       <c r="R114" t="n">
-        <v>7457282</v>
+        <v>7457363</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12541,12 +12536,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12573,10 +12573,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121988611</v>
+        <v>121988609</v>
       </c>
       <c r="B115" t="n">
-        <v>57793</v>
+        <v>56577</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12585,25 +12585,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12613,10 +12613,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732230</v>
+        <v>732093</v>
       </c>
       <c r="R115" t="n">
-        <v>7457160</v>
+        <v>7457394</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>1 hane i flykt</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988615</v>
+        <v>121988633</v>
       </c>
       <c r="B33" t="n">
-        <v>97135</v>
+        <v>57374</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4016,25 +4016,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734947</v>
+        <v>735194</v>
       </c>
       <c r="R33" t="n">
-        <v>7459023</v>
+        <v>7459625</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,6 +4080,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4106,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988638</v>
+        <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>90797</v>
+        <v>97135</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4118,25 +4123,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>735553</v>
+        <v>735177</v>
       </c>
       <c r="R34" t="n">
-        <v>7459238</v>
+        <v>7459604</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,11 +4187,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,7 +4213,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988614</v>
+        <v>121988618</v>
       </c>
       <c r="B35" t="n">
         <v>56584</v>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>735030</v>
+        <v>734513</v>
       </c>
       <c r="R35" t="n">
-        <v>7459026</v>
+        <v>7459096</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,10 +4320,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121988618</v>
+        <v>121988617</v>
       </c>
       <c r="B36" t="n">
-        <v>56584</v>
+        <v>57390</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4332,25 +4332,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>734513</v>
+        <v>734668</v>
       </c>
       <c r="R36" t="n">
-        <v>7459096</v>
+        <v>7459020</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 hona i flykt</t>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,7 +4427,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988632</v>
+        <v>121988625</v>
       </c>
       <c r="B37" t="n">
         <v>97135</v>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735185</v>
+        <v>734707</v>
       </c>
       <c r="R37" t="n">
-        <v>7459609</v>
+        <v>7459457</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988633</v>
+        <v>121988630</v>
       </c>
       <c r="B38" t="n">
-        <v>57374</v>
+        <v>92049</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4545,21 +4545,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>735194</v>
+        <v>735177</v>
       </c>
       <c r="R38" t="n">
-        <v>7459625</v>
+        <v>7459602</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska hackmärken i smedja</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988631</v>
+        <v>121988638</v>
       </c>
       <c r="B39" t="n">
-        <v>92047</v>
+        <v>90797</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>735185</v>
+        <v>735553</v>
       </c>
       <c r="R39" t="n">
-        <v>7459609</v>
+        <v>7459238</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>1 fruktkropp</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,7 +4743,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988625</v>
+        <v>121988615</v>
       </c>
       <c r="B40" t="n">
         <v>97135</v>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>734707</v>
+        <v>734947</v>
       </c>
       <c r="R40" t="n">
-        <v>7459457</v>
+        <v>7459023</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988630</v>
+        <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>92049</v>
+        <v>97135</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,25 +4857,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735177</v>
+        <v>735185</v>
       </c>
       <c r="R41" t="n">
-        <v>7459602</v>
+        <v>7459609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4921,11 +4921,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,10 +4947,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988617</v>
+        <v>121988631</v>
       </c>
       <c r="B42" t="n">
-        <v>57390</v>
+        <v>92047</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4968,21 +4963,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4992,10 +4987,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734668</v>
+        <v>735185</v>
       </c>
       <c r="R42" t="n">
-        <v>7459020</v>
+        <v>7459609</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5032,7 +5027,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackmärken i tallraka</t>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +5054,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988629</v>
+        <v>121988614</v>
       </c>
       <c r="B43" t="n">
-        <v>97135</v>
+        <v>56584</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5075,21 +5070,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>735177</v>
+        <v>735030</v>
       </c>
       <c r="R43" t="n">
-        <v>7459604</v>
+        <v>7459026</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,6 +5130,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6706,7 +6706,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121988605</v>
+        <v>121988601</v>
       </c>
       <c r="B59" t="n">
         <v>56584</v>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>731925</v>
+        <v>732420</v>
       </c>
       <c r="R59" t="n">
-        <v>7457696</v>
+        <v>7457510</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3 hanar i flykt</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6813,7 +6813,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121988601</v>
+        <v>121988605</v>
       </c>
       <c r="B60" t="n">
         <v>56584</v>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>732420</v>
+        <v>731925</v>
       </c>
       <c r="R60" t="n">
-        <v>7457510</v>
+        <v>7457696</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>3 hanar i flykt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988613</v>
+        <v>121988596</v>
       </c>
       <c r="B106" t="n">
-        <v>91065</v>
+        <v>97129</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11627,25 +11627,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732261</v>
+        <v>732317</v>
       </c>
       <c r="R106" t="n">
-        <v>7457083</v>
+        <v>7457282</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11685,17 +11685,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>3 fruktkroppar</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11722,10 +11717,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988608</v>
+        <v>121988595</v>
       </c>
       <c r="B107" t="n">
-        <v>56587</v>
+        <v>57803</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11734,25 +11729,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102613</v>
+        <v>103001</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11762,10 +11757,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732161</v>
+        <v>732828</v>
       </c>
       <c r="R107" t="n">
-        <v>7457336</v>
+        <v>7457044</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11792,17 +11787,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11829,10 +11824,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988599</v>
+        <v>121988600</v>
       </c>
       <c r="B108" t="n">
-        <v>57485</v>
+        <v>56584</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11845,21 +11840,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11909,7 +11904,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11936,10 +11931,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988610</v>
+        <v>121988613</v>
       </c>
       <c r="B109" t="n">
-        <v>57374</v>
+        <v>91065</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11952,21 +11947,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11976,10 +11971,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732280</v>
+        <v>732261</v>
       </c>
       <c r="R109" t="n">
-        <v>7457367</v>
+        <v>7457083</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12016,7 +12011,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>hackspår på tall</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12150,10 +12145,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988600</v>
+        <v>121988610</v>
       </c>
       <c r="B111" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12162,25 +12157,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12190,10 +12185,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732438</v>
+        <v>732280</v>
       </c>
       <c r="R111" t="n">
-        <v>7457363</v>
+        <v>7457367</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12230,7 +12225,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12257,10 +12252,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988595</v>
+        <v>121988609</v>
       </c>
       <c r="B112" t="n">
-        <v>57803</v>
+        <v>56584</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12269,25 +12264,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12297,10 +12292,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732828</v>
+        <v>732093</v>
       </c>
       <c r="R112" t="n">
-        <v>7457044</v>
+        <v>7457394</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12327,17 +12322,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>1 hane i flykt</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12364,10 +12359,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121988611</v>
+        <v>121988599</v>
       </c>
       <c r="B113" t="n">
-        <v>57803</v>
+        <v>57485</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12376,25 +12371,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103001</v>
+        <v>103031</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12404,10 +12399,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>732230</v>
+        <v>732438</v>
       </c>
       <c r="R113" t="n">
-        <v>7457160</v>
+        <v>7457363</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12444,7 +12439,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12471,10 +12466,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121988609</v>
+        <v>121988611</v>
       </c>
       <c r="B114" t="n">
-        <v>56584</v>
+        <v>57803</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12483,25 +12478,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12511,10 +12506,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732093</v>
+        <v>732230</v>
       </c>
       <c r="R114" t="n">
-        <v>7457394</v>
+        <v>7457160</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12551,7 +12546,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 hane i flykt</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12578,10 +12573,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121988596</v>
+        <v>121988608</v>
       </c>
       <c r="B115" t="n">
-        <v>97129</v>
+        <v>56587</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12594,21 +12589,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>102613</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12618,10 +12613,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732317</v>
+        <v>732161</v>
       </c>
       <c r="R115" t="n">
-        <v>7457282</v>
+        <v>7457336</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12648,12 +12643,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988633</v>
+        <v>121988618</v>
       </c>
       <c r="B33" t="n">
-        <v>57374</v>
+        <v>56584</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4016,25 +4016,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>735194</v>
+        <v>734513</v>
       </c>
       <c r="R33" t="n">
-        <v>7459625</v>
+        <v>7459096</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska hackmärken i smedja</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4111,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988629</v>
+        <v>121988631</v>
       </c>
       <c r="B34" t="n">
-        <v>97135</v>
+        <v>92057</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4123,25 +4123,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>735177</v>
+        <v>735185</v>
       </c>
       <c r="R34" t="n">
-        <v>7459604</v>
+        <v>7459609</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4187,6 +4187,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4218,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988618</v>
+        <v>121988625</v>
       </c>
       <c r="B35" t="n">
-        <v>56584</v>
+        <v>97145</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4234,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>734513</v>
+        <v>734707</v>
       </c>
       <c r="R35" t="n">
-        <v>7459096</v>
+        <v>7459457</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,11 +4294,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988625</v>
+        <v>121988614</v>
       </c>
       <c r="B37" t="n">
-        <v>97135</v>
+        <v>56584</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>734707</v>
+        <v>735030</v>
       </c>
       <c r="R37" t="n">
-        <v>7459457</v>
+        <v>7459026</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,6 +4503,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4529,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988630</v>
+        <v>121988632</v>
       </c>
       <c r="B38" t="n">
-        <v>92049</v>
+        <v>97145</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4541,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4569,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>735177</v>
+        <v>735185</v>
       </c>
       <c r="R38" t="n">
-        <v>7459602</v>
+        <v>7459609</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4605,11 +4610,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988638</v>
+        <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>90797</v>
+        <v>92059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4652,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>735553</v>
+        <v>735177</v>
       </c>
       <c r="R39" t="n">
-        <v>7459238</v>
+        <v>7459602</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988615</v>
+        <v>121988633</v>
       </c>
       <c r="B40" t="n">
-        <v>97135</v>
+        <v>57374</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>734947</v>
+        <v>735194</v>
       </c>
       <c r="R40" t="n">
-        <v>7459023</v>
+        <v>7459625</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,6 +4819,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,10 +4850,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988632</v>
+        <v>121988638</v>
       </c>
       <c r="B41" t="n">
-        <v>97135</v>
+        <v>90807</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,25 +4862,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4890,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735185</v>
+        <v>735553</v>
       </c>
       <c r="R41" t="n">
-        <v>7459609</v>
+        <v>7459238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4921,6 +4926,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4947,10 +4957,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988631</v>
+        <v>121988629</v>
       </c>
       <c r="B42" t="n">
-        <v>92047</v>
+        <v>97145</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4959,25 +4969,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4987,10 +4997,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735185</v>
+        <v>735177</v>
       </c>
       <c r="R42" t="n">
-        <v>7459609</v>
+        <v>7459604</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5023,11 +5033,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5054,10 +5059,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988614</v>
+        <v>121988615</v>
       </c>
       <c r="B43" t="n">
-        <v>56584</v>
+        <v>97145</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5070,21 +5075,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5094,10 +5099,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>735030</v>
+        <v>734947</v>
       </c>
       <c r="R43" t="n">
-        <v>7459026</v>
+        <v>7459023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,11 +5135,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6923,7 +6923,7 @@
         <v>121988563</v>
       </c>
       <c r="B61" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121988573</v>
+        <v>121988576</v>
       </c>
       <c r="B79" t="n">
-        <v>97129</v>
+        <v>57390</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8828,25 +8828,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>734788</v>
+        <v>734752</v>
       </c>
       <c r="R79" t="n">
-        <v>7456898</v>
+        <v>7456933</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8892,6 +8892,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8918,10 +8923,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121988577</v>
+        <v>121988573</v>
       </c>
       <c r="B80" t="n">
-        <v>57803</v>
+        <v>97139</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8930,25 +8935,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8958,10 +8963,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>734782</v>
+        <v>734788</v>
       </c>
       <c r="R80" t="n">
-        <v>7456909</v>
+        <v>7456898</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9020,10 +9025,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121988576</v>
+        <v>121988577</v>
       </c>
       <c r="B81" t="n">
-        <v>57390</v>
+        <v>57803</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9036,21 +9041,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9060,10 +9065,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>734752</v>
+        <v>734782</v>
       </c>
       <c r="R81" t="n">
-        <v>7456933</v>
+        <v>7456909</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9096,11 +9101,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988596</v>
+        <v>121988608</v>
       </c>
       <c r="B106" t="n">
-        <v>97129</v>
+        <v>56587</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11631,21 +11631,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>102613</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732317</v>
+        <v>732161</v>
       </c>
       <c r="R106" t="n">
-        <v>7457282</v>
+        <v>7457336</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11685,12 +11685,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11717,10 +11722,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988595</v>
+        <v>121988600</v>
       </c>
       <c r="B107" t="n">
-        <v>57803</v>
+        <v>56584</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11729,25 +11734,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11757,10 +11762,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732828</v>
+        <v>732438</v>
       </c>
       <c r="R107" t="n">
-        <v>7457044</v>
+        <v>7457363</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11787,17 +11792,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11824,7 +11829,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988600</v>
+        <v>121988609</v>
       </c>
       <c r="B108" t="n">
         <v>56584</v>
@@ -11864,10 +11869,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732438</v>
+        <v>732093</v>
       </c>
       <c r="R108" t="n">
-        <v>7457363</v>
+        <v>7457394</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11904,7 +11909,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>1 hane i flykt</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11931,10 +11936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988613</v>
+        <v>121988611</v>
       </c>
       <c r="B109" t="n">
-        <v>91065</v>
+        <v>57803</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11947,21 +11952,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>103001</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732261</v>
+        <v>732230</v>
       </c>
       <c r="R109" t="n">
-        <v>7457083</v>
+        <v>7457160</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12011,7 +12016,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12038,10 +12043,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121988612</v>
+        <v>121988613</v>
       </c>
       <c r="B110" t="n">
-        <v>57485</v>
+        <v>91075</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12050,25 +12055,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12078,10 +12083,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>732243</v>
+        <v>732261</v>
       </c>
       <c r="R110" t="n">
-        <v>7457122</v>
+        <v>7457083</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12118,7 +12123,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12145,10 +12150,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988610</v>
+        <v>121988599</v>
       </c>
       <c r="B111" t="n">
-        <v>57374</v>
+        <v>57485</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12157,20 +12162,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12185,10 +12190,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732280</v>
+        <v>732438</v>
       </c>
       <c r="R111" t="n">
-        <v>7457367</v>
+        <v>7457363</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12225,7 +12230,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>hackspår på tall</t>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12252,10 +12257,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988609</v>
+        <v>121988596</v>
       </c>
       <c r="B112" t="n">
-        <v>56584</v>
+        <v>97139</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12268,21 +12273,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12292,10 +12297,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732093</v>
+        <v>732317</v>
       </c>
       <c r="R112" t="n">
-        <v>7457394</v>
+        <v>7457282</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12322,17 +12327,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>1 hane i flykt</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12359,10 +12359,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121988599</v>
+        <v>121988595</v>
       </c>
       <c r="B113" t="n">
-        <v>57485</v>
+        <v>57803</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12371,25 +12371,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103031</v>
+        <v>103001</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12399,10 +12399,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>732438</v>
+        <v>732828</v>
       </c>
       <c r="R113" t="n">
-        <v>7457363</v>
+        <v>7457044</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12429,17 +12429,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,10 +12466,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121988611</v>
+        <v>121988610</v>
       </c>
       <c r="B114" t="n">
-        <v>57803</v>
+        <v>57374</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12482,21 +12482,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12506,10 +12506,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732230</v>
+        <v>732280</v>
       </c>
       <c r="R114" t="n">
-        <v>7457160</v>
+        <v>7457367</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12573,10 +12573,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121988608</v>
+        <v>121988612</v>
       </c>
       <c r="B115" t="n">
-        <v>56587</v>
+        <v>57485</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12589,16 +12589,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12613,10 +12613,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732161</v>
+        <v>732243</v>
       </c>
       <c r="R115" t="n">
-        <v>7457336</v>
+        <v>7457122</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988618</v>
+        <v>121988615</v>
       </c>
       <c r="B33" t="n">
-        <v>56584</v>
+        <v>97145</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4020,21 +4020,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734513</v>
+        <v>734947</v>
       </c>
       <c r="R33" t="n">
-        <v>7459096</v>
+        <v>7459023</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,11 +4080,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4111,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988631</v>
+        <v>121988618</v>
       </c>
       <c r="B34" t="n">
-        <v>92057</v>
+        <v>56584</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4123,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>735185</v>
+        <v>734513</v>
       </c>
       <c r="R34" t="n">
-        <v>7459609</v>
+        <v>7459096</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4191,7 +4186,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1 fruktkropp</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4218,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988625</v>
+        <v>121988638</v>
       </c>
       <c r="B35" t="n">
-        <v>97145</v>
+        <v>90807</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4230,25 +4225,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4258,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>734707</v>
+        <v>735553</v>
       </c>
       <c r="R35" t="n">
-        <v>7459457</v>
+        <v>7459238</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4294,6 +4289,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,10 +4320,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121988617</v>
+        <v>121988631</v>
       </c>
       <c r="B36" t="n">
-        <v>57390</v>
+        <v>92057</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4336,21 +4336,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>734668</v>
+        <v>735185</v>
       </c>
       <c r="R36" t="n">
-        <v>7459020</v>
+        <v>7459609</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken i tallraka</t>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988614</v>
+        <v>121988633</v>
       </c>
       <c r="B37" t="n">
-        <v>56584</v>
+        <v>57374</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4439,25 +4439,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735030</v>
+        <v>735194</v>
       </c>
       <c r="R37" t="n">
-        <v>7459026</v>
+        <v>7459625</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hona i flykt</t>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988632</v>
+        <v>121988630</v>
       </c>
       <c r="B38" t="n">
-        <v>97145</v>
+        <v>92059</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>735185</v>
+        <v>735177</v>
       </c>
       <c r="R38" t="n">
-        <v>7459609</v>
+        <v>7459602</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,6 +4610,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988630</v>
+        <v>121988629</v>
       </c>
       <c r="B39" t="n">
-        <v>92059</v>
+        <v>97145</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4653,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4679,7 +4684,7 @@
         <v>735177</v>
       </c>
       <c r="R39" t="n">
-        <v>7459602</v>
+        <v>7459604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,11 +4717,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988633</v>
+        <v>121988625</v>
       </c>
       <c r="B40" t="n">
-        <v>57374</v>
+        <v>97145</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735194</v>
+        <v>734707</v>
       </c>
       <c r="R40" t="n">
-        <v>7459625</v>
+        <v>7459457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,11 +4819,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4850,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988638</v>
+        <v>121988617</v>
       </c>
       <c r="B41" t="n">
-        <v>90807</v>
+        <v>57390</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4866,21 +4861,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4890,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735553</v>
+        <v>734668</v>
       </c>
       <c r="R41" t="n">
-        <v>7459238</v>
+        <v>7459020</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4930,7 +4925,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4957,10 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988629</v>
+        <v>121988614</v>
       </c>
       <c r="B42" t="n">
-        <v>97145</v>
+        <v>56584</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4973,21 +4968,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4997,10 +4992,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735177</v>
+        <v>735030</v>
       </c>
       <c r="R42" t="n">
-        <v>7459604</v>
+        <v>7459026</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5033,6 +5028,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,7 +5059,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988615</v>
+        <v>121988632</v>
       </c>
       <c r="B43" t="n">
         <v>97145</v>
@@ -5099,10 +5099,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734947</v>
+        <v>735185</v>
       </c>
       <c r="R43" t="n">
-        <v>7459023</v>
+        <v>7459609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121988601</v>
+        <v>121988605</v>
       </c>
       <c r="B59" t="n">
         <v>56584</v>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>732420</v>
+        <v>731925</v>
       </c>
       <c r="R59" t="n">
-        <v>7457510</v>
+        <v>7457696</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Sång</t>
+          <t>3 hanar i flykt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6813,7 +6813,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121988605</v>
+        <v>121988601</v>
       </c>
       <c r="B60" t="n">
         <v>56584</v>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731925</v>
+        <v>732420</v>
       </c>
       <c r="R60" t="n">
-        <v>7457696</v>
+        <v>7457510</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>3 hanar i flykt</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8816,10 +8816,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121988576</v>
+        <v>121988577</v>
       </c>
       <c r="B79" t="n">
-        <v>57390</v>
+        <v>57803</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8832,21 +8832,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>103001</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>734752</v>
+        <v>734782</v>
       </c>
       <c r="R79" t="n">
-        <v>7456933</v>
+        <v>7456909</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8892,11 +8892,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9025,10 +9020,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121988577</v>
+        <v>121988576</v>
       </c>
       <c r="B81" t="n">
-        <v>57803</v>
+        <v>57390</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9065,10 +9060,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>734782</v>
+        <v>734752</v>
       </c>
       <c r="R81" t="n">
-        <v>7456909</v>
+        <v>7456933</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9101,6 +9096,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Hackmärken i död granlåga</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988608</v>
+        <v>121988596</v>
       </c>
       <c r="B106" t="n">
-        <v>56587</v>
+        <v>97139</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11631,21 +11631,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102613</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732161</v>
+        <v>732317</v>
       </c>
       <c r="R106" t="n">
-        <v>7457336</v>
+        <v>7457282</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11685,17 +11685,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11722,10 +11717,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988600</v>
+        <v>121988608</v>
       </c>
       <c r="B107" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11738,21 +11733,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11762,10 +11757,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732438</v>
+        <v>732161</v>
       </c>
       <c r="R107" t="n">
-        <v>7457363</v>
+        <v>7457336</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11802,7 +11797,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11829,10 +11824,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988609</v>
+        <v>121988599</v>
       </c>
       <c r="B108" t="n">
-        <v>56584</v>
+        <v>57485</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11845,21 +11840,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11869,10 +11864,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732093</v>
+        <v>732438</v>
       </c>
       <c r="R108" t="n">
-        <v>7457394</v>
+        <v>7457363</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11909,7 +11904,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>1 hane i flykt</t>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12043,10 +12038,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121988613</v>
+        <v>121988609</v>
       </c>
       <c r="B110" t="n">
-        <v>91075</v>
+        <v>56584</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12055,25 +12050,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12083,10 +12078,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>732261</v>
+        <v>732093</v>
       </c>
       <c r="R110" t="n">
-        <v>7457083</v>
+        <v>7457394</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12123,7 +12118,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>1 hane i flykt</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12150,10 +12145,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988599</v>
+        <v>121988600</v>
       </c>
       <c r="B111" t="n">
-        <v>57485</v>
+        <v>56584</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12166,21 +12161,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12230,7 +12225,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12257,10 +12252,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988596</v>
+        <v>121988595</v>
       </c>
       <c r="B112" t="n">
-        <v>97139</v>
+        <v>57803</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12269,25 +12264,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>103001</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12297,10 +12292,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732317</v>
+        <v>732828</v>
       </c>
       <c r="R112" t="n">
-        <v>7457282</v>
+        <v>7457044</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12333,6 +12328,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-01-18</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12359,10 +12359,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121988595</v>
+        <v>121988610</v>
       </c>
       <c r="B113" t="n">
-        <v>57803</v>
+        <v>57374</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12375,21 +12375,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12399,10 +12399,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>732828</v>
+        <v>732280</v>
       </c>
       <c r="R113" t="n">
-        <v>7457044</v>
+        <v>7457367</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12429,17 +12429,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,10 +12466,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121988610</v>
+        <v>121988613</v>
       </c>
       <c r="B114" t="n">
-        <v>57374</v>
+        <v>91075</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12482,21 +12482,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12506,10 +12506,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732280</v>
+        <v>732261</v>
       </c>
       <c r="R114" t="n">
-        <v>7457367</v>
+        <v>7457083</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>hackspår på tall</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988630</v>
+        <v>121988629</v>
       </c>
       <c r="B38" t="n">
-        <v>92059</v>
+        <v>97145</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4577,7 +4577,7 @@
         <v>735177</v>
       </c>
       <c r="R38" t="n">
-        <v>7459602</v>
+        <v>7459604</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,11 +4610,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4641,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988629</v>
+        <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>97145</v>
+        <v>92059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4653,25 +4648,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4684,7 +4679,7 @@
         <v>735177</v>
       </c>
       <c r="R39" t="n">
-        <v>7459604</v>
+        <v>7459602</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,6 +4712,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -11717,10 +11717,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988608</v>
+        <v>121988599</v>
       </c>
       <c r="B107" t="n">
-        <v>56587</v>
+        <v>57485</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11733,16 +11733,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732161</v>
+        <v>732438</v>
       </c>
       <c r="R107" t="n">
-        <v>7457336</v>
+        <v>7457363</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11824,10 +11824,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988599</v>
+        <v>121988611</v>
       </c>
       <c r="B108" t="n">
-        <v>57485</v>
+        <v>57803</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11836,25 +11836,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>103001</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732438</v>
+        <v>732230</v>
       </c>
       <c r="R108" t="n">
-        <v>7457363</v>
+        <v>7457160</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11904,7 +11904,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11931,10 +11931,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988611</v>
+        <v>121988608</v>
       </c>
       <c r="B109" t="n">
-        <v>57803</v>
+        <v>56587</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11943,25 +11943,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103001</v>
+        <v>102613</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732230</v>
+        <v>732161</v>
       </c>
       <c r="R109" t="n">
-        <v>7457160</v>
+        <v>7457336</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988615</v>
+        <v>121988614</v>
       </c>
       <c r="B33" t="n">
-        <v>97145</v>
+        <v>56589</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4020,21 +4020,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734947</v>
+        <v>735030</v>
       </c>
       <c r="R33" t="n">
-        <v>7459023</v>
+        <v>7459026</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,6 +4080,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4106,10 +4111,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988618</v>
+        <v>121988625</v>
       </c>
       <c r="B34" t="n">
-        <v>56584</v>
+        <v>97157</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4122,21 +4127,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4146,10 +4151,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734513</v>
+        <v>734707</v>
       </c>
       <c r="R34" t="n">
-        <v>7459096</v>
+        <v>7459457</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,11 +4187,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988638</v>
+        <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>90807</v>
+        <v>92069</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>735553</v>
+        <v>735185</v>
       </c>
       <c r="R35" t="n">
-        <v>7459238</v>
+        <v>7459609</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,10 +4320,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121988631</v>
+        <v>121988633</v>
       </c>
       <c r="B36" t="n">
-        <v>92057</v>
+        <v>57379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4336,21 +4336,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4360,10 +4360,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>735185</v>
+        <v>735194</v>
       </c>
       <c r="R36" t="n">
-        <v>7459609</v>
+        <v>7459625</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1 fruktkropp</t>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988633</v>
+        <v>121988618</v>
       </c>
       <c r="B37" t="n">
-        <v>57374</v>
+        <v>56589</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4439,25 +4439,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735194</v>
+        <v>734513</v>
       </c>
       <c r="R37" t="n">
-        <v>7459625</v>
+        <v>7459096</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska hackmärken i smedja</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4534,10 +4534,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988629</v>
+        <v>121988630</v>
       </c>
       <c r="B38" t="n">
-        <v>97145</v>
+        <v>92071</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4546,25 +4546,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4577,7 +4577,7 @@
         <v>735177</v>
       </c>
       <c r="R38" t="n">
-        <v>7459604</v>
+        <v>7459602</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4610,6 +4610,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4636,10 +4641,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988630</v>
+        <v>121988615</v>
       </c>
       <c r="B39" t="n">
-        <v>92059</v>
+        <v>97157</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4648,25 +4653,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4676,10 +4681,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>735177</v>
+        <v>734947</v>
       </c>
       <c r="R39" t="n">
-        <v>7459602</v>
+        <v>7459023</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4712,11 +4717,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4743,10 +4743,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988625</v>
+        <v>121988632</v>
       </c>
       <c r="B40" t="n">
-        <v>97145</v>
+        <v>97157</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>734707</v>
+        <v>735185</v>
       </c>
       <c r="R40" t="n">
-        <v>7459457</v>
+        <v>7459609</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988617</v>
+        <v>121988638</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>90819</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4861,21 +4861,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>734668</v>
+        <v>735553</v>
       </c>
       <c r="R41" t="n">
-        <v>7459020</v>
+        <v>7459238</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackmärken i tallraka</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,10 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988614</v>
+        <v>121988629</v>
       </c>
       <c r="B42" t="n">
-        <v>56584</v>
+        <v>97157</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4968,21 +4968,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735030</v>
+        <v>735177</v>
       </c>
       <c r="R42" t="n">
-        <v>7459026</v>
+        <v>7459604</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5028,11 +5028,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,10 +5054,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988632</v>
+        <v>121988617</v>
       </c>
       <c r="B43" t="n">
-        <v>97145</v>
+        <v>57395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5071,25 +5066,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5099,10 +5094,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>735185</v>
+        <v>734668</v>
       </c>
       <c r="R43" t="n">
-        <v>7459609</v>
+        <v>7459020</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5135,6 +5130,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6709,7 +6709,7 @@
         <v>121988605</v>
       </c>
       <c r="B59" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>121988601</v>
       </c>
       <c r="B60" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>121988563</v>
       </c>
       <c r="B61" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>121988577</v>
       </c>
       <c r="B79" t="n">
-        <v>57803</v>
+        <v>57808</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>121988573</v>
       </c>
       <c r="B80" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>121988576</v>
       </c>
       <c r="B81" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988596</v>
+        <v>121988599</v>
       </c>
       <c r="B106" t="n">
-        <v>97139</v>
+        <v>57490</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11631,21 +11631,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732317</v>
+        <v>732438</v>
       </c>
       <c r="R106" t="n">
-        <v>7457282</v>
+        <v>7457363</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11685,12 +11685,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11717,10 +11722,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988599</v>
+        <v>121988600</v>
       </c>
       <c r="B107" t="n">
-        <v>57485</v>
+        <v>56589</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11733,21 +11738,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11797,7 +11802,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11824,10 +11829,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988611</v>
+        <v>121988610</v>
       </c>
       <c r="B108" t="n">
-        <v>57803</v>
+        <v>57379</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11840,21 +11845,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11864,10 +11869,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732230</v>
+        <v>732280</v>
       </c>
       <c r="R108" t="n">
-        <v>7457160</v>
+        <v>7457367</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11904,7 +11909,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11931,10 +11936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988608</v>
+        <v>121988612</v>
       </c>
       <c r="B109" t="n">
-        <v>56587</v>
+        <v>57490</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11947,16 +11952,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732161</v>
+        <v>732243</v>
       </c>
       <c r="R109" t="n">
-        <v>7457336</v>
+        <v>7457122</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12011,7 +12016,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12041,7 +12046,7 @@
         <v>121988609</v>
       </c>
       <c r="B110" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12145,10 +12150,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988600</v>
+        <v>121988595</v>
       </c>
       <c r="B111" t="n">
-        <v>56584</v>
+        <v>57808</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12157,25 +12162,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>103001</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12185,10 +12190,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732438</v>
+        <v>732828</v>
       </c>
       <c r="R111" t="n">
-        <v>7457363</v>
+        <v>7457044</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12215,17 +12220,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12252,10 +12257,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988595</v>
+        <v>121988608</v>
       </c>
       <c r="B112" t="n">
-        <v>57803</v>
+        <v>56592</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12264,25 +12269,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103001</v>
+        <v>102613</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12292,10 +12297,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732828</v>
+        <v>732161</v>
       </c>
       <c r="R112" t="n">
-        <v>7457044</v>
+        <v>7457336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12322,17 +12327,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12359,10 +12364,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121988610</v>
+        <v>121988611</v>
       </c>
       <c r="B113" t="n">
-        <v>57374</v>
+        <v>57808</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12375,21 +12380,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12399,10 +12404,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>732280</v>
+        <v>732230</v>
       </c>
       <c r="R113" t="n">
-        <v>7457367</v>
+        <v>7457160</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12439,7 +12444,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>hackspår på tall</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12469,7 +12474,7 @@
         <v>121988613</v>
       </c>
       <c r="B114" t="n">
-        <v>91075</v>
+        <v>91087</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12573,10 +12578,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121988612</v>
+        <v>121988596</v>
       </c>
       <c r="B115" t="n">
-        <v>57485</v>
+        <v>97151</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12589,21 +12594,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103031</v>
+        <v>221945</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12613,10 +12618,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732243</v>
+        <v>732317</v>
       </c>
       <c r="R115" t="n">
-        <v>7457122</v>
+        <v>7457282</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12643,17 +12648,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>1 individ, sång</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4004,10 +4004,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121988614</v>
+        <v>121988629</v>
       </c>
       <c r="B33" t="n">
-        <v>56589</v>
+        <v>97162</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4020,21 +4020,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>735030</v>
+        <v>735177</v>
       </c>
       <c r="R33" t="n">
-        <v>7459026</v>
+        <v>7459604</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,11 +4080,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4111,10 +4106,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988625</v>
+        <v>121988631</v>
       </c>
       <c r="B34" t="n">
-        <v>97157</v>
+        <v>92074</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4123,25 +4118,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4151,10 +4146,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734707</v>
+        <v>735185</v>
       </c>
       <c r="R34" t="n">
-        <v>7459457</v>
+        <v>7459609</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4187,6 +4182,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4213,10 +4213,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988631</v>
+        <v>121988638</v>
       </c>
       <c r="B35" t="n">
-        <v>92069</v>
+        <v>90826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4229,21 +4229,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>735185</v>
+        <v>735553</v>
       </c>
       <c r="R35" t="n">
-        <v>7459609</v>
+        <v>7459238</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 fruktkropp</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4427,10 +4427,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988618</v>
+        <v>121988615</v>
       </c>
       <c r="B37" t="n">
-        <v>56589</v>
+        <v>97162</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>734513</v>
+        <v>734947</v>
       </c>
       <c r="R37" t="n">
-        <v>7459096</v>
+        <v>7459023</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4503,11 +4503,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4537,7 +4532,7 @@
         <v>121988630</v>
       </c>
       <c r="B38" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4641,10 +4636,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988615</v>
+        <v>121988614</v>
       </c>
       <c r="B39" t="n">
-        <v>97157</v>
+        <v>56589</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4657,21 +4652,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4681,10 +4676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>734947</v>
+        <v>735030</v>
       </c>
       <c r="R39" t="n">
-        <v>7459023</v>
+        <v>7459026</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4717,6 +4712,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4746,7 +4746,7 @@
         <v>121988632</v>
       </c>
       <c r="B40" t="n">
-        <v>97157</v>
+        <v>97162</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988638</v>
+        <v>121988618</v>
       </c>
       <c r="B41" t="n">
-        <v>90819</v>
+        <v>56589</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4857,25 +4857,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735553</v>
+        <v>734513</v>
       </c>
       <c r="R41" t="n">
-        <v>7459238</v>
+        <v>7459096</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>1 hona i flykt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,10 +4952,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988629</v>
+        <v>121988625</v>
       </c>
       <c r="B42" t="n">
-        <v>97157</v>
+        <v>97162</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>735177</v>
+        <v>734707</v>
       </c>
       <c r="R42" t="n">
-        <v>7459604</v>
+        <v>7459457</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6923,7 +6923,7 @@
         <v>121988563</v>
       </c>
       <c r="B61" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>121988573</v>
       </c>
       <c r="B80" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11615,10 +11615,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121988599</v>
+        <v>121988610</v>
       </c>
       <c r="B106" t="n">
-        <v>57490</v>
+        <v>57379</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11627,20 +11627,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>732438</v>
+        <v>732280</v>
       </c>
       <c r="R106" t="n">
-        <v>7457363</v>
+        <v>7457367</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 individ, förbiflygande</t>
+          <t>hackspår på tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11722,7 +11722,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121988600</v>
+        <v>121988609</v>
       </c>
       <c r="B107" t="n">
         <v>56589</v>
@@ -11762,10 +11762,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>732438</v>
+        <v>732093</v>
       </c>
       <c r="R107" t="n">
-        <v>7457363</v>
+        <v>7457394</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 högar spillning</t>
+          <t>1 hane i flykt</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11829,10 +11829,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121988610</v>
+        <v>121988613</v>
       </c>
       <c r="B108" t="n">
-        <v>57379</v>
+        <v>91092</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11845,21 +11845,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>732280</v>
+        <v>732261</v>
       </c>
       <c r="R108" t="n">
-        <v>7457367</v>
+        <v>7457083</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>hackspår på tall</t>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11936,10 +11936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121988612</v>
+        <v>121988608</v>
       </c>
       <c r="B109" t="n">
-        <v>57490</v>
+        <v>56592</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11952,16 +11952,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>732243</v>
+        <v>732161</v>
       </c>
       <c r="R109" t="n">
-        <v>7457122</v>
+        <v>7457336</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>1 individ, sång</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12043,10 +12043,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121988609</v>
+        <v>121988612</v>
       </c>
       <c r="B110" t="n">
-        <v>56589</v>
+        <v>57490</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12059,21 +12059,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>732093</v>
+        <v>732243</v>
       </c>
       <c r="R110" t="n">
-        <v>7457394</v>
+        <v>7457122</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>1 hane i flykt</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12150,10 +12150,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121988595</v>
+        <v>121988596</v>
       </c>
       <c r="B111" t="n">
-        <v>57808</v>
+        <v>97156</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12162,25 +12162,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103001</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>732828</v>
+        <v>732317</v>
       </c>
       <c r="R111" t="n">
-        <v>7457044</v>
+        <v>7457282</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12226,11 +12226,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-01-18</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12257,10 +12252,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121988608</v>
+        <v>121988599</v>
       </c>
       <c r="B112" t="n">
-        <v>56592</v>
+        <v>57490</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12273,16 +12268,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12297,10 +12292,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>732161</v>
+        <v>732438</v>
       </c>
       <c r="R112" t="n">
-        <v>7457336</v>
+        <v>7457363</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12337,7 +12332,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>1 individ, förbiflygande</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12471,10 +12466,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121988613</v>
+        <v>121988595</v>
       </c>
       <c r="B114" t="n">
-        <v>91087</v>
+        <v>57808</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12487,21 +12482,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>658</v>
+        <v>103001</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12511,10 +12506,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>732261</v>
+        <v>732828</v>
       </c>
       <c r="R114" t="n">
-        <v>7457083</v>
+        <v>7457044</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12541,17 +12536,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-01-17</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>1 individ, sång</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12578,10 +12573,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121988596</v>
+        <v>121988600</v>
       </c>
       <c r="B115" t="n">
-        <v>97151</v>
+        <v>56589</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12594,21 +12589,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12618,10 +12613,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>732317</v>
+        <v>732438</v>
       </c>
       <c r="R115" t="n">
-        <v>7457282</v>
+        <v>7457363</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12648,12 +12643,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-01-18</t>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>2 högar spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -2355,7 +2355,7 @@
         <v>120302933</v>
       </c>
       <c r="B17" t="n">
-        <v>56691</v>
+        <v>56694</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>121988608</v>
       </c>
       <c r="B109" t="n">
-        <v>56691</v>
+        <v>56694</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4104,12 +4104,7 @@
         <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>97162</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,12 +4166,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,12 +4201,7 @@
         <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>92074</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4273,12 +4263,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4313,12 +4303,7 @@
         <v>121988638</v>
       </c>
       <c r="B36" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4335,14 +4320,10 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4380,12 +4361,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4420,12 +4401,7 @@
         <v>121988633</v>
       </c>
       <c r="B37" t="n">
-        <v>57379</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,12 +4463,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4527,12 +4503,7 @@
         <v>121988615</v>
       </c>
       <c r="B38" t="n">
-        <v>97162</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97671</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4594,12 +4565,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,12 +4600,7 @@
         <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>92076</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92878</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4696,12 +4662,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4843,12 +4809,7 @@
         <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97162</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97671</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,12 +4871,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,12 +5013,7 @@
         <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97162</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97671</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5119,12 +5075,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5154,12 +5110,7 @@
         <v>121988617</v>
       </c>
       <c r="B44" t="n">
-        <v>57395</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57734</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5221,12 +5172,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4104,7 +4104,7 @@
         <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>92876</v>
+        <v>92879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>121988638</v>
       </c>
       <c r="B36" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>121988633</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>121988615</v>
       </c>
       <c r="B38" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>92878</v>
+        <v>92881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>121988617</v>
       </c>
       <c r="B44" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4104,7 +4104,7 @@
         <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>92879</v>
+        <v>92880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>121988638</v>
       </c>
       <c r="B36" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>121988615</v>
       </c>
       <c r="B38" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4104,7 +4104,7 @@
         <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>92880</v>
+        <v>92897</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>121988638</v>
       </c>
       <c r="B36" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>121988615</v>
       </c>
       <c r="B38" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>92882</v>
+        <v>92899</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4104,7 +4104,7 @@
         <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>121988638</v>
       </c>
       <c r="B36" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>121988615</v>
       </c>
       <c r="B38" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97708</v>
+        <v>97710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -4104,7 +4104,7 @@
         <v>121988629</v>
       </c>
       <c r="B34" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>121988631</v>
       </c>
       <c r="B35" t="n">
-        <v>92915</v>
+        <v>93002</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>121988638</v>
       </c>
       <c r="B36" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>121988633</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>121988615</v>
       </c>
       <c r="B38" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>121988630</v>
       </c>
       <c r="B39" t="n">
-        <v>92917</v>
+        <v>93004</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>121988632</v>
       </c>
       <c r="B41" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>121988625</v>
       </c>
       <c r="B43" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>121988617</v>
       </c>
       <c r="B44" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103360492</v>
+        <v>103360614</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,28 +686,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>735181.4535099637</v>
+        <v>735179</v>
       </c>
       <c r="R2" t="n">
-        <v>7459600.4444911</v>
+        <v>7459595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +746,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103360614</v>
+        <v>121338719</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,40 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>735179.5679854422</v>
+        <v>735757</v>
       </c>
       <c r="R3" t="n">
-        <v>7459595.203172942</v>
+        <v>7459269</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,56 +855,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Vivi Eriksson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Björn Svanelöv</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103360624</v>
+        <v>103360557</v>
       </c>
       <c r="B4" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>735179.5679854422</v>
+        <v>735178</v>
       </c>
       <c r="R4" t="n">
-        <v>7459595.203172942</v>
+        <v>7459703</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,19 +944,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,22 +967,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Björn Svanelöv</t>
+          <t>Björn Svanelöv, Vivi Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103360472</v>
+        <v>103360857</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,45 +985,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ringat träd (tretåig hackspett) Sikträsk, Lu lm</t>
+          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>735145.1492475753</v>
+        <v>735170</v>
       </c>
       <c r="R5" t="n">
-        <v>7459697.99770986</v>
+        <v>7459696</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,59 +1045,40 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackmärken på tall, blandskog</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Björn Svanelöv</t>
+          <t>Vivi Eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Svanelöv</t>
+          <t>Vivi Eriksson, Björn Svanelöv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103360822</v>
+        <v>121338702</v>
       </c>
       <c r="B6" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,49 +1086,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>735186.6210599719</v>
+        <v>735224</v>
       </c>
       <c r="R6" t="n">
-        <v>7459746.535131355</v>
+        <v>7459176</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,22 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,65 +1160,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Vivi Eriksson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Björn Svanelöv</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103360557</v>
+        <v>121988631</v>
       </c>
       <c r="B7" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>735178.3691936788</v>
+        <v>735185</v>
       </c>
       <c r="R7" t="n">
-        <v>7459702.472451664</v>
+        <v>7459609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,22 +1237,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,56 +1256,50 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Vivi Eriksson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Björn Svanelöv</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103360782</v>
+        <v>103360492</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1439,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>735186.6210599719</v>
+        <v>735182</v>
       </c>
       <c r="R8" t="n">
-        <v>7459746.535131355</v>
+        <v>7459600</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,26 +1349,16 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
@@ -1505,22 +1372,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Björn Svanelöv</t>
+          <t>Björn Svanelöv, Vivi Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103360857</v>
+        <v>120302941</v>
       </c>
       <c r="B9" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,40 +1390,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>735170.3119845761</v>
+        <v>735661</v>
       </c>
       <c r="R9" t="n">
-        <v>7459696.299669756</v>
+        <v>7459088</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,22 +1444,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,34 +1458,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vivi Eriksson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vivi Eriksson, Björn Svanelöv</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120302934</v>
+        <v>121338704</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,37 +1487,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>734919</v>
+        <v>735170</v>
       </c>
       <c r="R10" t="n">
-        <v>7459493</v>
+        <v>7459303</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,65 +1561,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120302929</v>
+        <v>121988630</v>
       </c>
       <c r="B11" t="n">
-        <v>96966</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>734710</v>
+        <v>735177</v>
       </c>
       <c r="R11" t="n">
-        <v>7459012</v>
+        <v>7459602</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,6 +1644,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,49 +1663,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120302930</v>
+        <v>120302938</v>
       </c>
       <c r="B12" t="n">
-        <v>56545</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>734730</v>
+        <v>735356</v>
       </c>
       <c r="R12" t="n">
-        <v>7459077</v>
+        <v>7459135</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1913,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,53 +1772,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120302940</v>
+        <v>121338701</v>
       </c>
       <c r="B13" t="n">
-        <v>96966</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>735608</v>
+        <v>735254</v>
       </c>
       <c r="R13" t="n">
-        <v>7459127</v>
+        <v>7459137</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,27 +1857,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120302936</v>
+        <v>121338709</v>
       </c>
       <c r="B14" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,37 +1880,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>735289</v>
+        <v>735490</v>
       </c>
       <c r="R14" t="n">
-        <v>7459144</v>
+        <v>7459479</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,27 +1954,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120302932</v>
+        <v>103360782</v>
       </c>
       <c r="B15" t="n">
-        <v>96966</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,37 +1977,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>734754</v>
+        <v>735187</v>
       </c>
       <c r="R15" t="n">
-        <v>7459460</v>
+        <v>7459747</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,47 +2038,43 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Vivi Eriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Vivi Eriksson, Björn Svanelöv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120302927</v>
+        <v>120302939</v>
       </c>
       <c r="B16" t="n">
-        <v>79151</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,21 +2082,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2290,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>735126</v>
+        <v>735534</v>
       </c>
       <c r="R16" t="n">
-        <v>7459188</v>
+        <v>7459189</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2320,12 +2136,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>9 fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2352,15 +2173,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120302933</v>
+        <v>121338713</v>
       </c>
       <c r="B17" t="n">
-        <v>56694</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,37 +2184,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102613</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>735031</v>
+        <v>735621</v>
       </c>
       <c r="R17" t="n">
-        <v>7459592</v>
+        <v>7459340</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2428,11 +2244,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,65 +2258,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120302937</v>
+        <v>121338716</v>
       </c>
       <c r="B18" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>735316</v>
+        <v>735787</v>
       </c>
       <c r="R18" t="n">
-        <v>7459160</v>
+        <v>7459247</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2535,11 +2341,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sång</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2554,65 +2355,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120302935</v>
+        <v>121338717</v>
       </c>
       <c r="B19" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stubba, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734905</v>
+        <v>735799</v>
       </c>
       <c r="R19" t="n">
-        <v>7459394</v>
+        <v>7459254</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2642,11 +2438,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,65 +2452,63 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Åsedahl</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121338712</v>
+        <v>103360624</v>
       </c>
       <c r="B20" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>735645</v>
+        <v>735179</v>
       </c>
       <c r="R20" t="n">
-        <v>7459290</v>
+        <v>7459595</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2743,12 +2532,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2757,33 +2546,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Vivi Eriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Vivi Eriksson, Björn Svanelöv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121338700</v>
+        <v>121988617</v>
       </c>
       <c r="B21" t="n">
-        <v>97073</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2791,37 +2576,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>735294</v>
+        <v>734668</v>
       </c>
       <c r="R21" t="n">
-        <v>7459118</v>
+        <v>7459020</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2851,6 +2636,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hackmärken i tallraka</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2865,62 +2655,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121338716</v>
+        <v>103360472</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Ringat träd (tretåig hackspett) Sikträsk, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>735787</v>
+        <v>735145</v>
       </c>
       <c r="R22" t="n">
-        <v>7459247</v>
+        <v>7459698</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2947,12 +2740,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hackmärken på tall, blandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2967,27 +2765,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Björn Svanelöv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Björn Svanelöv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121338718</v>
+        <v>120302936</v>
       </c>
       <c r="B23" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,37 +2788,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>735749</v>
+        <v>735289</v>
       </c>
       <c r="R23" t="n">
-        <v>7459256</v>
+        <v>7459144</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3069,27 +2862,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121338702</v>
+        <v>121988633</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3097,37 +2885,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Porjusberget, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>735224</v>
+        <v>735194</v>
       </c>
       <c r="R24" t="n">
-        <v>7459176</v>
+        <v>7459625</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3157,6 +2945,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3171,27 +2964,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Hanna Emanuelsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121338713</v>
+        <v>120302933</v>
       </c>
       <c r="B25" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,37 +2987,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>735621</v>
+        <v>735031</v>
       </c>
       <c r="R25" t="n">
-        <v>7459340</v>
+        <v>7459592</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3259,6 +3047,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3273,65 +3066,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121338699</v>
+        <v>120302934</v>
       </c>
       <c r="B26" t="n">
-        <v>97073</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>103001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>735424</v>
+        <v>734919</v>
       </c>
       <c r="R26" t="n">
-        <v>7459188</v>
+        <v>7459493</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3361,6 +3149,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,27 +3168,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121338719</v>
+        <v>120302935</v>
       </c>
       <c r="B27" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3403,37 +3191,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>735757</v>
+        <v>734905</v>
       </c>
       <c r="R27" t="n">
-        <v>7459269</v>
+        <v>7459394</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,6 +3251,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fem födosökande individer</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3477,65 +3270,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121338701</v>
+        <v>120302937</v>
       </c>
       <c r="B28" t="n">
-        <v>92004</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>735254</v>
+        <v>735316</v>
       </c>
       <c r="R28" t="n">
-        <v>7459137</v>
+        <v>7459160</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3565,6 +3353,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3579,65 +3372,72 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121338717</v>
+        <v>103360822</v>
       </c>
       <c r="B29" t="n">
-        <v>79726</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Gällivare Sikträsket Luspavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>735799</v>
+        <v>735187</v>
       </c>
       <c r="R29" t="n">
-        <v>7459254</v>
+        <v>7459747</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3661,12 +3461,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3681,27 +3481,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Vivi Eriksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Vivi Eriksson, Björn Svanelöv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121338711</v>
+        <v>120302929</v>
       </c>
       <c r="B30" t="n">
-        <v>97073</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3729,17 +3524,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>735499</v>
+        <v>734710</v>
       </c>
       <c r="R30" t="n">
-        <v>7459458</v>
+        <v>7459012</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3783,27 +3578,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121338721</v>
+        <v>120302932</v>
       </c>
       <c r="B31" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3811,16 +3601,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3831,17 +3621,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>735756</v>
+        <v>734754</v>
       </c>
       <c r="R31" t="n">
-        <v>7459178</v>
+        <v>7459460</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3885,65 +3675,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121338704</v>
+        <v>120302940</v>
       </c>
       <c r="B32" t="n">
-        <v>91998</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gällivare kn, Lu lm</t>
+          <t>Stubba, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>735170</v>
+        <v>735608</v>
       </c>
       <c r="R32" t="n">
-        <v>7459303</v>
+        <v>7459127</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3987,27 +3772,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121338703</v>
+        <v>121338699</v>
       </c>
       <c r="B33" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4015,16 +3795,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4039,10 +3819,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>735177</v>
+        <v>735424</v>
       </c>
       <c r="R33" t="n">
-        <v>7459280</v>
+        <v>7459188</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4101,10 +3881,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121988629</v>
+        <v>121338700</v>
       </c>
       <c r="B34" t="n">
-        <v>97797</v>
+        <v>97989</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4132,17 +3912,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Porjusberget, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>735177</v>
+        <v>735294</v>
       </c>
       <c r="R34" t="n">
-        <v>7459604</v>
+        <v>7459118</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4186,60 +3966,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121988631</v>
+        <v>121338711</v>
       </c>
       <c r="B35" t="n">
-        <v>93002</v>
+        <v>97989</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Porjusberget, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>735185</v>
+        <v>735499</v>
       </c>
       <c r="R35" t="n">
-        <v>7459609</v>
+        <v>7459458</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4269,11 +4049,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,42 +4063,46 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121988638</v>
+        <v>121988615</v>
       </c>
       <c r="B36" t="n">
-        <v>91748</v>
+        <v>97989</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4331,10 +4110,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>735553</v>
+        <v>734947</v>
       </c>
       <c r="R36" t="n">
-        <v>7459238</v>
+        <v>7459023</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4367,11 +4146,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4398,32 +4172,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121988633</v>
+        <v>121988619</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>97989</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4207,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>735194</v>
+        <v>734511</v>
       </c>
       <c r="R37" t="n">
-        <v>7459625</v>
+        <v>7459147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4469,11 +4243,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska hackmärken i smedja</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4500,10 +4269,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121988615</v>
+        <v>121988625</v>
       </c>
       <c r="B38" t="n">
-        <v>97797</v>
+        <v>97989</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4535,10 +4304,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>734947</v>
+        <v>734707</v>
       </c>
       <c r="R38" t="n">
-        <v>7459023</v>
+        <v>7459457</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,32 +4366,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121988630</v>
+        <v>121988629</v>
       </c>
       <c r="B39" t="n">
-        <v>93004</v>
+        <v>97989</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4635,7 +4404,7 @@
         <v>735177</v>
       </c>
       <c r="R39" t="n">
-        <v>7459602</v>
+        <v>7459604</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4668,11 +4437,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,15 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121988614</v>
+        <v>121988632</v>
       </c>
       <c r="B40" t="n">
-        <v>56589</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4715,21 +4474,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4739,10 +4498,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>735030</v>
+        <v>735185</v>
       </c>
       <c r="R40" t="n">
-        <v>7459026</v>
+        <v>7459609</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4769,17 +4528,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hona i flykt</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4806,10 +4560,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121988632</v>
+        <v>121338703</v>
       </c>
       <c r="B41" t="n">
-        <v>97797</v>
+        <v>97983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4817,16 +4571,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4837,17 +4591,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Porjusberget, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>735185</v>
+        <v>735177</v>
       </c>
       <c r="R41" t="n">
-        <v>7459609</v>
+        <v>7459280</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4891,27 +4645,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121988618</v>
+        <v>121338712</v>
       </c>
       <c r="B42" t="n">
-        <v>56589</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4919,37 +4668,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Porjusberget, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734513</v>
+        <v>735645</v>
       </c>
       <c r="R42" t="n">
-        <v>7459096</v>
+        <v>7459290</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4973,17 +4722,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-01-16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 hona i flykt</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,22 +4742,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121988625</v>
+        <v>121338721</v>
       </c>
       <c r="B43" t="n">
-        <v>97797</v>
+        <v>97983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5021,16 +4765,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5041,17 +4785,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Porjusberget, Lu lm</t>
+          <t>Gällivare kn, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734707</v>
+        <v>735756</v>
       </c>
       <c r="R43" t="n">
-        <v>7459457</v>
+        <v>7459178</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5095,44 +4839,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hanna Emanuelsson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121988617</v>
+        <v>121988616</v>
       </c>
       <c r="B44" t="n">
-        <v>57823</v>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5142,10 +4886,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>734668</v>
+        <v>734877</v>
       </c>
       <c r="R44" t="n">
-        <v>7459020</v>
+        <v>7458985</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5180,11 +4924,6 @@
           <t>2024-09-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hackmärken i tallraka</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5206,6 +4945,103 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120302927</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stubba, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>735126</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7459188</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linnea Åsedahl</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36345-2022 artfynd.xlsx
+++ b/artfynd/A 36345-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360614</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338719</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360557</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360857</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338702</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360492</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302941</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988630</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302938</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338701</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338709</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360782</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2170,6 +2245,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302939</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2267,6 +2347,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338713</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,6 +2449,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338716</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2461,6 +2551,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338717</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2562,6 +2657,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360624</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988617</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2774,6 +2879,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360472</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302936</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2973,6 +3088,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988633</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,6 +3195,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302933</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3177,6 +3302,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302934</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3279,6 +3409,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302935</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3381,6 +3516,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302937</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3490,6 +3630,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103360822</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3587,6 +3732,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302929</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3684,6 +3834,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302932</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3781,6 +3936,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302940</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3878,6 +4038,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338699</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3975,6 +4140,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338700</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4072,6 +4242,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338711</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4169,6 +4344,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988615</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4266,6 +4446,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988619</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4363,6 +4548,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988625</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4460,6 +4650,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988629</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4557,6 +4752,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988632</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4654,6 +4854,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338703</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4751,6 +4956,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338712</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4848,6 +5058,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121338721</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4945,6 +5160,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121988616</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5042,8 +5262,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120302927</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>